--- a/docs/reports/swift_space_weather_2026-09.xlsx
+++ b/docs/reports/swift_space_weather_2026-09.xlsx
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-16T13:41:12Z</t>
+    <t>2026-09-16T13:42:12Z</t>
   </si>
   <si>
     <t>Workbook</t>
@@ -1206,10 +1206,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>32.5</c:v>
+                  <c:v>45.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>95.5</c:v>
+                  <c:v>94.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2340,232 +2340,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>535.8200000000001</c:v>
+                  <c:v>527.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>528.92</c:v>
+                  <c:v>520.9400000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>525.62</c:v>
+                  <c:v>517.64</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>522.12</c:v>
+                  <c:v>514.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>522.84</c:v>
+                  <c:v>515.02</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>525.46</c:v>
+                  <c:v>517.6900000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>531.85</c:v>
+                  <c:v>524.11</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>543.09</c:v>
+                  <c:v>535.4299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>561.08</c:v>
+                  <c:v>553.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>583.42</c:v>
+                  <c:v>576.42</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>601.01</c:v>
+                  <c:v>593.87</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>619.8</c:v>
+                  <c:v>612.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>636.9</c:v>
+                  <c:v>629.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>647.72</c:v>
+                  <c:v>640.53</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>654.1900000000001</c:v>
+                  <c:v>646.99</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>657.64</c:v>
+                  <c:v>650.4400000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>658.97</c:v>
+                  <c:v>651.77</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>660.3200000000001</c:v>
+                  <c:v>653.12</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>656.73</c:v>
+                  <c:v>649.52</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>656.97</c:v>
+                  <c:v>649.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>659.4400000000001</c:v>
+                  <c:v>652.23</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>661.9400000000001</c:v>
+                  <c:v>654.73</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>659.24</c:v>
+                  <c:v>652.02</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>657.83</c:v>
+                  <c:v>650.6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>654.9</c:v>
+                  <c:v>647.65</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>649.34</c:v>
+                  <c:v>642.0599999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>641.17</c:v>
+                  <c:v>633.86</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>629.09</c:v>
+                  <c:v>621.72</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>615.04</c:v>
+                  <c:v>607.6</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>600.1799999999999</c:v>
+                  <c:v>592.6900000000001</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>585.23</c:v>
+                  <c:v>577.67</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>570.59</c:v>
+                  <c:v>562.96</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>556.49</c:v>
+                  <c:v>548.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>542.92</c:v>
+                  <c:v>535.17</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>528.5599999999999</c:v>
+                  <c:v>520.74</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>515.51</c:v>
+                  <c:v>507.64</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>503.54</c:v>
+                  <c:v>495.61</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>492.47</c:v>
+                  <c:v>484.5</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>482.22</c:v>
+                  <c:v>474.2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>471.98</c:v>
+                  <c:v>463.92</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>463.75</c:v>
+                  <c:v>455.64</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>457.01</c:v>
+                  <c:v>448.87</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>451.5</c:v>
+                  <c:v>443.34</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>447.18</c:v>
+                  <c:v>439</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>444.17</c:v>
+                  <c:v>435.98</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>441.87</c:v>
+                  <c:v>433.67</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>441.12</c:v>
+                  <c:v>432.91</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>442.72</c:v>
+                  <c:v>434.52</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>447.41</c:v>
+                  <c:v>439.22</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>450.22</c:v>
+                  <c:v>442.05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>459.16</c:v>
+                  <c:v>451.02</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>470.61</c:v>
+                  <c:v>462.51</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>485.87</c:v>
+                  <c:v>477.84</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>502.34</c:v>
+                  <c:v>494.38</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>517.29</c:v>
+                  <c:v>509.39</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>528.17</c:v>
+                  <c:v>520.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>530.75</c:v>
+                  <c:v>522.9</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>525.6799999999999</c:v>
+                  <c:v>517.8200000000001</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>518.36</c:v>
+                  <c:v>510.46</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>509.89</c:v>
+                  <c:v>501.96</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>498.69</c:v>
+                  <c:v>490.71</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>488.46</c:v>
+                  <c:v>480.43</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>479.02</c:v>
+                  <c:v>470.95</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>468.05</c:v>
+                  <c:v>459.93</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>458.76</c:v>
+                  <c:v>450.6</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>450.67</c:v>
+                  <c:v>442.48</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>443.48</c:v>
+                  <c:v>435.25</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>436.98</c:v>
+                  <c:v>428.73</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>431.04</c:v>
+                  <c:v>422.77</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>425.58</c:v>
+                  <c:v>417.28</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>420.52</c:v>
+                  <c:v>412.2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>415.82</c:v>
+                  <c:v>407.48</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>411.45</c:v>
+                  <c:v>403.09</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>407.37</c:v>
+                  <c:v>399</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>403.57</c:v>
+                  <c:v>395.17</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>400.01</c:v>
+                  <c:v>391.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2824,232 +2824,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>340.55</c:v>
+                  <c:v>331.71</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>336.51</c:v>
+                  <c:v>327.72</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>336.15</c:v>
+                  <c:v>327.37</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>336.93</c:v>
+                  <c:v>328.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>337.56</c:v>
+                  <c:v>328.96</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>337.98</c:v>
+                  <c:v>329.42</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>338.63</c:v>
+                  <c:v>330.08</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>339.79</c:v>
+                  <c:v>331.26</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>343.26</c:v>
+                  <c:v>335.01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>347.41</c:v>
+                  <c:v>339.41</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>344.73</c:v>
+                  <c:v>336.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>343.32</c:v>
+                  <c:v>334.96</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>342.68</c:v>
+                  <c:v>334.24</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>342.53</c:v>
+                  <c:v>334.04</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>342.66</c:v>
+                  <c:v>334.15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>342.63</c:v>
+                  <c:v>334.11</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>342.47</c:v>
+                  <c:v>333.94</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>342.16</c:v>
+                  <c:v>333.63</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>341.76</c:v>
+                  <c:v>333.22</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>341.3</c:v>
+                  <c:v>332.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>340.81</c:v>
+                  <c:v>332.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>340.64</c:v>
+                  <c:v>332.08</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>340.68</c:v>
+                  <c:v>332.11</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>340.84</c:v>
+                  <c:v>332.27</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>341.08</c:v>
+                  <c:v>332.51</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>341.38</c:v>
+                  <c:v>332.8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>341.7</c:v>
+                  <c:v>333.13</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>341.89</c:v>
+                  <c:v>333.31</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>341.99</c:v>
+                  <c:v>333.41</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>342.04</c:v>
+                  <c:v>333.45</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>342.06</c:v>
+                  <c:v>333.47</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>342.06</c:v>
+                  <c:v>333.47</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>342.05</c:v>
+                  <c:v>333.45</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>341.91</c:v>
+                  <c:v>333.31</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>341.7</c:v>
+                  <c:v>333.09</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>341.43</c:v>
+                  <c:v>332.83</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>341.14</c:v>
+                  <c:v>332.53</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>340.83</c:v>
+                  <c:v>332.22</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>340.51</c:v>
+                  <c:v>331.89</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>341.13</c:v>
+                  <c:v>332.51</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>342.33</c:v>
+                  <c:v>333.72</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>343.9</c:v>
+                  <c:v>335.29</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>345.68</c:v>
+                  <c:v>337.08</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>347.61</c:v>
+                  <c:v>339.01</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>349.63</c:v>
+                  <c:v>341.04</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>350.79</c:v>
+                  <c:v>342.2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>351.42</c:v>
+                  <c:v>342.83</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>351.72</c:v>
+                  <c:v>343.13</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>351.81</c:v>
+                  <c:v>343.22</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>351.79</c:v>
+                  <c:v>343.19</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>351.68</c:v>
+                  <c:v>343.09</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>351.53</c:v>
+                  <c:v>342.94</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>351.35</c:v>
+                  <c:v>342.76</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>351.16</c:v>
+                  <c:v>342.56</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>350.96</c:v>
+                  <c:v>342.36</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>350.75</c:v>
+                  <c:v>342.15</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>350.54</c:v>
+                  <c:v>341.93</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>350.32</c:v>
+                  <c:v>341.72</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>350.11</c:v>
+                  <c:v>341.5</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>349.89</c:v>
+                  <c:v>341.28</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>349.68</c:v>
+                  <c:v>341.06</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>349.46</c:v>
+                  <c:v>340.85</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>349.25</c:v>
+                  <c:v>340.63</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>349.11</c:v>
+                  <c:v>340.49</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>349.01</c:v>
+                  <c:v>340.39</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>348.95</c:v>
+                  <c:v>340.33</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>348.9</c:v>
+                  <c:v>340.28</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>348.87</c:v>
+                  <c:v>340.24</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>348.84</c:v>
+                  <c:v>340.22</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>348.82</c:v>
+                  <c:v>340.19</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>348.8</c:v>
+                  <c:v>340.17</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>348.78</c:v>
+                  <c:v>340.15</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>348.76</c:v>
+                  <c:v>340.14</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>348.75</c:v>
+                  <c:v>340.12</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>348.74</c:v>
+                  <c:v>340.11</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>348.72</c:v>
+                  <c:v>340.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,79 +4203,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-11.44</c:v>
+                  <c:v>-11.59</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.46</c:v>
+                  <c:v>-10.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10.62</c:v>
+                  <c:v>-10.78</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-11.47</c:v>
+                  <c:v>-11.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-11</c:v>
+                  <c:v>-11.16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.75</c:v>
+                  <c:v>-11.91</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-12.07</c:v>
+                  <c:v>-12.23</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-12.21</c:v>
+                  <c:v>-12.37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-12.22</c:v>
+                  <c:v>-12.38</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-11.19</c:v>
+                  <c:v>-11.34</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-9.33</c:v>
+                  <c:v>-9.49</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-7.43</c:v>
+                  <c:v>-7.58</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.01</c:v>
+                  <c:v>-6.17</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.93</c:v>
+                  <c:v>-6.08</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-7.33</c:v>
+                  <c:v>-7.49</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-9.220000000000001</c:v>
+                  <c:v>-9.369999999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-11.1</c:v>
+                  <c:v>-11.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-12.24</c:v>
+                  <c:v>-12.39</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-12.12</c:v>
+                  <c:v>-12.27</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-10.81</c:v>
+                  <c:v>-10.97</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-8.92</c:v>
+                  <c:v>-9.08</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-7.16</c:v>
+                  <c:v>-7.31</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-5.93</c:v>
+                  <c:v>-6.08</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-5.25</c:v>
+                  <c:v>-5.41</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-4.96</c:v>
+                  <c:v>-5.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4381,46 +4381,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>12.04</c:v>
+                  <c:v>12.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.11</c:v>
+                  <c:v>11.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.3</c:v>
+                  <c:v>11.28</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.11</c:v>
+                  <c:v>12.08</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.67</c:v>
+                  <c:v>11.65</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.25</c:v>
+                  <c:v>12.23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.48</c:v>
+                  <c:v>12.46</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.51</c:v>
+                  <c:v>12.49</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.39</c:v>
+                  <c:v>12.37</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.31</c:v>
+                  <c:v>11.28</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.51</c:v>
+                  <c:v>9.49</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.69</c:v>
+                  <c:v>7.67</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.32</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.15</c:v>
+                  <c:v>6.14</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>7.34</c:v>
@@ -4429,19 +4429,19 @@
                   <c:v>8.949999999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.63</c:v>
+                  <c:v>10.6</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.73</c:v>
+                  <c:v>11.71</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11.62</c:v>
+                  <c:v>11.6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>10.38</c:v>
+                  <c:v>10.36</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.630000000000001</c:v>
+                  <c:v>8.609999999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>7.04</c:v>
@@ -5481,7 +5481,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="4">
-        <v>85.8</v>
+        <v>87.2</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>30</v>
@@ -5510,7 +5510,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>22.36</v>
+        <v>23.96</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>15</v>
@@ -5539,7 +5539,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="4">
-        <v>5.26</v>
+        <v>-2.25</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>15</v>
@@ -5595,10 +5595,10 @@
         <v>77</v>
       </c>
       <c r="L23" s="4">
-        <v>32.5</v>
+        <v>45.5</v>
       </c>
       <c r="M23" s="4">
-        <v>63.1</v>
+        <v>56</v>
       </c>
       <c r="N23" s="4">
         <v>7</v>
@@ -5636,10 +5636,10 @@
         <v>423</v>
       </c>
       <c r="L24" s="4">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="M24" s="4">
-        <v>14.9</v>
+        <v>18.1</v>
       </c>
       <c r="N24" s="4">
         <v>9</v>
@@ -6194,13 +6194,13 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B2" s="4">
-        <v>535.8200000000001</v>
+        <v>527.8099999999999</v>
       </c>
       <c r="C2" s="4">
-        <v>340.55</v>
+        <v>331.71</v>
       </c>
       <c r="D2" s="4">
-        <v>541.3</v>
+        <v>541.97</v>
       </c>
       <c r="E2" s="4">
         <v>253.37</v>
@@ -6215,13 +6215,13 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B3" s="4">
-        <v>528.92</v>
+        <v>520.9400000000001</v>
       </c>
       <c r="C3" s="4">
-        <v>336.51</v>
+        <v>327.72</v>
       </c>
       <c r="D3" s="4">
-        <v>540.14</v>
+        <v>539.33</v>
       </c>
       <c r="E3" s="4">
         <v>249.65</v>
@@ -6236,13 +6236,13 @@
         <v>46281.5</v>
       </c>
       <c r="B4" s="4">
-        <v>525.62</v>
+        <v>517.64</v>
       </c>
       <c r="C4" s="4">
-        <v>336.15</v>
+        <v>327.37</v>
       </c>
       <c r="D4" s="4">
-        <v>538.5</v>
+        <v>537.7</v>
       </c>
       <c r="E4" s="4">
         <v>245.84</v>
@@ -6257,13 +6257,13 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B5" s="4">
-        <v>522.12</v>
+        <v>514.3200000000001</v>
       </c>
       <c r="C5" s="4">
-        <v>336.93</v>
+        <v>328.35</v>
       </c>
       <c r="D5" s="4">
-        <v>561.85</v>
+        <v>562.15</v>
       </c>
       <c r="E5" s="4">
         <v>240.28</v>
@@ -6278,10 +6278,10 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B6" s="4">
-        <v>522.84</v>
+        <v>515.02</v>
       </c>
       <c r="C6" s="4">
-        <v>337.56</v>
+        <v>328.96</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -6297,10 +6297,10 @@
         <v>46281.625</v>
       </c>
       <c r="B7" s="4">
-        <v>525.46</v>
+        <v>517.6900000000001</v>
       </c>
       <c r="C7" s="4">
-        <v>337.98</v>
+        <v>329.42</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4">
@@ -6316,10 +6316,10 @@
         <v>46281.66666666666</v>
       </c>
       <c r="B8" s="4">
-        <v>531.85</v>
+        <v>524.11</v>
       </c>
       <c r="C8" s="4">
-        <v>338.63</v>
+        <v>330.08</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4">
@@ -6335,10 +6335,10 @@
         <v>46281.70833333334</v>
       </c>
       <c r="B9" s="4">
-        <v>543.09</v>
+        <v>535.4299999999999</v>
       </c>
       <c r="C9" s="4">
-        <v>339.79</v>
+        <v>331.26</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4">
@@ -6354,10 +6354,10 @@
         <v>46281.75</v>
       </c>
       <c r="B10" s="4">
-        <v>561.08</v>
+        <v>553.75</v>
       </c>
       <c r="C10" s="4">
-        <v>343.26</v>
+        <v>335.01</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4">
@@ -6373,10 +6373,10 @@
         <v>46281.79166666666</v>
       </c>
       <c r="B11" s="4">
-        <v>583.42</v>
+        <v>576.42</v>
       </c>
       <c r="C11" s="4">
-        <v>347.41</v>
+        <v>339.41</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4">
@@ -6392,10 +6392,10 @@
         <v>46281.83333333334</v>
       </c>
       <c r="B12" s="4">
-        <v>601.01</v>
+        <v>593.87</v>
       </c>
       <c r="C12" s="4">
-        <v>344.73</v>
+        <v>336.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4">
@@ -6411,10 +6411,10 @@
         <v>46281.875</v>
       </c>
       <c r="B13" s="4">
-        <v>619.8</v>
+        <v>612.6</v>
       </c>
       <c r="C13" s="4">
-        <v>343.32</v>
+        <v>334.96</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4">
@@ -6430,10 +6430,10 @@
         <v>46281.91666666666</v>
       </c>
       <c r="B14" s="4">
-        <v>636.9</v>
+        <v>629.7</v>
       </c>
       <c r="C14" s="4">
-        <v>342.68</v>
+        <v>334.24</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4">
@@ -6449,10 +6449,10 @@
         <v>46281.95833333334</v>
       </c>
       <c r="B15" s="4">
-        <v>647.72</v>
+        <v>640.53</v>
       </c>
       <c r="C15" s="4">
-        <v>342.53</v>
+        <v>334.04</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4">
@@ -6468,10 +6468,10 @@
         <v>46282</v>
       </c>
       <c r="B16" s="4">
-        <v>654.1900000000001</v>
+        <v>646.99</v>
       </c>
       <c r="C16" s="4">
-        <v>342.66</v>
+        <v>334.15</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4">
@@ -6487,10 +6487,10 @@
         <v>46282.04166666666</v>
       </c>
       <c r="B17" s="4">
-        <v>657.64</v>
+        <v>650.4400000000001</v>
       </c>
       <c r="C17" s="4">
-        <v>342.63</v>
+        <v>334.11</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4">
@@ -6506,10 +6506,10 @@
         <v>46282.08333333334</v>
       </c>
       <c r="B18" s="4">
-        <v>658.97</v>
+        <v>651.77</v>
       </c>
       <c r="C18" s="4">
-        <v>342.47</v>
+        <v>333.94</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4">
@@ -6525,10 +6525,10 @@
         <v>46282.125</v>
       </c>
       <c r="B19" s="4">
-        <v>660.3200000000001</v>
+        <v>653.12</v>
       </c>
       <c r="C19" s="4">
-        <v>342.16</v>
+        <v>333.63</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4">
@@ -6544,10 +6544,10 @@
         <v>46282.16666666666</v>
       </c>
       <c r="B20" s="4">
-        <v>656.73</v>
+        <v>649.52</v>
       </c>
       <c r="C20" s="4">
-        <v>341.76</v>
+        <v>333.22</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4">
@@ -6563,10 +6563,10 @@
         <v>46282.20833333334</v>
       </c>
       <c r="B21" s="4">
-        <v>656.97</v>
+        <v>649.75</v>
       </c>
       <c r="C21" s="4">
-        <v>341.3</v>
+        <v>332.75</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4">
@@ -6582,10 +6582,10 @@
         <v>46282.25</v>
       </c>
       <c r="B22" s="4">
-        <v>659.4400000000001</v>
+        <v>652.23</v>
       </c>
       <c r="C22" s="4">
-        <v>340.81</v>
+        <v>332.25</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4">
@@ -6601,10 +6601,10 @@
         <v>46282.29166666666</v>
       </c>
       <c r="B23" s="4">
-        <v>661.9400000000001</v>
+        <v>654.73</v>
       </c>
       <c r="C23" s="4">
-        <v>340.64</v>
+        <v>332.08</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4">
@@ -6620,10 +6620,10 @@
         <v>46282.33333333334</v>
       </c>
       <c r="B24" s="4">
-        <v>659.24</v>
+        <v>652.02</v>
       </c>
       <c r="C24" s="4">
-        <v>340.68</v>
+        <v>332.11</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4">
@@ -6639,10 +6639,10 @@
         <v>46282.375</v>
       </c>
       <c r="B25" s="4">
-        <v>657.83</v>
+        <v>650.6</v>
       </c>
       <c r="C25" s="4">
-        <v>340.84</v>
+        <v>332.27</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4">
@@ -6658,10 +6658,10 @@
         <v>46282.41666666666</v>
       </c>
       <c r="B26" s="4">
-        <v>654.9</v>
+        <v>647.65</v>
       </c>
       <c r="C26" s="4">
-        <v>341.08</v>
+        <v>332.51</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4">
@@ -6677,10 +6677,10 @@
         <v>46282.45833333334</v>
       </c>
       <c r="B27" s="4">
-        <v>649.34</v>
+        <v>642.0599999999999</v>
       </c>
       <c r="C27" s="4">
-        <v>341.38</v>
+        <v>332.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4">
@@ -6696,10 +6696,10 @@
         <v>46282.5</v>
       </c>
       <c r="B28" s="4">
-        <v>641.17</v>
+        <v>633.86</v>
       </c>
       <c r="C28" s="4">
-        <v>341.7</v>
+        <v>333.13</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4">
@@ -6715,10 +6715,10 @@
         <v>46282.54166666666</v>
       </c>
       <c r="B29" s="4">
-        <v>629.09</v>
+        <v>621.72</v>
       </c>
       <c r="C29" s="4">
-        <v>341.89</v>
+        <v>333.31</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4">
@@ -6734,10 +6734,10 @@
         <v>46282.58333333334</v>
       </c>
       <c r="B30" s="4">
-        <v>615.04</v>
+        <v>607.6</v>
       </c>
       <c r="C30" s="4">
-        <v>341.99</v>
+        <v>333.41</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4">
@@ -6753,10 +6753,10 @@
         <v>46282.625</v>
       </c>
       <c r="B31" s="4">
-        <v>600.1799999999999</v>
+        <v>592.6900000000001</v>
       </c>
       <c r="C31" s="4">
-        <v>342.04</v>
+        <v>333.45</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4">
@@ -6772,10 +6772,10 @@
         <v>46282.66666666666</v>
       </c>
       <c r="B32" s="4">
-        <v>585.23</v>
+        <v>577.67</v>
       </c>
       <c r="C32" s="4">
-        <v>342.06</v>
+        <v>333.47</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4">
@@ -6791,10 +6791,10 @@
         <v>46282.70833333334</v>
       </c>
       <c r="B33" s="4">
-        <v>570.59</v>
+        <v>562.96</v>
       </c>
       <c r="C33" s="4">
-        <v>342.06</v>
+        <v>333.47</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4">
@@ -6810,10 +6810,10 @@
         <v>46282.75</v>
       </c>
       <c r="B34" s="4">
-        <v>556.49</v>
+        <v>548.8</v>
       </c>
       <c r="C34" s="4">
-        <v>342.05</v>
+        <v>333.45</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4">
@@ -6829,10 +6829,10 @@
         <v>46282.79166666666</v>
       </c>
       <c r="B35" s="4">
-        <v>542.92</v>
+        <v>535.17</v>
       </c>
       <c r="C35" s="4">
-        <v>341.91</v>
+        <v>333.31</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4">
@@ -6848,10 +6848,10 @@
         <v>46282.83333333334</v>
       </c>
       <c r="B36" s="4">
-        <v>528.5599999999999</v>
+        <v>520.74</v>
       </c>
       <c r="C36" s="4">
-        <v>341.7</v>
+        <v>333.09</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4">
@@ -6867,10 +6867,10 @@
         <v>46282.875</v>
       </c>
       <c r="B37" s="4">
-        <v>515.51</v>
+        <v>507.64</v>
       </c>
       <c r="C37" s="4">
-        <v>341.43</v>
+        <v>332.83</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4">
@@ -6886,10 +6886,10 @@
         <v>46282.91666666666</v>
       </c>
       <c r="B38" s="4">
-        <v>503.54</v>
+        <v>495.61</v>
       </c>
       <c r="C38" s="4">
-        <v>341.14</v>
+        <v>332.53</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4">
@@ -6905,10 +6905,10 @@
         <v>46282.95833333334</v>
       </c>
       <c r="B39" s="4">
-        <v>492.47</v>
+        <v>484.5</v>
       </c>
       <c r="C39" s="4">
-        <v>340.83</v>
+        <v>332.22</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4">
@@ -6924,10 +6924,10 @@
         <v>46283</v>
       </c>
       <c r="B40" s="4">
-        <v>482.22</v>
+        <v>474.2</v>
       </c>
       <c r="C40" s="4">
-        <v>340.51</v>
+        <v>331.89</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4">
@@ -6943,10 +6943,10 @@
         <v>46283.04166666666</v>
       </c>
       <c r="B41" s="4">
-        <v>471.98</v>
+        <v>463.92</v>
       </c>
       <c r="C41" s="4">
-        <v>341.13</v>
+        <v>332.51</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4">
@@ -6962,10 +6962,10 @@
         <v>46283.08333333334</v>
       </c>
       <c r="B42" s="4">
-        <v>463.75</v>
+        <v>455.64</v>
       </c>
       <c r="C42" s="4">
-        <v>342.33</v>
+        <v>333.72</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4">
@@ -6981,10 +6981,10 @@
         <v>46283.125</v>
       </c>
       <c r="B43" s="4">
-        <v>457.01</v>
+        <v>448.87</v>
       </c>
       <c r="C43" s="4">
-        <v>343.9</v>
+        <v>335.29</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4">
@@ -7000,10 +7000,10 @@
         <v>46283.16666666666</v>
       </c>
       <c r="B44" s="4">
-        <v>451.5</v>
+        <v>443.34</v>
       </c>
       <c r="C44" s="4">
-        <v>345.68</v>
+        <v>337.08</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4">
@@ -7019,10 +7019,10 @@
         <v>46283.20833333334</v>
       </c>
       <c r="B45" s="4">
-        <v>447.18</v>
+        <v>439</v>
       </c>
       <c r="C45" s="4">
-        <v>347.61</v>
+        <v>339.01</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4">
@@ -7038,10 +7038,10 @@
         <v>46283.25</v>
       </c>
       <c r="B46" s="4">
-        <v>444.17</v>
+        <v>435.98</v>
       </c>
       <c r="C46" s="4">
-        <v>349.63</v>
+        <v>341.04</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4">
@@ -7057,10 +7057,10 @@
         <v>46283.29166666666</v>
       </c>
       <c r="B47" s="4">
-        <v>441.87</v>
+        <v>433.67</v>
       </c>
       <c r="C47" s="4">
-        <v>350.79</v>
+        <v>342.2</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4">
@@ -7076,10 +7076,10 @@
         <v>46283.33333333334</v>
       </c>
       <c r="B48" s="4">
-        <v>441.12</v>
+        <v>432.91</v>
       </c>
       <c r="C48" s="4">
-        <v>351.42</v>
+        <v>342.83</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4">
@@ -7095,10 +7095,10 @@
         <v>46283.375</v>
       </c>
       <c r="B49" s="4">
-        <v>442.72</v>
+        <v>434.52</v>
       </c>
       <c r="C49" s="4">
-        <v>351.72</v>
+        <v>343.13</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4">
@@ -7114,10 +7114,10 @@
         <v>46283.41666666666</v>
       </c>
       <c r="B50" s="4">
-        <v>447.41</v>
+        <v>439.22</v>
       </c>
       <c r="C50" s="4">
-        <v>351.81</v>
+        <v>343.22</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4">
@@ -7133,10 +7133,10 @@
         <v>46283.45833333334</v>
       </c>
       <c r="B51" s="4">
-        <v>450.22</v>
+        <v>442.05</v>
       </c>
       <c r="C51" s="4">
-        <v>351.79</v>
+        <v>343.19</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4">
@@ -7152,10 +7152,10 @@
         <v>46283.5</v>
       </c>
       <c r="B52" s="4">
-        <v>459.16</v>
+        <v>451.02</v>
       </c>
       <c r="C52" s="4">
-        <v>351.68</v>
+        <v>343.09</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4">
@@ -7171,10 +7171,10 @@
         <v>46283.54166666666</v>
       </c>
       <c r="B53" s="4">
-        <v>470.61</v>
+        <v>462.51</v>
       </c>
       <c r="C53" s="4">
-        <v>351.53</v>
+        <v>342.94</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
@@ -7190,10 +7190,10 @@
         <v>46283.58333333334</v>
       </c>
       <c r="B54" s="4">
-        <v>485.87</v>
+        <v>477.84</v>
       </c>
       <c r="C54" s="4">
-        <v>351.35</v>
+        <v>342.76</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4">
@@ -7209,10 +7209,10 @@
         <v>46283.625</v>
       </c>
       <c r="B55" s="4">
-        <v>502.34</v>
+        <v>494.38</v>
       </c>
       <c r="C55" s="4">
-        <v>351.16</v>
+        <v>342.56</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4">
@@ -7228,10 +7228,10 @@
         <v>46283.66666666666</v>
       </c>
       <c r="B56" s="4">
-        <v>517.29</v>
+        <v>509.39</v>
       </c>
       <c r="C56" s="4">
-        <v>350.96</v>
+        <v>342.36</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4">
@@ -7247,10 +7247,10 @@
         <v>46283.70833333334</v>
       </c>
       <c r="B57" s="4">
-        <v>528.17</v>
+        <v>520.3200000000001</v>
       </c>
       <c r="C57" s="4">
-        <v>350.75</v>
+        <v>342.15</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4">
@@ -7266,10 +7266,10 @@
         <v>46283.75</v>
       </c>
       <c r="B58" s="4">
-        <v>530.75</v>
+        <v>522.9</v>
       </c>
       <c r="C58" s="4">
-        <v>350.54</v>
+        <v>341.93</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4">
@@ -7285,10 +7285,10 @@
         <v>46283.79166666666</v>
       </c>
       <c r="B59" s="4">
-        <v>525.6799999999999</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="C59" s="4">
-        <v>350.32</v>
+        <v>341.72</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4">
@@ -7304,10 +7304,10 @@
         <v>46283.83333333334</v>
       </c>
       <c r="B60" s="4">
-        <v>518.36</v>
+        <v>510.46</v>
       </c>
       <c r="C60" s="4">
-        <v>350.11</v>
+        <v>341.5</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4">
@@ -7323,10 +7323,10 @@
         <v>46283.875</v>
       </c>
       <c r="B61" s="4">
-        <v>509.89</v>
+        <v>501.96</v>
       </c>
       <c r="C61" s="4">
-        <v>349.89</v>
+        <v>341.28</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4">
@@ -7342,10 +7342,10 @@
         <v>46283.91666666666</v>
       </c>
       <c r="B62" s="4">
-        <v>498.69</v>
+        <v>490.71</v>
       </c>
       <c r="C62" s="4">
-        <v>349.68</v>
+        <v>341.06</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4">
@@ -7361,10 +7361,10 @@
         <v>46283.95833333334</v>
       </c>
       <c r="B63" s="4">
-        <v>488.46</v>
+        <v>480.43</v>
       </c>
       <c r="C63" s="4">
-        <v>349.46</v>
+        <v>340.85</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4">
@@ -7380,10 +7380,10 @@
         <v>46284</v>
       </c>
       <c r="B64" s="4">
-        <v>479.02</v>
+        <v>470.95</v>
       </c>
       <c r="C64" s="4">
-        <v>349.25</v>
+        <v>340.63</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4">
@@ -7399,10 +7399,10 @@
         <v>46284.04166666666</v>
       </c>
       <c r="B65" s="4">
-        <v>468.05</v>
+        <v>459.93</v>
       </c>
       <c r="C65" s="4">
-        <v>349.11</v>
+        <v>340.49</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4">
@@ -7418,10 +7418,10 @@
         <v>46284.08333333334</v>
       </c>
       <c r="B66" s="4">
-        <v>458.76</v>
+        <v>450.6</v>
       </c>
       <c r="C66" s="4">
-        <v>349.01</v>
+        <v>340.39</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4">
@@ -7437,10 +7437,10 @@
         <v>46284.125</v>
       </c>
       <c r="B67" s="4">
-        <v>450.67</v>
+        <v>442.48</v>
       </c>
       <c r="C67" s="4">
-        <v>348.95</v>
+        <v>340.33</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4">
@@ -7456,10 +7456,10 @@
         <v>46284.16666666666</v>
       </c>
       <c r="B68" s="4">
-        <v>443.48</v>
+        <v>435.25</v>
       </c>
       <c r="C68" s="4">
-        <v>348.9</v>
+        <v>340.28</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4">
@@ -7475,10 +7475,10 @@
         <v>46284.20833333334</v>
       </c>
       <c r="B69" s="4">
-        <v>436.98</v>
+        <v>428.73</v>
       </c>
       <c r="C69" s="4">
-        <v>348.87</v>
+        <v>340.24</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4">
@@ -7494,10 +7494,10 @@
         <v>46284.25</v>
       </c>
       <c r="B70" s="4">
-        <v>431.04</v>
+        <v>422.77</v>
       </c>
       <c r="C70" s="4">
-        <v>348.84</v>
+        <v>340.22</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4">
@@ -7513,10 +7513,10 @@
         <v>46284.29166666666</v>
       </c>
       <c r="B71" s="4">
-        <v>425.58</v>
+        <v>417.28</v>
       </c>
       <c r="C71" s="4">
-        <v>348.82</v>
+        <v>340.19</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4">
@@ -7532,10 +7532,10 @@
         <v>46284.33333333334</v>
       </c>
       <c r="B72" s="4">
-        <v>420.52</v>
+        <v>412.2</v>
       </c>
       <c r="C72" s="4">
-        <v>348.8</v>
+        <v>340.17</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4">
@@ -7551,10 +7551,10 @@
         <v>46284.375</v>
       </c>
       <c r="B73" s="4">
-        <v>415.82</v>
+        <v>407.48</v>
       </c>
       <c r="C73" s="4">
-        <v>348.78</v>
+        <v>340.15</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4">
@@ -7570,10 +7570,10 @@
         <v>46284.41666666666</v>
       </c>
       <c r="B74" s="4">
-        <v>411.45</v>
+        <v>403.09</v>
       </c>
       <c r="C74" s="4">
-        <v>348.76</v>
+        <v>340.14</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4">
@@ -7589,10 +7589,10 @@
         <v>46284.45833333334</v>
       </c>
       <c r="B75" s="4">
-        <v>407.37</v>
+        <v>399</v>
       </c>
       <c r="C75" s="4">
-        <v>348.75</v>
+        <v>340.12</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4">
@@ -7608,10 +7608,10 @@
         <v>46284.5</v>
       </c>
       <c r="B76" s="4">
-        <v>403.57</v>
+        <v>395.17</v>
       </c>
       <c r="C76" s="4">
-        <v>348.74</v>
+        <v>340.11</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4">
@@ -7627,10 +7627,10 @@
         <v>46284.54166666666</v>
       </c>
       <c r="B77" s="4">
-        <v>400.01</v>
+        <v>391.6</v>
       </c>
       <c r="C77" s="4">
-        <v>348.72</v>
+        <v>340.1</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4">
@@ -8098,19 +8098,19 @@
         <v>500</v>
       </c>
       <c r="D4" s="4">
-        <v>22.36</v>
+        <v>23.962</v>
       </c>
       <c r="E4" s="4">
-        <v>34.036</v>
+        <v>33.507</v>
       </c>
       <c r="F4" s="4">
-        <v>5.261</v>
+        <v>-2.248</v>
       </c>
       <c r="G4" s="4">
-        <v>85.8</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="4">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8124,19 +8124,19 @@
         <v>500</v>
       </c>
       <c r="D5" s="4">
-        <v>22.36</v>
+        <v>23.962</v>
       </c>
       <c r="E5" s="4">
-        <v>34.036</v>
+        <v>33.507</v>
       </c>
       <c r="F5" s="4">
-        <v>5.261</v>
+        <v>-2.248</v>
       </c>
       <c r="G5" s="4">
-        <v>85.8</v>
+        <v>87.2</v>
       </c>
       <c r="H5" s="4">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -8150,19 +8150,19 @@
         <v>500</v>
       </c>
       <c r="D6" s="4">
-        <v>22.36</v>
+        <v>23.962</v>
       </c>
       <c r="E6" s="4">
-        <v>34.036</v>
+        <v>33.507</v>
       </c>
       <c r="F6" s="4">
-        <v>5.261</v>
+        <v>-2.248</v>
       </c>
       <c r="G6" s="4">
-        <v>85.8</v>
+        <v>87.2</v>
       </c>
       <c r="H6" s="4">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -8299,11 +8299,11 @@
         <v>450.3</v>
       </c>
       <c r="C19" s="4">
-        <v>550.1799999999999</v>
+        <v>542.96</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4">
-        <v>99.87999999999994</v>
+        <v>92.66000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8314,11 +8314,11 @@
         <v>434.32</v>
       </c>
       <c r="C20" s="4">
-        <v>549.08</v>
+        <v>542.5700000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4">
-        <v>114.76</v>
+        <v>108.2500000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8326,14 +8326,14 @@
         <v>46280.92222222222</v>
       </c>
       <c r="B21" s="4">
-        <v>449.2</v>
+        <v>433.74</v>
       </c>
       <c r="C21" s="4">
-        <v>547.35</v>
+        <v>541.11</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4">
-        <v>98.15000000000003</v>
+        <v>107.37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8344,11 +8344,11 @@
         <v>435.21</v>
       </c>
       <c r="C22" s="4">
-        <v>546.6900000000001</v>
+        <v>540.72</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4">
-        <v>111.4800000000001</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8356,14 +8356,14 @@
         <v>46280.92430555556</v>
       </c>
       <c r="B23" s="4">
-        <v>457.1</v>
+        <v>445.73</v>
       </c>
       <c r="C23" s="4">
-        <v>545.65</v>
+        <v>539.9400000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4">
-        <v>88.54999999999995</v>
+        <v>94.21000000000004</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8374,11 +8374,11 @@
         <v>438.84</v>
       </c>
       <c r="C24" s="4">
-        <v>545.03</v>
+        <v>538.76</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4">
-        <v>106.19</v>
+        <v>99.92000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8386,14 +8386,14 @@
         <v>46280.92638888889</v>
       </c>
       <c r="B25" s="4">
-        <v>450.9</v>
+        <v>475.7</v>
       </c>
       <c r="C25" s="4">
-        <v>543.61</v>
+        <v>537.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4">
-        <v>92.71000000000004</v>
+        <v>61.50000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8404,11 +8404,11 @@
         <v>440.73</v>
       </c>
       <c r="C26" s="4">
-        <v>542.27</v>
+        <v>536.75</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4">
-        <v>101.54</v>
+        <v>96.01999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8416,14 +8416,14 @@
         <v>46280.92847222222</v>
       </c>
       <c r="B27" s="4">
-        <v>464.3</v>
+        <v>459.18</v>
       </c>
       <c r="C27" s="4">
-        <v>540.83</v>
+        <v>534.3099999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4">
-        <v>76.53000000000003</v>
+        <v>75.12999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8434,11 +8434,11 @@
         <v>449.48</v>
       </c>
       <c r="C28" s="4">
-        <v>539.97</v>
+        <v>533.13</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4">
-        <v>90.49000000000001</v>
+        <v>83.64999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8449,11 +8449,11 @@
         <v>417.65</v>
       </c>
       <c r="C29" s="4">
-        <v>538.85</v>
+        <v>531.09</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4">
-        <v>121.2</v>
+        <v>113.4400000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8464,11 +8464,11 @@
         <v>444.48</v>
       </c>
       <c r="C30" s="4">
-        <v>537.8</v>
+        <v>530.29</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4">
-        <v>93.31999999999994</v>
+        <v>85.80999999999995</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8479,11 +8479,11 @@
         <v>442.77</v>
       </c>
       <c r="C31" s="4">
-        <v>536.72</v>
+        <v>529.15</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4">
-        <v>93.95000000000005</v>
+        <v>86.38</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8494,11 +8494,11 @@
         <v>434.41</v>
       </c>
       <c r="C32" s="4">
-        <v>536.3</v>
+        <v>528.76</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4">
-        <v>101.8899999999999</v>
+        <v>94.34999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8509,11 +8509,11 @@
         <v>467.89</v>
       </c>
       <c r="C33" s="4">
-        <v>535.79</v>
+        <v>528.23</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4">
-        <v>67.89999999999998</v>
+        <v>60.34000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8524,11 +8524,11 @@
         <v>428.23</v>
       </c>
       <c r="C34" s="4">
-        <v>535.36</v>
+        <v>527.77</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4">
-        <v>107.13</v>
+        <v>99.53999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8539,11 +8539,11 @@
         <v>405.44</v>
       </c>
       <c r="C35" s="4">
-        <v>534.23</v>
+        <v>526.55</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4">
-        <v>128.79</v>
+        <v>121.11</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8554,11 +8554,11 @@
         <v>436.59</v>
       </c>
       <c r="C36" s="4">
-        <v>533.77</v>
+        <v>525.92</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4">
-        <v>97.18000000000001</v>
+        <v>89.32999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8566,14 +8566,14 @@
         <v>46280.93888888889</v>
       </c>
       <c r="B37" s="4">
-        <v>476.8</v>
+        <v>485.84</v>
       </c>
       <c r="C37" s="4">
-        <v>531.52</v>
+        <v>522.53</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4">
-        <v>54.71999999999997</v>
+        <v>36.69</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8584,11 +8584,11 @@
         <v>433.29</v>
       </c>
       <c r="C38" s="4">
-        <v>531.0599999999999</v>
+        <v>521.96</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4">
-        <v>97.76999999999992</v>
+        <v>88.67000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8599,11 +8599,11 @@
         <v>479.54</v>
       </c>
       <c r="C39" s="4">
-        <v>529.13</v>
+        <v>520.84</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4">
-        <v>49.58999999999997</v>
+        <v>41.30000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8614,11 +8614,11 @@
         <v>446.83</v>
       </c>
       <c r="C40" s="4">
-        <v>528.45</v>
+        <v>518.95</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4">
-        <v>81.62000000000006</v>
+        <v>72.12000000000006</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8629,11 +8629,11 @@
         <v>522.79</v>
       </c>
       <c r="C41" s="4">
-        <v>526.28</v>
+        <v>518.04</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4">
-        <v>3.490000000000009</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8644,11 +8644,11 @@
         <v>449.38</v>
       </c>
       <c r="C42" s="4">
-        <v>525.1799999999999</v>
+        <v>517.13</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4">
-        <v>75.79999999999995</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -8656,14 +8656,14 @@
         <v>46280.94513888889</v>
       </c>
       <c r="B43" s="4">
-        <v>451.19</v>
+        <v>475.2</v>
       </c>
       <c r="C43" s="4">
-        <v>523.97</v>
+        <v>516.37</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4">
-        <v>72.78000000000003</v>
+        <v>41.17000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -8674,11 +8674,11 @@
         <v>440.84</v>
       </c>
       <c r="C44" s="4">
-        <v>523.63</v>
+        <v>516.1</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4">
-        <v>82.79000000000002</v>
+        <v>75.26000000000005</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -8689,11 +8689,11 @@
         <v>429.56</v>
       </c>
       <c r="C45" s="4">
-        <v>523.09</v>
+        <v>515.39</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4">
-        <v>93.53000000000003</v>
+        <v>85.82999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -8704,11 +8704,11 @@
         <v>439.86</v>
       </c>
       <c r="C46" s="4">
-        <v>522.65</v>
+        <v>514.8</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4">
-        <v>82.78999999999996</v>
+        <v>74.93999999999994</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -8719,11 +8719,11 @@
         <v>465.49</v>
       </c>
       <c r="C47" s="4">
-        <v>521.74</v>
+        <v>513.97</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4">
-        <v>56.25</v>
+        <v>48.48000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -8734,11 +8734,11 @@
         <v>441.12</v>
       </c>
       <c r="C48" s="4">
-        <v>521.38</v>
+        <v>513.71</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4">
-        <v>80.25999999999999</v>
+        <v>72.59000000000003</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -8746,14 +8746,14 @@
         <v>46280.95138888889</v>
       </c>
       <c r="B49" s="4">
-        <v>491.7</v>
+        <v>464.22</v>
       </c>
       <c r="C49" s="4">
-        <v>520.49</v>
+        <v>513.11</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4">
-        <v>28.79000000000002</v>
+        <v>48.88999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -8764,11 +8764,11 @@
         <v>435.57</v>
       </c>
       <c r="C50" s="4">
-        <v>520.26</v>
+        <v>512.79</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4">
-        <v>84.69</v>
+        <v>77.21999999999997</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -8779,11 +8779,11 @@
         <v>509.37</v>
       </c>
       <c r="C51" s="4">
-        <v>519.59</v>
+        <v>512.0599999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4">
-        <v>10.22000000000003</v>
+        <v>2.689999999999941</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -8794,11 +8794,11 @@
         <v>454.07</v>
       </c>
       <c r="C52" s="4">
-        <v>519.3</v>
+        <v>511.46</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4">
-        <v>65.22999999999996</v>
+        <v>57.38999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -8806,14 +8806,14 @@
         <v>46280.95555555556</v>
       </c>
       <c r="B53" s="4">
-        <v>464.8</v>
+        <v>525.16</v>
       </c>
       <c r="C53" s="4">
-        <v>519</v>
+        <v>511.07</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
-        <v>54.19999999999999</v>
+        <v>-14.08999999999997</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -8824,11 +8824,11 @@
         <v>459.39</v>
       </c>
       <c r="C54" s="4">
-        <v>518.73</v>
+        <v>510.84</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4">
-        <v>59.34000000000003</v>
+        <v>51.44999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -8836,14 +8836,14 @@
         <v>46280.95763888889</v>
       </c>
       <c r="B55" s="4">
-        <v>452.8</v>
+        <v>468.61</v>
       </c>
       <c r="C55" s="4">
-        <v>518.21</v>
+        <v>510.13</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4">
-        <v>65.41000000000003</v>
+        <v>41.51999999999998</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -8854,11 +8854,11 @@
         <v>453.95</v>
       </c>
       <c r="C56" s="4">
-        <v>517.95</v>
+        <v>509.8</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4">
-        <v>64.00000000000006</v>
+        <v>55.85000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -8869,11 +8869,11 @@
         <v>482.6</v>
       </c>
       <c r="C57" s="4">
-        <v>517.05</v>
+        <v>509.27</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4">
-        <v>34.44999999999993</v>
+        <v>26.66999999999996</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -8884,11 +8884,11 @@
         <v>424.56</v>
       </c>
       <c r="C58" s="4">
-        <v>516.78</v>
+        <v>508.17</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4">
-        <v>92.21999999999997</v>
+        <v>83.61000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -8899,11 +8899,11 @@
         <v>492.49</v>
       </c>
       <c r="C59" s="4">
-        <v>516.03</v>
+        <v>507.7</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4">
-        <v>23.53999999999996</v>
+        <v>15.20999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -8914,11 +8914,11 @@
         <v>423.24</v>
       </c>
       <c r="C60" s="4">
-        <v>515.63</v>
+        <v>507.33</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4">
-        <v>92.38999999999999</v>
+        <v>84.08999999999997</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -8926,14 +8926,14 @@
         <v>46280.96388888889</v>
       </c>
       <c r="B61" s="4">
-        <v>450.7</v>
+        <v>472.49</v>
       </c>
       <c r="C61" s="4">
-        <v>515.34</v>
+        <v>506.88</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4">
-        <v>64.64000000000004</v>
+        <v>34.38999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -8944,11 +8944,11 @@
         <v>429.28</v>
       </c>
       <c r="C62" s="4">
-        <v>515.0599999999999</v>
+        <v>506.57</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4">
-        <v>85.77999999999997</v>
+        <v>77.29000000000002</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -8959,11 +8959,11 @@
         <v>479.47</v>
       </c>
       <c r="C63" s="4">
-        <v>513.98</v>
+        <v>505.65</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4">
-        <v>34.50999999999999</v>
+        <v>26.17999999999995</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -8974,11 +8974,11 @@
         <v>427.79</v>
       </c>
       <c r="C64" s="4">
-        <v>513.3</v>
+        <v>505.14</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4">
-        <v>85.50999999999993</v>
+        <v>77.34999999999997</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -8989,11 +8989,11 @@
         <v>458.7</v>
       </c>
       <c r="C65" s="4">
-        <v>512.49</v>
+        <v>504.51</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4">
-        <v>53.79000000000002</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -9004,11 +9004,11 @@
         <v>446.56</v>
       </c>
       <c r="C66" s="4">
-        <v>512.03</v>
+        <v>503.93</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4">
-        <v>65.46999999999997</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -9019,11 +9019,11 @@
         <v>449.85</v>
       </c>
       <c r="C67" s="4">
-        <v>511.57</v>
+        <v>503.51</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4">
-        <v>61.71999999999997</v>
+        <v>53.65999999999997</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -9034,11 +9034,11 @@
         <v>457.52</v>
       </c>
       <c r="C68" s="4">
-        <v>510.52</v>
+        <v>501.77</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4">
-        <v>53</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -9046,14 +9046,14 @@
         <v>46280.97222222222</v>
       </c>
       <c r="B69" s="4">
-        <v>445.65</v>
+        <v>464.9</v>
       </c>
       <c r="C69" s="4">
-        <v>509.93</v>
+        <v>500.54</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4">
-        <v>64.28000000000003</v>
+        <v>35.64000000000004</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -9064,11 +9064,11 @@
         <v>442.96</v>
       </c>
       <c r="C70" s="4">
-        <v>509.64</v>
+        <v>500.24</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4">
-        <v>66.68000000000001</v>
+        <v>57.28000000000003</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -9079,11 +9079,11 @@
         <v>446.77</v>
       </c>
       <c r="C71" s="4">
-        <v>508.45</v>
+        <v>498.99</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4">
-        <v>61.68000000000001</v>
+        <v>52.22000000000003</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -9094,11 +9094,11 @@
         <v>432.68</v>
       </c>
       <c r="C72" s="4">
-        <v>507.77</v>
+        <v>498.15</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4">
-        <v>75.08999999999997</v>
+        <v>65.46999999999997</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -9106,14 +9106,14 @@
         <v>46280.97638888889</v>
       </c>
       <c r="B73" s="4">
-        <v>464.4</v>
+        <v>461.2</v>
       </c>
       <c r="C73" s="4">
-        <v>506.82</v>
+        <v>497.68</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4">
-        <v>42.42000000000002</v>
+        <v>36.48000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -9124,11 +9124,11 @@
         <v>445.45</v>
       </c>
       <c r="C74" s="4">
-        <v>505.27</v>
+        <v>497.28</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4">
-        <v>59.81999999999999</v>
+        <v>51.82999999999998</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -9139,11 +9139,11 @@
         <v>390.5</v>
       </c>
       <c r="C75" s="4">
-        <v>504.5</v>
+        <v>496.33</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4">
-        <v>114</v>
+        <v>105.83</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -9154,11 +9154,11 @@
         <v>459.18</v>
       </c>
       <c r="C76" s="4">
-        <v>504.44</v>
+        <v>496.27</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4">
-        <v>45.25999999999999</v>
+        <v>37.08999999999997</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -9169,11 +9169,11 @@
         <v>435.85</v>
       </c>
       <c r="C77" s="4">
-        <v>503.75</v>
+        <v>495.67</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4">
-        <v>67.89999999999998</v>
+        <v>59.81999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -9184,11 +9184,11 @@
         <v>453.25</v>
       </c>
       <c r="C78" s="4">
-        <v>503.23</v>
+        <v>495.31</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4">
-        <v>49.98000000000002</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -9199,11 +9199,11 @@
         <v>465.6</v>
       </c>
       <c r="C79" s="4">
-        <v>502.93</v>
+        <v>494.93</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4">
-        <v>37.32999999999998</v>
+        <v>29.32999999999998</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -9214,11 +9214,11 @@
         <v>461.6</v>
       </c>
       <c r="C80" s="4">
-        <v>502.52</v>
+        <v>493.88</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4">
-        <v>40.91999999999996</v>
+        <v>32.27999999999997</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -9229,11 +9229,11 @@
         <v>471.47</v>
       </c>
       <c r="C81" s="4">
-        <v>501.46</v>
+        <v>493.62</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4">
-        <v>29.98999999999995</v>
+        <v>22.14999999999998</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -9244,11 +9244,11 @@
         <v>474.45</v>
       </c>
       <c r="C82" s="4">
-        <v>501.46</v>
+        <v>493.64</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4">
-        <v>27.00999999999999</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -9259,11 +9259,11 @@
         <v>525.5</v>
       </c>
       <c r="C83" s="4">
-        <v>501.36</v>
+        <v>493.6</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4">
-        <v>-24.13999999999999</v>
+        <v>-31.89999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -9274,11 +9274,11 @@
         <v>508.06</v>
       </c>
       <c r="C84" s="4">
-        <v>501.3</v>
+        <v>493.61</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4">
-        <v>-6.759999999999991</v>
+        <v>-14.44999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -9289,11 +9289,11 @@
         <v>467.21</v>
       </c>
       <c r="C85" s="4">
-        <v>501.28</v>
+        <v>494.31</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4">
-        <v>34.06999999999999</v>
+        <v>27.10000000000002</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -9304,11 +9304,11 @@
         <v>517.66</v>
       </c>
       <c r="C86" s="4">
-        <v>501.93</v>
+        <v>494.47</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4">
-        <v>-15.72999999999996</v>
+        <v>-23.18999999999994</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -9316,14 +9316,14 @@
         <v>46280.99097222222</v>
       </c>
       <c r="B87" s="4">
-        <v>508</v>
+        <v>517.61</v>
       </c>
       <c r="C87" s="4">
-        <v>501.94</v>
+        <v>494.41</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="4">
-        <v>-6.060000000000002</v>
+        <v>-23.19999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -9334,11 +9334,11 @@
         <v>506.12</v>
       </c>
       <c r="C88" s="4">
-        <v>502.36</v>
+        <v>494.65</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4">
-        <v>-3.759999999999991</v>
+        <v>-11.47000000000003</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -9349,11 +9349,11 @@
         <v>561.17</v>
       </c>
       <c r="C89" s="4">
-        <v>502.35</v>
+        <v>494.58</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4">
-        <v>-58.81999999999994</v>
+        <v>-66.58999999999997</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -9364,11 +9364,11 @@
         <v>493.36</v>
       </c>
       <c r="C90" s="4">
-        <v>503.25</v>
+        <v>494.67</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4">
-        <v>9.889999999999986</v>
+        <v>1.310000000000002</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -9376,14 +9376,14 @@
         <v>46280.99513888889</v>
       </c>
       <c r="B91" s="4">
-        <v>560.03</v>
+        <v>537.9</v>
       </c>
       <c r="C91" s="4">
-        <v>503.63</v>
+        <v>494.83</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4">
-        <v>-56.39999999999998</v>
+        <v>-43.06999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -9394,11 +9394,11 @@
         <v>493.66</v>
       </c>
       <c r="C92" s="4">
-        <v>504.02</v>
+        <v>495.46</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4">
-        <v>10.35999999999996</v>
+        <v>1.799999999999955</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -9406,14 +9406,14 @@
         <v>46280.99722222222</v>
       </c>
       <c r="B93" s="4">
-        <v>509.1</v>
+        <v>543.46</v>
       </c>
       <c r="C93" s="4">
-        <v>504.02</v>
+        <v>496.48</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4">
-        <v>-5.080000000000041</v>
+        <v>-46.98000000000002</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -9424,11 +9424,11 @@
         <v>486.02</v>
       </c>
       <c r="C94" s="4">
-        <v>504.13</v>
+        <v>497.04</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4">
-        <v>18.11000000000001</v>
+        <v>11.02000000000004</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -9436,14 +9436,14 @@
         <v>46280.99930555555</v>
       </c>
       <c r="B95" s="4">
-        <v>532.59</v>
+        <v>494.4</v>
       </c>
       <c r="C95" s="4">
-        <v>504.34</v>
+        <v>497.05</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4">
-        <v>-28.25000000000006</v>
+        <v>2.650000000000034</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -9454,11 +9454,11 @@
         <v>504.44</v>
       </c>
       <c r="C96" s="4">
-        <v>504.78</v>
+        <v>497.14</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4">
-        <v>0.339999999999975</v>
+        <v>-7.300000000000011</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -9466,14 +9466,14 @@
         <v>46281.00138888889</v>
       </c>
       <c r="B97" s="4">
-        <v>475.24</v>
+        <v>512.5</v>
       </c>
       <c r="C97" s="4">
-        <v>504.8</v>
+        <v>497.37</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4">
-        <v>29.56</v>
+        <v>-15.13</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -9484,11 +9484,11 @@
         <v>448.07</v>
       </c>
       <c r="C98" s="4">
-        <v>505.28</v>
+        <v>497.44</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4">
-        <v>57.20999999999998</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -9496,14 +9496,14 @@
         <v>46281.00347222222</v>
       </c>
       <c r="B99" s="4">
-        <v>578.01</v>
+        <v>515.4</v>
       </c>
       <c r="C99" s="4">
-        <v>505.42</v>
+        <v>497.48</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4">
-        <v>-72.58999999999997</v>
+        <v>-17.91999999999996</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -9514,11 +9514,11 @@
         <v>488.43</v>
       </c>
       <c r="C100" s="4">
-        <v>505.7</v>
+        <v>498.06</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4">
-        <v>17.26999999999998</v>
+        <v>9.629999999999995</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -9526,14 +9526,14 @@
         <v>46281.00555555556</v>
       </c>
       <c r="B101" s="4">
-        <v>540.5</v>
+        <v>543.37</v>
       </c>
       <c r="C101" s="4">
-        <v>505.75</v>
+        <v>497.9</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4">
-        <v>-34.75</v>
+        <v>-45.47000000000003</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -9544,11 +9544,11 @@
         <v>508.58</v>
       </c>
       <c r="C102" s="4">
-        <v>505.58</v>
+        <v>497.71</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4">
-        <v>-3</v>
+        <v>-10.87</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -9559,11 +9559,11 @@
         <v>522.8</v>
       </c>
       <c r="C103" s="4">
-        <v>505.86</v>
+        <v>497.91</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4">
-        <v>-16.93999999999994</v>
+        <v>-24.88999999999993</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -9574,11 +9574,11 @@
         <v>494.95</v>
       </c>
       <c r="C104" s="4">
-        <v>506.39</v>
+        <v>498.48</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4">
-        <v>11.44</v>
+        <v>3.53000000000003</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -9589,11 +9589,11 @@
         <v>459.03</v>
       </c>
       <c r="C105" s="4">
-        <v>506.51</v>
+        <v>498.49</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4">
-        <v>47.48000000000002</v>
+        <v>39.46000000000004</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -9604,11 +9604,11 @@
         <v>503.23</v>
       </c>
       <c r="C106" s="4">
-        <v>506.83</v>
+        <v>498.43</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4">
-        <v>3.599999999999966</v>
+        <v>-4.800000000000011</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -9616,14 +9616,14 @@
         <v>46281.01180555556</v>
       </c>
       <c r="B107" s="4">
-        <v>571.66</v>
+        <v>526</v>
       </c>
       <c r="C107" s="4">
-        <v>507.04</v>
+        <v>498.4</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4">
-        <v>-64.61999999999995</v>
+        <v>-27.60000000000002</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -9634,11 +9634,11 @@
         <v>500.29</v>
       </c>
       <c r="C108" s="4">
-        <v>507.51</v>
+        <v>498.35</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4">
-        <v>7.21999999999997</v>
+        <v>-1.939999999999998</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -9649,11 +9649,11 @@
         <v>566.42</v>
       </c>
       <c r="C109" s="4">
-        <v>507.73</v>
+        <v>498.31</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4">
-        <v>-58.68999999999994</v>
+        <v>-68.10999999999996</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -9664,11 +9664,11 @@
         <v>513.36</v>
       </c>
       <c r="C110" s="4">
-        <v>508.46</v>
+        <v>498.91</v>
       </c>
       <c r="D110" s="4"/>
       <c r="E110" s="4">
-        <v>-4.900000000000034</v>
+        <v>-14.44999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -9676,14 +9676,14 @@
         <v>46281.01597222222</v>
       </c>
       <c r="B111" s="4">
-        <v>541.1</v>
+        <v>462.78</v>
       </c>
       <c r="C111" s="4">
-        <v>509.18</v>
+        <v>499.65</v>
       </c>
       <c r="D111" s="4"/>
       <c r="E111" s="4">
-        <v>-31.92000000000002</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -9694,11 +9694,11 @@
         <v>527.53</v>
       </c>
       <c r="C112" s="4">
-        <v>509.46</v>
+        <v>499.39</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4">
-        <v>-18.06999999999999</v>
+        <v>-28.13999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -9709,11 +9709,11 @@
         <v>514.8</v>
       </c>
       <c r="C113" s="4">
-        <v>509.59</v>
+        <v>499.95</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4">
-        <v>-5.20999999999998</v>
+        <v>-14.84999999999997</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -9724,11 +9724,11 @@
         <v>497.86</v>
       </c>
       <c r="C114" s="4">
-        <v>509.51</v>
+        <v>499.97</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4">
-        <v>11.64999999999998</v>
+        <v>2.110000000000014</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -9739,11 +9739,11 @@
         <v>547.59</v>
       </c>
       <c r="C115" s="4">
-        <v>509.4</v>
+        <v>499.89</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4">
-        <v>-38.19000000000005</v>
+        <v>-47.70000000000005</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -9754,11 +9754,11 @@
         <v>512.98</v>
       </c>
       <c r="C116" s="4">
-        <v>509.5</v>
+        <v>500.12</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4">
-        <v>-3.480000000000018</v>
+        <v>-12.86000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -9769,11 +9769,11 @@
         <v>530.2</v>
       </c>
       <c r="C117" s="4">
-        <v>509.44</v>
+        <v>500.05</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4">
-        <v>-20.76000000000005</v>
+        <v>-30.15000000000003</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -9784,11 +9784,11 @@
         <v>516.12</v>
       </c>
       <c r="C118" s="4">
-        <v>509.44</v>
+        <v>500.37</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4">
-        <v>-6.680000000000007</v>
+        <v>-15.75</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -9799,11 +9799,11 @@
         <v>564.61</v>
       </c>
       <c r="C119" s="4">
-        <v>509.35</v>
+        <v>500.95</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4">
-        <v>-55.25999999999999</v>
+        <v>-63.66000000000003</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -9814,11 +9814,11 @@
         <v>509.26</v>
       </c>
       <c r="C120" s="4">
-        <v>509.26</v>
+        <v>501.19</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4">
-        <v>0</v>
+        <v>-8.069999999999993</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -9826,14 +9826,14 @@
         <v>46281.02638888889</v>
       </c>
       <c r="B121" s="4">
-        <v>537.26</v>
+        <v>531.9</v>
       </c>
       <c r="C121" s="4">
-        <v>509.23</v>
+        <v>501.37</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4">
-        <v>-28.02999999999997</v>
+        <v>-30.52999999999997</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -9844,11 +9844,11 @@
         <v>505.25</v>
       </c>
       <c r="C122" s="4">
-        <v>509.23</v>
+        <v>501.43</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4">
-        <v>3.980000000000018</v>
+        <v>-3.819999999999993</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -9859,11 +9859,11 @@
         <v>535.4400000000001</v>
       </c>
       <c r="C123" s="4">
-        <v>509.39</v>
+        <v>501.65</v>
       </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4">
-        <v>-26.05000000000007</v>
+        <v>-33.79000000000008</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -9874,11 +9874,11 @@
         <v>506.25</v>
       </c>
       <c r="C124" s="4">
-        <v>509.61</v>
+        <v>501.76</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4">
-        <v>3.360000000000014</v>
+        <v>-4.490000000000009</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -9886,14 +9886,14 @@
         <v>46281.03055555555</v>
       </c>
       <c r="B125" s="4">
-        <v>544.9</v>
+        <v>553.91</v>
       </c>
       <c r="C125" s="4">
-        <v>510.96</v>
+        <v>503.1</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4">
-        <v>-33.94</v>
+        <v>-50.80999999999995</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -9904,11 +9904,11 @@
         <v>514.9299999999999</v>
       </c>
       <c r="C126" s="4">
-        <v>511.25</v>
+        <v>503.39</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4">
-        <v>-3.67999999999995</v>
+        <v>-11.53999999999996</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -9916,14 +9916,14 @@
         <v>46281.03263888889</v>
       </c>
       <c r="B127" s="4">
-        <v>565.83</v>
+        <v>540.1</v>
       </c>
       <c r="C127" s="4">
-        <v>511.46</v>
+        <v>503.4</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4">
-        <v>-54.37000000000006</v>
+        <v>-36.70000000000005</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -9934,11 +9934,11 @@
         <v>510.87</v>
       </c>
       <c r="C128" s="4">
-        <v>511.78</v>
+        <v>503.8</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4">
-        <v>0.9099999999999682</v>
+        <v>-7.069999999999993</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -9949,11 +9949,11 @@
         <v>413.86</v>
       </c>
       <c r="C129" s="4">
-        <v>511.92</v>
+        <v>503.87</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4">
-        <v>98.06</v>
+        <v>90.00999999999999</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -9964,11 +9964,11 @@
         <v>513.9</v>
       </c>
       <c r="C130" s="4">
-        <v>512.26</v>
+        <v>504.22</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4">
-        <v>-1.639999999999986</v>
+        <v>-9.67999999999995</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -9979,11 +9979,11 @@
         <v>588.11</v>
       </c>
       <c r="C131" s="4">
-        <v>512.33</v>
+        <v>504.44</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4">
-        <v>-75.77999999999997</v>
+        <v>-83.67000000000002</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -9994,11 +9994,11 @@
         <v>516.48</v>
       </c>
       <c r="C132" s="4">
-        <v>512.59</v>
+        <v>504.85</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4">
-        <v>-3.889999999999986</v>
+        <v>-11.63</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -10009,11 +10009,11 @@
         <v>546.7</v>
       </c>
       <c r="C133" s="4">
-        <v>512.53</v>
+        <v>504.87</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4">
-        <v>-34.17000000000007</v>
+        <v>-41.83000000000004</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -10024,11 +10024,11 @@
         <v>523.23</v>
       </c>
       <c r="C134" s="4">
-        <v>513.37</v>
+        <v>505.68</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4">
-        <v>-9.860000000000014</v>
+        <v>-17.55000000000001</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -10039,11 +10039,11 @@
         <v>575.63</v>
       </c>
       <c r="C135" s="4">
-        <v>513.7</v>
+        <v>506.02</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4">
-        <v>-61.92999999999995</v>
+        <v>-69.61000000000001</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -10054,11 +10054,11 @@
         <v>516.15</v>
       </c>
       <c r="C136" s="4">
-        <v>514.33</v>
+        <v>506.49</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4">
-        <v>-1.819999999999936</v>
+        <v>-9.659999999999968</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -10066,14 +10066,14 @@
         <v>46281.04305555556</v>
       </c>
       <c r="B137" s="4">
-        <v>542</v>
+        <v>597.75</v>
       </c>
       <c r="C137" s="4">
-        <v>514.77</v>
+        <v>507.03</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4">
-        <v>-27.23000000000002</v>
+        <v>-90.72000000000003</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -10084,11 +10084,11 @@
         <v>515.5700000000001</v>
       </c>
       <c r="C138" s="4">
-        <v>515.23</v>
+        <v>507.45</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4">
-        <v>-0.3400000000000318</v>
+        <v>-8.120000000000061</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -10099,11 +10099,11 @@
         <v>426.33</v>
       </c>
       <c r="C139" s="4">
-        <v>516.58</v>
+        <v>508.33</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4">
-        <v>90.25000000000006</v>
+        <v>82</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -10114,11 +10114,11 @@
         <v>517.98</v>
       </c>
       <c r="C140" s="4">
-        <v>517.04</v>
+        <v>509.28</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4">
-        <v>-0.9400000000000546</v>
+        <v>-8.700000000000045</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -10126,14 +10126,14 @@
         <v>46281.04722222222</v>
       </c>
       <c r="B141" s="4">
-        <v>530.76</v>
+        <v>537.1</v>
       </c>
       <c r="C141" s="4">
-        <v>518.08</v>
+        <v>510.64</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4">
-        <v>-12.67999999999995</v>
+        <v>-26.46000000000004</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -10144,11 +10144,11 @@
         <v>503.42</v>
       </c>
       <c r="C142" s="4">
-        <v>518.83</v>
+        <v>511.06</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4">
-        <v>15.41000000000003</v>
+        <v>7.639999999999986</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -10156,14 +10156,14 @@
         <v>46281.04930555556</v>
       </c>
       <c r="B143" s="4">
-        <v>531.88</v>
+        <v>527.2</v>
       </c>
       <c r="C143" s="4">
-        <v>518.99</v>
+        <v>511.17</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4">
-        <v>-12.88999999999999</v>
+        <v>-16.03000000000003</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -10174,11 +10174,11 @@
         <v>512.0599999999999</v>
       </c>
       <c r="C144" s="4">
-        <v>519.28</v>
+        <v>511.58</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4">
-        <v>7.220000000000027</v>
+        <v>-0.4799999999999613</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -10186,14 +10186,14 @@
         <v>46281.05138888889</v>
       </c>
       <c r="B145" s="4">
-        <v>521</v>
+        <v>524.9400000000001</v>
       </c>
       <c r="C145" s="4">
-        <v>519.7</v>
+        <v>511.83</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4">
-        <v>-1.299999999999955</v>
+        <v>-13.11000000000007</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -10204,11 +10204,11 @@
         <v>499.4</v>
       </c>
       <c r="C146" s="4">
-        <v>519.92</v>
+        <v>512.16</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4">
-        <v>20.51999999999998</v>
+        <v>12.75999999999999</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -10216,14 +10216,14 @@
         <v>46281.05347222222</v>
       </c>
       <c r="B147" s="4">
-        <v>535.92</v>
+        <v>541.6</v>
       </c>
       <c r="C147" s="4">
-        <v>519.9400000000001</v>
+        <v>512.58</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4">
-        <v>-15.9799999999999</v>
+        <v>-29.01999999999998</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -10234,11 +10234,11 @@
         <v>523.3099999999999</v>
       </c>
       <c r="C148" s="4">
-        <v>520.04</v>
+        <v>512.73</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4">
-        <v>-3.269999999999982</v>
+        <v>-10.57999999999993</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -10246,14 +10246,14 @@
         <v>46281.05555555555</v>
       </c>
       <c r="B149" s="4">
-        <v>561.33</v>
+        <v>560.1</v>
       </c>
       <c r="C149" s="4">
-        <v>520.28</v>
+        <v>512.99</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4">
-        <v>-41.05000000000007</v>
+        <v>-47.11000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -10264,11 +10264,11 @@
         <v>522.45</v>
       </c>
       <c r="C150" s="4">
-        <v>520.3</v>
+        <v>513.1</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4">
-        <v>-2.150000000000091</v>
+        <v>-9.350000000000023</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -10279,11 +10279,11 @@
         <v>505.61</v>
       </c>
       <c r="C151" s="4">
-        <v>520.12</v>
+        <v>513.05</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4">
-        <v>14.50999999999999</v>
+        <v>7.439999999999941</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -10294,11 +10294,11 @@
         <v>514.42</v>
       </c>
       <c r="C152" s="4">
-        <v>520.22</v>
+        <v>512.96</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4">
-        <v>5.800000000000068</v>
+        <v>-1.459999999999923</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -10309,11 +10309,11 @@
         <v>544.4</v>
       </c>
       <c r="C153" s="4">
-        <v>520.3200000000001</v>
+        <v>513.2</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4">
-        <v>-24.07999999999993</v>
+        <v>-31.19999999999993</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -10324,11 +10324,11 @@
         <v>516.55</v>
       </c>
       <c r="C154" s="4">
-        <v>520.45</v>
+        <v>513.26</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4">
-        <v>3.900000000000091</v>
+        <v>-3.289999999999964</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -10336,14 +10336,14 @@
         <v>46281.06180555555</v>
       </c>
       <c r="B155" s="4">
-        <v>548.3</v>
+        <v>551.64</v>
       </c>
       <c r="C155" s="4">
-        <v>520.5599999999999</v>
+        <v>513.24</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4">
-        <v>-27.74000000000001</v>
+        <v>-38.39999999999998</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -10354,11 +10354,11 @@
         <v>533.8099999999999</v>
       </c>
       <c r="C156" s="4">
-        <v>521.3099999999999</v>
+        <v>513.38</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4">
-        <v>-12.5</v>
+        <v>-20.42999999999995</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -10366,14 +10366,14 @@
         <v>46281.06388888889</v>
       </c>
       <c r="B157" s="4">
-        <v>586.6799999999999</v>
+        <v>574.3</v>
       </c>
       <c r="C157" s="4">
-        <v>521.48</v>
+        <v>513.66</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4">
-        <v>-65.19999999999993</v>
+        <v>-60.63999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -10384,11 +10384,11 @@
         <v>522.8</v>
       </c>
       <c r="C158" s="4">
-        <v>521.71</v>
+        <v>514.34</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4">
-        <v>-1.089999999999918</v>
+        <v>-8.459999999999923</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -10399,11 +10399,11 @@
         <v>450.7</v>
       </c>
       <c r="C159" s="4">
-        <v>521.64</v>
+        <v>514.3200000000001</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4">
-        <v>70.94</v>
+        <v>63.62000000000006</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -10414,11 +10414,11 @@
         <v>544.12</v>
       </c>
       <c r="C160" s="4">
-        <v>521.52</v>
+        <v>514.05</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4">
-        <v>-22.60000000000002</v>
+        <v>-30.07000000000005</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -10429,11 +10429,11 @@
         <v>529.05</v>
       </c>
       <c r="C161" s="4">
-        <v>521.38</v>
+        <v>514.26</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4">
-        <v>-7.669999999999959</v>
+        <v>-14.78999999999996</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -10444,11 +10444,11 @@
         <v>503.75</v>
       </c>
       <c r="C162" s="4">
-        <v>521.05</v>
+        <v>514</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4">
-        <v>17.29999999999995</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -10459,11 +10459,11 @@
         <v>536.5</v>
       </c>
       <c r="C163" s="4">
-        <v>520.89</v>
+        <v>513.51</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4">
-        <v>-15.61000000000001</v>
+        <v>-22.99000000000001</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -10474,11 +10474,11 @@
         <v>489.59</v>
       </c>
       <c r="C164" s="4">
-        <v>520.72</v>
+        <v>513.14</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4">
-        <v>31.13000000000005</v>
+        <v>23.55000000000001</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -10489,11 +10489,11 @@
         <v>576.02</v>
       </c>
       <c r="C165" s="4">
-        <v>520.95</v>
+        <v>513.3200000000001</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4">
-        <v>-55.06999999999994</v>
+        <v>-62.69999999999993</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -10504,11 +10504,11 @@
         <v>502.99</v>
       </c>
       <c r="C166" s="4">
-        <v>520.8099999999999</v>
+        <v>513.04</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4">
-        <v>17.81999999999994</v>
+        <v>10.04999999999995</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -10519,11 +10519,11 @@
         <v>571.47</v>
       </c>
       <c r="C167" s="4">
-        <v>520.83</v>
+        <v>514.03</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4">
-        <v>-50.63999999999999</v>
+        <v>-57.44000000000005</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -10534,11 +10534,11 @@
         <v>517.41</v>
       </c>
       <c r="C168" s="4">
-        <v>520.49</v>
+        <v>512.98</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4">
-        <v>3.080000000000041</v>
+        <v>-4.42999999999995</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -10549,11 +10549,11 @@
         <v>557.34</v>
       </c>
       <c r="C169" s="4">
-        <v>520.48</v>
+        <v>513.74</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4">
-        <v>-36.86000000000001</v>
+        <v>-43.60000000000002</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -10564,11 +10564,11 @@
         <v>512.5700000000001</v>
       </c>
       <c r="C170" s="4">
-        <v>520.5</v>
+        <v>513.6799999999999</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4">
-        <v>7.92999999999995</v>
+        <v>1.1099999999999</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -10579,11 +10579,11 @@
         <v>526</v>
       </c>
       <c r="C171" s="4">
-        <v>520.59</v>
+        <v>513.64</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4">
-        <v>-5.409999999999968</v>
+        <v>-12.36000000000001</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -10594,11 +10594,11 @@
         <v>504.84</v>
       </c>
       <c r="C172" s="4">
-        <v>520.6</v>
+        <v>513.74</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4">
-        <v>15.76000000000005</v>
+        <v>8.900000000000034</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -10606,14 +10606,14 @@
         <v>46281.08055555556</v>
       </c>
       <c r="B173" s="4">
-        <v>532.8</v>
+        <v>532.84</v>
       </c>
       <c r="C173" s="4">
-        <v>520.51</v>
+        <v>513.8099999999999</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4">
-        <v>-12.28999999999996</v>
+        <v>-19.03000000000009</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -10624,11 +10624,11 @@
         <v>493.49</v>
       </c>
       <c r="C174" s="4">
-        <v>521.23</v>
+        <v>513.84</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4">
-        <v>27.74000000000001</v>
+        <v>20.35000000000002</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -10639,11 +10639,11 @@
         <v>561.98</v>
       </c>
       <c r="C175" s="4">
-        <v>522.04</v>
+        <v>514.5599999999999</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4">
-        <v>-39.94000000000005</v>
+        <v>-47.42000000000007</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -10654,11 +10654,11 @@
         <v>506.13</v>
       </c>
       <c r="C176" s="4">
-        <v>522.05</v>
+        <v>514.92</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4">
-        <v>15.91999999999996</v>
+        <v>8.789999999999964</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -10669,11 +10669,11 @@
         <v>571.39</v>
       </c>
       <c r="C177" s="4">
-        <v>522.47</v>
+        <v>515.5</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4">
-        <v>-48.91999999999996</v>
+        <v>-55.88999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -10684,11 +10684,11 @@
         <v>499.96</v>
       </c>
       <c r="C178" s="4">
-        <v>522.16</v>
+        <v>515.0700000000001</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4">
-        <v>22.19999999999999</v>
+        <v>15.11000000000007</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -10699,11 +10699,11 @@
         <v>516.4</v>
       </c>
       <c r="C179" s="4">
-        <v>522.1799999999999</v>
+        <v>515.46</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4">
-        <v>5.779999999999973</v>
+        <v>-0.9399999999999409</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -10714,11 +10714,11 @@
         <v>503.14</v>
       </c>
       <c r="C180" s="4">
-        <v>521.97</v>
+        <v>515.58</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4">
-        <v>18.83000000000004</v>
+        <v>12.44000000000005</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -10729,11 +10729,11 @@
         <v>527.2</v>
       </c>
       <c r="C181" s="4">
-        <v>522.5700000000001</v>
+        <v>515.61</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4">
-        <v>-4.629999999999995</v>
+        <v>-11.59000000000003</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -10744,11 +10744,11 @@
         <v>513.53</v>
       </c>
       <c r="C182" s="4">
-        <v>523.04</v>
+        <v>515.5700000000001</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4">
-        <v>9.509999999999991</v>
+        <v>2.040000000000077</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -10759,11 +10759,11 @@
         <v>530</v>
       </c>
       <c r="C183" s="4">
-        <v>523.17</v>
+        <v>515.54</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4">
-        <v>-6.830000000000041</v>
+        <v>-14.46000000000004</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -10774,11 +10774,11 @@
         <v>518.7</v>
       </c>
       <c r="C184" s="4">
-        <v>523.11</v>
+        <v>515.48</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4">
-        <v>4.409999999999968</v>
+        <v>-3.220000000000027</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -10789,11 +10789,11 @@
         <v>538.87</v>
       </c>
       <c r="C185" s="4">
-        <v>523.24</v>
+        <v>516</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4">
-        <v>-15.63</v>
+        <v>-22.87</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -10804,11 +10804,11 @@
         <v>514.38</v>
       </c>
       <c r="C186" s="4">
-        <v>523.1799999999999</v>
+        <v>516.4</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4">
-        <v>8.799999999999955</v>
+        <v>2.019999999999982</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -10819,11 +10819,11 @@
         <v>531</v>
       </c>
       <c r="C187" s="4">
-        <v>523.08</v>
+        <v>516.4</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4">
-        <v>-7.919999999999959</v>
+        <v>-14.60000000000002</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -10834,11 +10834,11 @@
         <v>517.61</v>
       </c>
       <c r="C188" s="4">
-        <v>523.28</v>
+        <v>516.38</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4">
-        <v>5.669999999999959</v>
+        <v>-1.230000000000018</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -10849,11 +10849,11 @@
         <v>531.89</v>
       </c>
       <c r="C189" s="4">
-        <v>523.58</v>
+        <v>516.36</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4">
-        <v>-8.309999999999945</v>
+        <v>-15.52999999999997</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -10864,11 +10864,11 @@
         <v>513.58</v>
       </c>
       <c r="C190" s="4">
-        <v>523.76</v>
+        <v>516.61</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4">
-        <v>10.17999999999995</v>
+        <v>3.029999999999973</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -10879,11 +10879,11 @@
         <v>524.77</v>
       </c>
       <c r="C191" s="4">
-        <v>523.87</v>
+        <v>516.8200000000001</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4">
-        <v>-0.8999999999999773</v>
+        <v>-7.949999999999932</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -10894,11 +10894,11 @@
         <v>517.35</v>
       </c>
       <c r="C192" s="4">
-        <v>523.99</v>
+        <v>516.8099999999999</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4">
-        <v>6.639999999999986</v>
+        <v>-0.5400000000000773</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -10909,11 +10909,11 @@
         <v>531.83</v>
       </c>
       <c r="C193" s="4">
-        <v>524.59</v>
+        <v>516.78</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4">
-        <v>-7.240000000000009</v>
+        <v>-15.05000000000007</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -10924,11 +10924,11 @@
         <v>515.33</v>
       </c>
       <c r="C194" s="4">
-        <v>524.65</v>
+        <v>516.84</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4">
-        <v>9.319999999999936</v>
+        <v>1.509999999999991</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -10939,11 +10939,11 @@
         <v>532</v>
       </c>
       <c r="C195" s="4">
-        <v>524.45</v>
+        <v>516.8</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="4">
-        <v>-7.549999999999955</v>
+        <v>-15.20000000000005</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -10954,11 +10954,11 @@
         <v>523.97</v>
       </c>
       <c r="C196" s="4">
-        <v>524.37</v>
+        <v>516.9299999999999</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="4">
-        <v>0.3999999999999773</v>
+        <v>-7.040000000000077</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -10969,11 +10969,11 @@
         <v>526.6</v>
       </c>
       <c r="C197" s="4">
-        <v>524.41</v>
+        <v>517.27</v>
       </c>
       <c r="D197" s="4"/>
       <c r="E197" s="4">
-        <v>-2.190000000000055</v>
+        <v>-9.330000000000041</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -10984,11 +10984,11 @@
         <v>525.3</v>
       </c>
       <c r="C198" s="4">
-        <v>524.51</v>
+        <v>517.28</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4">
-        <v>-0.7899999999999636</v>
+        <v>-8.019999999999982</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -10999,11 +10999,11 @@
         <v>521.47</v>
       </c>
       <c r="C199" s="4">
-        <v>524.5</v>
+        <v>517.25</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4">
-        <v>3.029999999999973</v>
+        <v>-4.220000000000027</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -11014,11 +11014,11 @@
         <v>528.49</v>
       </c>
       <c r="C200" s="4">
-        <v>524.5700000000001</v>
+        <v>517.46</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="4">
-        <v>-3.919999999999959</v>
+        <v>-11.02999999999997</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -11029,11 +11029,11 @@
         <v>558.8099999999999</v>
       </c>
       <c r="C201" s="4">
-        <v>524.63</v>
+        <v>517.62</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="4">
-        <v>-34.17999999999995</v>
+        <v>-41.18999999999994</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -11044,11 +11044,11 @@
         <v>532.33</v>
       </c>
       <c r="C202" s="4">
-        <v>524.79</v>
+        <v>517.61</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="4">
-        <v>-7.540000000000077</v>
+        <v>-14.72000000000003</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -11059,11 +11059,11 @@
         <v>542</v>
       </c>
       <c r="C203" s="4">
-        <v>524.92</v>
+        <v>517.6799999999999</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4">
-        <v>-17.08000000000004</v>
+        <v>-24.32000000000005</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -11074,11 +11074,11 @@
         <v>525.54</v>
       </c>
       <c r="C204" s="4">
-        <v>524.71</v>
+        <v>517.49</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="4">
-        <v>-0.8299999999999272</v>
+        <v>-8.049999999999955</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -11089,11 +11089,11 @@
         <v>549</v>
       </c>
       <c r="C205" s="4">
-        <v>524.65</v>
+        <v>517.4299999999999</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="4">
-        <v>-24.35000000000002</v>
+        <v>-31.57000000000005</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -11104,11 +11104,11 @@
         <v>538.3200000000001</v>
       </c>
       <c r="C206" s="4">
-        <v>524.5700000000001</v>
+        <v>517.58</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="4">
-        <v>-13.75</v>
+        <v>-20.74000000000001</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -11116,14 +11116,14 @@
         <v>46281.11597222222</v>
       </c>
       <c r="B207" s="4">
-        <v>539.87</v>
+        <v>541</v>
       </c>
       <c r="C207" s="4">
-        <v>524.55</v>
+        <v>517.65</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="4">
-        <v>-15.32000000000005</v>
+        <v>-23.35000000000002</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -11134,11 +11134,11 @@
         <v>542.37</v>
       </c>
       <c r="C208" s="4">
-        <v>524.58</v>
+        <v>517.61</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="4">
-        <v>-17.78999999999996</v>
+        <v>-24.75999999999999</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -11149,11 +11149,11 @@
         <v>559.1900000000001</v>
       </c>
       <c r="C209" s="4">
-        <v>524.71</v>
+        <v>517.65</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="4">
-        <v>-34.48000000000002</v>
+        <v>-41.54000000000008</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -11164,11 +11164,11 @@
         <v>523.99</v>
       </c>
       <c r="C210" s="4">
-        <v>524.7</v>
+        <v>517.66</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="4">
-        <v>0.7100000000000364</v>
+        <v>-6.330000000000041</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -11176,14 +11176,14 @@
         <v>46281.12013888889</v>
       </c>
       <c r="B211" s="4">
-        <v>546.98</v>
+        <v>533.8</v>
       </c>
       <c r="C211" s="4">
-        <v>524.64</v>
+        <v>517.73</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="4">
-        <v>-22.34000000000003</v>
+        <v>-16.06999999999994</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -11194,11 +11194,11 @@
         <v>514.42</v>
       </c>
       <c r="C212" s="4">
-        <v>524.63</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="4">
-        <v>10.21000000000004</v>
+        <v>3.400000000000091</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -11209,11 +11209,11 @@
         <v>591.95</v>
       </c>
       <c r="C213" s="4">
-        <v>524.79</v>
+        <v>517.78</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="4">
-        <v>-67.16000000000008</v>
+        <v>-74.17000000000007</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -11224,11 +11224,11 @@
         <v>562.9</v>
       </c>
       <c r="C214" s="4">
-        <v>524.6799999999999</v>
+        <v>517.7</v>
       </c>
       <c r="D214" s="4"/>
       <c r="E214" s="4">
-        <v>-38.22000000000003</v>
+        <v>-45.19999999999993</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -11236,14 +11236,14 @@
         <v>46281.12430555555</v>
       </c>
       <c r="B215" s="4">
-        <v>532.9</v>
+        <v>512.0599999999999</v>
       </c>
       <c r="C215" s="4">
-        <v>524.76</v>
+        <v>517.6</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="4">
-        <v>-8.139999999999986</v>
+        <v>5.540000000000077</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -11254,11 +11254,11 @@
         <v>529.97</v>
       </c>
       <c r="C216" s="4">
-        <v>525.03</v>
+        <v>517.54</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="4">
-        <v>-4.940000000000055</v>
+        <v>-12.43000000000006</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -11266,14 +11266,14 @@
         <v>46281.12638888889</v>
       </c>
       <c r="B217" s="4">
-        <v>535.1</v>
+        <v>546.34</v>
       </c>
       <c r="C217" s="4">
-        <v>525.1</v>
+        <v>517.66</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="4">
-        <v>-10</v>
+        <v>-28.68000000000006</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -11284,11 +11284,11 @@
         <v>516.96</v>
       </c>
       <c r="C218" s="4">
-        <v>525.13</v>
+        <v>517.6799999999999</v>
       </c>
       <c r="D218" s="4"/>
       <c r="E218" s="4">
-        <v>8.169999999999959</v>
+        <v>0.7199999999999136</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -11296,14 +11296,14 @@
         <v>46281.12847222222</v>
       </c>
       <c r="B219" s="4">
-        <v>532.7</v>
+        <v>527</v>
       </c>
       <c r="C219" s="4">
-        <v>524.73</v>
+        <v>517.5700000000001</v>
       </c>
       <c r="D219" s="4"/>
       <c r="E219" s="4">
-        <v>-7.970000000000027</v>
+        <v>-9.42999999999995</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -11314,11 +11314,11 @@
         <v>515.4</v>
       </c>
       <c r="C220" s="4">
-        <v>524.76</v>
+        <v>517.42</v>
       </c>
       <c r="D220" s="4"/>
       <c r="E220" s="4">
-        <v>9.360000000000014</v>
+        <v>2.019999999999982</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -11326,14 +11326,14 @@
         <v>46281.13055555556</v>
       </c>
       <c r="B221" s="4">
-        <v>541.1</v>
+        <v>512.42</v>
       </c>
       <c r="C221" s="4">
-        <v>525</v>
+        <v>517.66</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="4">
-        <v>-16.10000000000002</v>
+        <v>5.240000000000009</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -11344,11 +11344,11 @@
         <v>517.58</v>
       </c>
       <c r="C222" s="4">
-        <v>525.09</v>
+        <v>517.92</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="4">
-        <v>7.509999999999991</v>
+        <v>0.3399999999999181</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -11359,11 +11359,11 @@
         <v>549.17</v>
       </c>
       <c r="C223" s="4">
-        <v>525.45</v>
+        <v>518.02</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="4">
-        <v>-23.71999999999991</v>
+        <v>-31.14999999999998</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -11374,11 +11374,11 @@
         <v>537.89</v>
       </c>
       <c r="C224" s="4">
-        <v>525.79</v>
+        <v>518.11</v>
       </c>
       <c r="D224" s="4"/>
       <c r="E224" s="4">
-        <v>-12.10000000000002</v>
+        <v>-19.77999999999997</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -11389,11 +11389,11 @@
         <v>550.01</v>
       </c>
       <c r="C225" s="4">
-        <v>525.91</v>
+        <v>518.03</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="4">
-        <v>-24.10000000000002</v>
+        <v>-31.98000000000002</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -11404,11 +11404,11 @@
         <v>530.12</v>
       </c>
       <c r="C226" s="4">
-        <v>525.98</v>
+        <v>518.22</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="4">
-        <v>-4.139999999999986</v>
+        <v>-11.89999999999998</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -11416,14 +11416,14 @@
         <v>46281.13680555556</v>
       </c>
       <c r="B227" s="4">
-        <v>536.5</v>
+        <v>544.41</v>
       </c>
       <c r="C227" s="4">
-        <v>525.97</v>
+        <v>518.83</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="4">
-        <v>-10.52999999999997</v>
+        <v>-25.57999999999993</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -11434,11 +11434,11 @@
         <v>531.71</v>
       </c>
       <c r="C228" s="4">
-        <v>526.17</v>
+        <v>519.16</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="4">
-        <v>-5.540000000000077</v>
+        <v>-12.55000000000007</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -11449,11 +11449,11 @@
         <v>546.25</v>
       </c>
       <c r="C229" s="4">
-        <v>526.09</v>
+        <v>519.08</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4">
-        <v>-20.15999999999997</v>
+        <v>-27.16999999999996</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -11464,11 +11464,11 @@
         <v>518.26</v>
       </c>
       <c r="C230" s="4">
-        <v>526.4400000000001</v>
+        <v>519.33</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="4">
-        <v>8.180000000000064</v>
+        <v>1.07000000000005</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -11479,11 +11479,11 @@
         <v>532.59</v>
       </c>
       <c r="C231" s="4">
-        <v>526.61</v>
+        <v>519.8</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="4">
-        <v>-5.980000000000018</v>
+        <v>-12.79000000000008</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -11494,11 +11494,11 @@
         <v>456.06</v>
       </c>
       <c r="C232" s="4">
-        <v>526.8</v>
+        <v>520.0700000000001</v>
       </c>
       <c r="D232" s="4"/>
       <c r="E232" s="4">
-        <v>70.73999999999995</v>
+        <v>64.01000000000005</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -11509,11 +11509,11 @@
         <v>556.9299999999999</v>
       </c>
       <c r="C233" s="4">
-        <v>526.95</v>
+        <v>520.14</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4">
-        <v>-29.9799999999999</v>
+        <v>-36.78999999999996</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -11524,11 +11524,11 @@
         <v>498.33</v>
       </c>
       <c r="C234" s="4">
-        <v>527.04</v>
+        <v>520.04</v>
       </c>
       <c r="D234" s="4"/>
       <c r="E234" s="4">
-        <v>28.70999999999998</v>
+        <v>21.70999999999998</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -11536,14 +11536,14 @@
         <v>46281.14513888889</v>
       </c>
       <c r="B235" s="4">
-        <v>527.15</v>
+        <v>518.6</v>
       </c>
       <c r="C235" s="4">
-        <v>527.39</v>
+        <v>520.12</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="4">
-        <v>0.2400000000000091</v>
+        <v>1.519999999999982</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -11554,11 +11554,11 @@
         <v>528.72</v>
       </c>
       <c r="C236" s="4">
-        <v>527.5</v>
+        <v>520.1</v>
       </c>
       <c r="D236" s="4"/>
       <c r="E236" s="4">
-        <v>-1.220000000000027</v>
+        <v>-8.620000000000005</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -11569,11 +11569,11 @@
         <v>552.3099999999999</v>
       </c>
       <c r="C237" s="4">
-        <v>527.33</v>
+        <v>519.99</v>
       </c>
       <c r="D237" s="4"/>
       <c r="E237" s="4">
-        <v>-24.9799999999999</v>
+        <v>-32.31999999999994</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -11584,11 +11584,11 @@
         <v>538.16</v>
       </c>
       <c r="C238" s="4">
-        <v>527.83</v>
+        <v>520.02</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="4">
-        <v>-10.32999999999993</v>
+        <v>-18.13999999999999</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -11596,14 +11596,14 @@
         <v>46281.14930555555</v>
       </c>
       <c r="B239" s="4">
-        <v>537.9</v>
+        <v>529.7</v>
       </c>
       <c r="C239" s="4">
-        <v>527.86</v>
+        <v>520.16</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4">
-        <v>-10.03999999999996</v>
+        <v>-9.540000000000077</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -11614,11 +11614,11 @@
         <v>508.52</v>
       </c>
       <c r="C240" s="4">
-        <v>527.84</v>
+        <v>520.45</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="4">
-        <v>19.32000000000005</v>
+        <v>11.93000000000006</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -11629,11 +11629,11 @@
         <v>556.67</v>
       </c>
       <c r="C241" s="4">
-        <v>528.29</v>
+        <v>520.4</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="4">
-        <v>-28.38</v>
+        <v>-36.26999999999998</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -11644,11 +11644,11 @@
         <v>507.61</v>
       </c>
       <c r="C242" s="4">
-        <v>528.3</v>
+        <v>520.42</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4">
-        <v>20.68999999999994</v>
+        <v>12.80999999999995</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -11659,11 +11659,11 @@
         <v>549.14</v>
       </c>
       <c r="C243" s="4">
-        <v>528.21</v>
+        <v>520.27</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="4">
-        <v>-20.92999999999995</v>
+        <v>-28.87</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -11674,11 +11674,11 @@
         <v>497.85</v>
       </c>
       <c r="C244" s="4">
-        <v>527.84</v>
+        <v>520.17</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="4">
-        <v>29.99000000000001</v>
+        <v>22.31999999999994</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -11689,11 +11689,11 @@
         <v>524.92</v>
       </c>
       <c r="C245" s="4">
-        <v>527.99</v>
+        <v>520.13</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="4">
-        <v>3.07000000000005</v>
+        <v>-4.789999999999964</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -11704,11 +11704,11 @@
         <v>566.86</v>
       </c>
       <c r="C246" s="4">
-        <v>527.8200000000001</v>
+        <v>519.97</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="4">
-        <v>-39.03999999999996</v>
+        <v>-46.88999999999999</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -11719,11 +11719,11 @@
         <v>535.24</v>
       </c>
       <c r="C247" s="4">
-        <v>527.99</v>
+        <v>520</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4">
-        <v>-7.25</v>
+        <v>-15.24000000000001</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -11734,11 +11734,11 @@
         <v>556.84</v>
       </c>
       <c r="C248" s="4">
-        <v>527.96</v>
+        <v>519.9299999999999</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="4">
-        <v>-28.88</v>
+        <v>-36.91000000000008</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -11749,11 +11749,11 @@
         <v>546.33</v>
       </c>
       <c r="C249" s="4">
-        <v>527.8099999999999</v>
+        <v>519.84</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="4">
-        <v>-18.5200000000001</v>
+        <v>-26.49000000000001</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -11764,11 +11764,11 @@
         <v>517.22</v>
       </c>
       <c r="C250" s="4">
-        <v>527.74</v>
+        <v>519.84</v>
       </c>
       <c r="D250" s="4"/>
       <c r="E250" s="4">
-        <v>10.51999999999998</v>
+        <v>2.620000000000005</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -11779,11 +11779,11 @@
         <v>554.03</v>
       </c>
       <c r="C251" s="4">
-        <v>527.58</v>
+        <v>519.9299999999999</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="4">
-        <v>-26.44999999999993</v>
+        <v>-34.10000000000002</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -11794,11 +11794,11 @@
         <v>531.62</v>
       </c>
       <c r="C252" s="4">
-        <v>527.66</v>
+        <v>519.64</v>
       </c>
       <c r="D252" s="4"/>
       <c r="E252" s="4">
-        <v>-3.960000000000036</v>
+        <v>-11.98000000000002</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -11806,14 +11806,14 @@
         <v>46281.16388888889</v>
       </c>
       <c r="B253" s="4">
-        <v>534.7</v>
+        <v>524.8</v>
       </c>
       <c r="C253" s="4">
-        <v>527.4299999999999</v>
+        <v>519.09</v>
       </c>
       <c r="D253" s="4"/>
       <c r="E253" s="4">
-        <v>-7.270000000000095</v>
+        <v>-5.709999999999923</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -11824,11 +11824,11 @@
         <v>541.21</v>
       </c>
       <c r="C254" s="4">
-        <v>527.23</v>
+        <v>519.05</v>
       </c>
       <c r="D254" s="4"/>
       <c r="E254" s="4">
-        <v>-13.98000000000002</v>
+        <v>-22.16000000000008</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -11839,11 +11839,11 @@
         <v>535.5</v>
       </c>
       <c r="C255" s="4">
-        <v>527.17</v>
+        <v>518.97</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="4">
-        <v>-8.330000000000041</v>
+        <v>-16.52999999999997</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -11854,11 +11854,11 @@
         <v>532.5700000000001</v>
       </c>
       <c r="C256" s="4">
-        <v>526.4299999999999</v>
+        <v>518.39</v>
       </c>
       <c r="D256" s="4"/>
       <c r="E256" s="4">
-        <v>-6.1400000000001</v>
+        <v>-14.18000000000006</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -11866,14 +11866,14 @@
         <v>46281.16805555556</v>
       </c>
       <c r="B257" s="4">
-        <v>552.7</v>
+        <v>535.4</v>
       </c>
       <c r="C257" s="4">
-        <v>526.17</v>
+        <v>518.34</v>
       </c>
       <c r="D257" s="4"/>
       <c r="E257" s="4">
-        <v>-26.53000000000009</v>
+        <v>-17.05999999999995</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -11884,11 +11884,11 @@
         <v>513.4400000000001</v>
       </c>
       <c r="C258" s="4">
-        <v>526.12</v>
+        <v>518.0599999999999</v>
       </c>
       <c r="D258" s="4"/>
       <c r="E258" s="4">
-        <v>12.67999999999995</v>
+        <v>4.619999999999891</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -11896,14 +11896,14 @@
         <v>46281.17013888889</v>
       </c>
       <c r="B259" s="4">
-        <v>539.7</v>
+        <v>571.3099999999999</v>
       </c>
       <c r="C259" s="4">
-        <v>525.91</v>
+        <v>517.8</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="4">
-        <v>-13.79000000000008</v>
+        <v>-53.50999999999999</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -11914,11 +11914,11 @@
         <v>538.66</v>
       </c>
       <c r="C260" s="4">
-        <v>525.28</v>
+        <v>517.5</v>
       </c>
       <c r="D260" s="4"/>
       <c r="E260" s="4">
-        <v>-13.38</v>
+        <v>-21.15999999999997</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -11929,11 +11929,11 @@
         <v>556.38</v>
       </c>
       <c r="C261" s="4">
-        <v>525.25</v>
+        <v>517.35</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="4">
-        <v>-31.13</v>
+        <v>-39.02999999999997</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -11944,11 +11944,11 @@
         <v>547.64</v>
       </c>
       <c r="C262" s="4">
-        <v>524.41</v>
+        <v>516.5</v>
       </c>
       <c r="D262" s="4"/>
       <c r="E262" s="4">
-        <v>-23.23000000000002</v>
+        <v>-31.13999999999999</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -11959,11 +11959,11 @@
         <v>552.36</v>
       </c>
       <c r="C263" s="4">
-        <v>524.27</v>
+        <v>516.36</v>
       </c>
       <c r="D263" s="4"/>
       <c r="E263" s="4">
-        <v>-28.09000000000003</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -11974,11 +11974,11 @@
         <v>546.29</v>
       </c>
       <c r="C264" s="4">
-        <v>524.35</v>
+        <v>516.1900000000001</v>
       </c>
       <c r="D264" s="4"/>
       <c r="E264" s="4">
-        <v>-21.93999999999994</v>
+        <v>-30.09999999999991</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -11989,11 +11989,11 @@
         <v>576.9</v>
       </c>
       <c r="C265" s="4">
-        <v>524.5</v>
+        <v>516.33</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4">
-        <v>-52.39999999999998</v>
+        <v>-60.56999999999994</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -12004,11 +12004,11 @@
         <v>541.8099999999999</v>
       </c>
       <c r="C266" s="4">
-        <v>524.33</v>
+        <v>516.34</v>
       </c>
       <c r="D266" s="4"/>
       <c r="E266" s="4">
-        <v>-17.4799999999999</v>
+        <v>-25.46999999999991</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -12019,11 +12019,11 @@
         <v>536.2</v>
       </c>
       <c r="C267" s="4">
-        <v>524.21</v>
+        <v>516.3099999999999</v>
       </c>
       <c r="D267" s="4"/>
       <c r="E267" s="4">
-        <v>-11.99000000000001</v>
+        <v>-19.8900000000001</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -12034,11 +12034,11 @@
         <v>539.7</v>
       </c>
       <c r="C268" s="4">
-        <v>524.1900000000001</v>
+        <v>516.25</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4">
-        <v>-15.50999999999999</v>
+        <v>-23.45000000000005</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -12049,11 +12049,11 @@
         <v>567.21</v>
       </c>
       <c r="C269" s="4">
-        <v>524.1900000000001</v>
+        <v>516.29</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="4">
-        <v>-43.01999999999998</v>
+        <v>-50.92000000000007</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -12064,11 +12064,11 @@
         <v>543.11</v>
       </c>
       <c r="C270" s="4">
-        <v>524.26</v>
+        <v>516.26</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4">
-        <v>-18.85000000000002</v>
+        <v>-26.85000000000002</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -12079,11 +12079,11 @@
         <v>558.3</v>
       </c>
       <c r="C271" s="4">
-        <v>524.21</v>
+        <v>516.3099999999999</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4">
-        <v>-34.08999999999992</v>
+        <v>-41.99000000000001</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -12094,11 +12094,11 @@
         <v>538.99</v>
       </c>
       <c r="C272" s="4">
-        <v>524.36</v>
+        <v>516.37</v>
       </c>
       <c r="D272" s="4"/>
       <c r="E272" s="4">
-        <v>-14.63</v>
+        <v>-22.62</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -12109,11 +12109,11 @@
         <v>539.87</v>
       </c>
       <c r="C273" s="4">
-        <v>524.91</v>
+        <v>516.84</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4">
-        <v>-14.96000000000004</v>
+        <v>-23.02999999999997</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -12124,11 +12124,11 @@
         <v>534.42</v>
       </c>
       <c r="C274" s="4">
-        <v>525.0700000000001</v>
+        <v>517.09</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4">
-        <v>-9.349999999999909</v>
+        <v>-17.32999999999993</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -12139,11 +12139,11 @@
         <v>533.8</v>
       </c>
       <c r="C275" s="4">
-        <v>524.96</v>
+        <v>517.04</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4">
-        <v>-8.839999999999918</v>
+        <v>-16.75999999999999</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -12154,11 +12154,11 @@
         <v>538.63</v>
       </c>
       <c r="C276" s="4">
-        <v>525.5700000000001</v>
+        <v>517.1799999999999</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4">
-        <v>-13.05999999999995</v>
+        <v>-21.45000000000005</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -12169,11 +12169,11 @@
         <v>552.87</v>
       </c>
       <c r="C277" s="4">
-        <v>525.36</v>
+        <v>517.3200000000001</v>
       </c>
       <c r="D277" s="4"/>
       <c r="E277" s="4">
-        <v>-27.50999999999999</v>
+        <v>-35.54999999999995</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -12184,11 +12184,11 @@
         <v>551.6900000000001</v>
       </c>
       <c r="C278" s="4">
-        <v>525.73</v>
+        <v>517.76</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4">
-        <v>-25.96000000000004</v>
+        <v>-33.93000000000006</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -12196,14 +12196,14 @@
         <v>46281.19097222222</v>
       </c>
       <c r="B279" s="4">
-        <v>537.3</v>
+        <v>571.3</v>
       </c>
       <c r="C279" s="4">
-        <v>525.99</v>
+        <v>518.3200000000001</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4">
-        <v>-11.30999999999995</v>
+        <v>-52.9799999999999</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -12214,11 +12214,11 @@
         <v>536.55</v>
       </c>
       <c r="C280" s="4">
-        <v>526.23</v>
+        <v>518.5700000000001</v>
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="4">
-        <v>-10.31999999999994</v>
+        <v>-17.9799999999999</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -12229,11 +12229,11 @@
         <v>538.2</v>
       </c>
       <c r="C281" s="4">
-        <v>526.5599999999999</v>
+        <v>518.98</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="4">
-        <v>-11.6400000000001</v>
+        <v>-19.22000000000003</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -12244,11 +12244,11 @@
         <v>534.8200000000001</v>
       </c>
       <c r="C282" s="4">
-        <v>526.61</v>
+        <v>519.3099999999999</v>
       </c>
       <c r="D282" s="4"/>
       <c r="E282" s="4">
-        <v>-8.210000000000036</v>
+        <v>-15.5100000000001</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -12259,11 +12259,11 @@
         <v>524.7</v>
       </c>
       <c r="C283" s="4">
-        <v>527.22</v>
+        <v>520.0700000000001</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4">
-        <v>2.519999999999982</v>
+        <v>-4.629999999999995</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -12274,11 +12274,11 @@
         <v>535.4</v>
       </c>
       <c r="C284" s="4">
-        <v>527.63</v>
+        <v>520.45</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4">
-        <v>-7.769999999999982</v>
+        <v>-14.94999999999993</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -12289,11 +12289,11 @@
         <v>551.04</v>
       </c>
       <c r="C285" s="4">
-        <v>527.85</v>
+        <v>520.63</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4">
-        <v>-23.18999999999994</v>
+        <v>-30.40999999999997</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -12304,11 +12304,11 @@
         <v>518.62</v>
       </c>
       <c r="C286" s="4">
-        <v>528.17</v>
+        <v>520.96</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4">
-        <v>9.549999999999955</v>
+        <v>2.340000000000032</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -12316,14 +12316,14 @@
         <v>46281.19930555556</v>
       </c>
       <c r="B287" s="4">
-        <v>545.2</v>
+        <v>532.6</v>
       </c>
       <c r="C287" s="4">
-        <v>528.39</v>
+        <v>521.1900000000001</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4">
-        <v>-16.81000000000006</v>
+        <v>-11.40999999999997</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -12334,11 +12334,11 @@
         <v>518.48</v>
       </c>
       <c r="C288" s="4">
-        <v>528.72</v>
+        <v>521.3099999999999</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4">
-        <v>10.24000000000001</v>
+        <v>2.829999999999927</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -12349,11 +12349,11 @@
         <v>528.7</v>
       </c>
       <c r="C289" s="4">
-        <v>528.8</v>
+        <v>521.37</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4">
-        <v>0.09999999999990905</v>
+        <v>-7.330000000000041</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -12364,11 +12364,11 @@
         <v>516.67</v>
       </c>
       <c r="C290" s="4">
-        <v>528.67</v>
+        <v>521.24</v>
       </c>
       <c r="D290" s="4"/>
       <c r="E290" s="4">
-        <v>12</v>
+        <v>4.57000000000005</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -12379,11 +12379,11 @@
         <v>534.8</v>
       </c>
       <c r="C291" s="4">
-        <v>528.91</v>
+        <v>521.3</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4">
-        <v>-5.889999999999986</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -12394,11 +12394,11 @@
         <v>520.3099999999999</v>
       </c>
       <c r="C292" s="4">
-        <v>528.8099999999999</v>
+        <v>521.28</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4">
-        <v>8.5</v>
+        <v>0.9700000000000273</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -12406,14 +12406,14 @@
         <v>46281.20555555556</v>
       </c>
       <c r="B293" s="4">
-        <v>551.2</v>
+        <v>535.9</v>
       </c>
       <c r="C293" s="4">
-        <v>528.74</v>
+        <v>521.23</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4">
-        <v>-22.46000000000004</v>
+        <v>-14.66999999999996</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -12424,11 +12424,11 @@
         <v>525.29</v>
       </c>
       <c r="C294" s="4">
-        <v>529</v>
+        <v>521.33</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4">
-        <v>3.710000000000036</v>
+        <v>-3.959999999999923</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -12439,11 +12439,11 @@
         <v>542.9</v>
       </c>
       <c r="C295" s="4">
-        <v>529.29</v>
+        <v>521.34</v>
       </c>
       <c r="D295" s="4"/>
       <c r="E295" s="4">
-        <v>-13.61000000000001</v>
+        <v>-21.55999999999995</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -12454,11 +12454,11 @@
         <v>529.2</v>
       </c>
       <c r="C296" s="4">
-        <v>529.4299999999999</v>
+        <v>521.4299999999999</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4">
-        <v>0.2299999999999045</v>
+        <v>-7.770000000000095</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -12466,14 +12466,14 @@
         <v>46281.20972222222</v>
       </c>
       <c r="B297" s="4">
-        <v>539.76</v>
+        <v>537.3</v>
       </c>
       <c r="C297" s="4">
-        <v>529.46</v>
+        <v>521.38</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4">
-        <v>-10.29999999999995</v>
+        <v>-15.91999999999996</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -12484,11 +12484,11 @@
         <v>531.9</v>
       </c>
       <c r="C298" s="4">
-        <v>529.66</v>
+        <v>521.45</v>
       </c>
       <c r="D298" s="4"/>
       <c r="E298" s="4">
-        <v>-2.240000000000009</v>
+        <v>-10.44999999999993</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -12496,14 +12496,14 @@
         <v>46281.21180555555</v>
       </c>
       <c r="B299" s="4">
-        <v>560.54</v>
+        <v>543.7</v>
       </c>
       <c r="C299" s="4">
-        <v>529.74</v>
+        <v>521.62</v>
       </c>
       <c r="D299" s="4"/>
       <c r="E299" s="4">
-        <v>-30.79999999999995</v>
+        <v>-22.08000000000004</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -12514,11 +12514,11 @@
         <v>537.52</v>
       </c>
       <c r="C300" s="4">
-        <v>530.09</v>
+        <v>521.95</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="4">
-        <v>-7.42999999999995</v>
+        <v>-15.56999999999994</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -12529,11 +12529,11 @@
         <v>534.42</v>
       </c>
       <c r="C301" s="4">
-        <v>530.1799999999999</v>
+        <v>522.12</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4">
-        <v>-4.240000000000009</v>
+        <v>-12.29999999999995</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -12544,11 +12544,11 @@
         <v>522.01</v>
       </c>
       <c r="C302" s="4">
-        <v>530.3099999999999</v>
+        <v>522.16</v>
       </c>
       <c r="D302" s="4"/>
       <c r="E302" s="4">
-        <v>8.299999999999955</v>
+        <v>0.1499999999999773</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -12556,14 +12556,14 @@
         <v>46281.21597222222</v>
       </c>
       <c r="B303" s="4">
-        <v>544.67</v>
+        <v>537.4</v>
       </c>
       <c r="C303" s="4">
-        <v>530.58</v>
+        <v>522.3099999999999</v>
       </c>
       <c r="D303" s="4"/>
       <c r="E303" s="4">
-        <v>-14.08999999999992</v>
+        <v>-15.09000000000003</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -12574,11 +12574,11 @@
         <v>533.71</v>
       </c>
       <c r="C304" s="4">
-        <v>530.84</v>
+        <v>522.5599999999999</v>
       </c>
       <c r="D304" s="4"/>
       <c r="E304" s="4">
-        <v>-2.870000000000005</v>
+        <v>-11.15000000000009</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -12589,11 +12589,11 @@
         <v>557.99</v>
       </c>
       <c r="C305" s="4">
-        <v>531.22</v>
+        <v>522.86</v>
       </c>
       <c r="D305" s="4"/>
       <c r="E305" s="4">
-        <v>-26.76999999999998</v>
+        <v>-35.13</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -12604,11 +12604,11 @@
         <v>525.01</v>
       </c>
       <c r="C306" s="4">
-        <v>531.58</v>
+        <v>522.9400000000001</v>
       </c>
       <c r="D306" s="4"/>
       <c r="E306" s="4">
-        <v>6.57000000000005</v>
+        <v>-2.069999999999936</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -12619,11 +12619,11 @@
         <v>527.7</v>
       </c>
       <c r="C307" s="4">
-        <v>532.11</v>
+        <v>523.4299999999999</v>
       </c>
       <c r="D307" s="4"/>
       <c r="E307" s="4">
-        <v>4.409999999999968</v>
+        <v>-4.270000000000095</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -12634,11 +12634,11 @@
         <v>507.58</v>
       </c>
       <c r="C308" s="4">
-        <v>532.28</v>
+        <v>523.5700000000001</v>
       </c>
       <c r="D308" s="4"/>
       <c r="E308" s="4">
-        <v>24.69999999999999</v>
+        <v>15.99000000000007</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -12649,11 +12649,11 @@
         <v>543.16</v>
       </c>
       <c r="C309" s="4">
-        <v>532.35</v>
+        <v>524.05</v>
       </c>
       <c r="D309" s="4"/>
       <c r="E309" s="4">
-        <v>-10.80999999999995</v>
+        <v>-19.11000000000001</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -12664,11 +12664,11 @@
         <v>510.43</v>
       </c>
       <c r="C310" s="4">
-        <v>532.34</v>
+        <v>524.05</v>
       </c>
       <c r="D310" s="4"/>
       <c r="E310" s="4">
-        <v>21.91000000000003</v>
+        <v>13.61999999999995</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -12676,14 +12676,14 @@
         <v>46281.22430555556</v>
       </c>
       <c r="B311" s="4">
-        <v>545.23</v>
+        <v>533.1</v>
       </c>
       <c r="C311" s="4">
-        <v>532.53</v>
+        <v>524.3099999999999</v>
       </c>
       <c r="D311" s="4"/>
       <c r="E311" s="4">
-        <v>-12.70000000000005</v>
+        <v>-8.790000000000077</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -12694,11 +12694,11 @@
         <v>526.58</v>
       </c>
       <c r="C312" s="4">
-        <v>532.66</v>
+        <v>524.3200000000001</v>
       </c>
       <c r="D312" s="4"/>
       <c r="E312" s="4">
-        <v>6.079999999999927</v>
+        <v>-2.259999999999991</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -12709,11 +12709,11 @@
         <v>558.72</v>
       </c>
       <c r="C313" s="4">
-        <v>533.3</v>
+        <v>524.41</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4">
-        <v>-25.42000000000007</v>
+        <v>-34.31000000000006</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -12724,11 +12724,11 @@
         <v>532.53</v>
       </c>
       <c r="C314" s="4">
-        <v>533.61</v>
+        <v>524.5700000000001</v>
       </c>
       <c r="D314" s="4"/>
       <c r="E314" s="4">
-        <v>1.080000000000041</v>
+        <v>-7.959999999999923</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -12739,11 +12739,11 @@
         <v>539</v>
       </c>
       <c r="C315" s="4">
-        <v>533.79</v>
+        <v>524.9299999999999</v>
       </c>
       <c r="D315" s="4"/>
       <c r="E315" s="4">
-        <v>-5.210000000000036</v>
+        <v>-14.07000000000005</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -12754,11 +12754,11 @@
         <v>537.76</v>
       </c>
       <c r="C316" s="4">
-        <v>533.88</v>
+        <v>525.38</v>
       </c>
       <c r="D316" s="4"/>
       <c r="E316" s="4">
-        <v>-3.879999999999995</v>
+        <v>-12.38</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -12769,11 +12769,11 @@
         <v>563.48</v>
       </c>
       <c r="C317" s="4">
-        <v>534.14</v>
+        <v>525.75</v>
       </c>
       <c r="D317" s="4"/>
       <c r="E317" s="4">
-        <v>-29.34000000000003</v>
+        <v>-37.73000000000002</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -12784,11 +12784,11 @@
         <v>537.8099999999999</v>
       </c>
       <c r="C318" s="4">
-        <v>534.34</v>
+        <v>525.9299999999999</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4">
-        <v>-3.469999999999914</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -12799,11 +12799,11 @@
         <v>539.3</v>
       </c>
       <c r="C319" s="4">
-        <v>534.46</v>
+        <v>526.3200000000001</v>
       </c>
       <c r="D319" s="4"/>
       <c r="E319" s="4">
-        <v>-4.839999999999918</v>
+        <v>-12.9799999999999</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -12814,11 +12814,11 @@
         <v>541.83</v>
       </c>
       <c r="C320" s="4">
-        <v>534.84</v>
+        <v>526.49</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4">
-        <v>-6.990000000000009</v>
+        <v>-15.34000000000003</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -12826,14 +12826,14 @@
         <v>46281.23472222222</v>
       </c>
       <c r="B321" s="4">
-        <v>541.28</v>
+        <v>535.9</v>
       </c>
       <c r="C321" s="4">
-        <v>535.12</v>
+        <v>526.59</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4">
-        <v>-6.159999999999968</v>
+        <v>-9.309999999999945</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -12844,11 +12844,11 @@
         <v>542.2</v>
       </c>
       <c r="C322" s="4">
-        <v>535.22</v>
+        <v>527.0700000000001</v>
       </c>
       <c r="D322" s="4"/>
       <c r="E322" s="4">
-        <v>-6.980000000000018</v>
+        <v>-15.13</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -12859,11 +12859,11 @@
         <v>548.1900000000001</v>
       </c>
       <c r="C323" s="4">
-        <v>535.3099999999999</v>
+        <v>527.1900000000001</v>
       </c>
       <c r="D323" s="4"/>
       <c r="E323" s="4">
-        <v>-12.88000000000011</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -12874,11 +12874,11 @@
         <v>544.52</v>
       </c>
       <c r="C324" s="4">
-        <v>535.61</v>
+        <v>527.3200000000001</v>
       </c>
       <c r="D324" s="4"/>
       <c r="E324" s="4">
-        <v>-8.909999999999968</v>
+        <v>-17.19999999999993</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -12889,11 +12889,11 @@
         <v>536.5</v>
       </c>
       <c r="C325" s="4">
-        <v>535.75</v>
+        <v>527.42</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4">
-        <v>-0.75</v>
+        <v>-9.080000000000041</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -12904,11 +12904,11 @@
         <v>532.54</v>
       </c>
       <c r="C326" s="4">
-        <v>535.8200000000001</v>
+        <v>527.51</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4">
-        <v>3.280000000000086</v>
+        <v>-5.029999999999973</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -12916,14 +12916,14 @@
         <v>46281.24097222222</v>
       </c>
       <c r="B327" s="4">
-        <v>537.7</v>
+        <v>522.4400000000001</v>
       </c>
       <c r="C327" s="4">
-        <v>535.85</v>
+        <v>527.67</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4">
-        <v>-1.850000000000023</v>
+        <v>5.229999999999905</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -12934,11 +12934,11 @@
         <v>535.72</v>
       </c>
       <c r="C328" s="4">
-        <v>535.99</v>
+        <v>527.83</v>
       </c>
       <c r="D328" s="4"/>
       <c r="E328" s="4">
-        <v>0.2699999999999818</v>
+        <v>-7.889999999999986</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -12949,11 +12949,11 @@
         <v>535</v>
       </c>
       <c r="C329" s="4">
-        <v>536.08</v>
+        <v>527.84</v>
       </c>
       <c r="D329" s="4"/>
       <c r="E329" s="4">
-        <v>1.080000000000041</v>
+        <v>-7.159999999999968</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -12964,11 +12964,11 @@
         <v>532.77</v>
       </c>
       <c r="C330" s="4">
-        <v>536.27</v>
+        <v>527.88</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4">
-        <v>3.5</v>
+        <v>-4.889999999999986</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -12979,11 +12979,11 @@
         <v>546.05</v>
       </c>
       <c r="C331" s="4">
-        <v>536.5</v>
+        <v>528.02</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4">
-        <v>-9.549999999999955</v>
+        <v>-18.02999999999997</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -12994,11 +12994,11 @@
         <v>538.4400000000001</v>
       </c>
       <c r="C332" s="4">
-        <v>536.55</v>
+        <v>528.24</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4">
-        <v>-1.8900000000001</v>
+        <v>-10.20000000000005</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -13009,11 +13009,11 @@
         <v>537.2</v>
       </c>
       <c r="C333" s="4">
-        <v>536.64</v>
+        <v>528.42</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="4">
-        <v>-0.5600000000000591</v>
+        <v>-8.780000000000086</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -13024,11 +13024,11 @@
         <v>535.96</v>
       </c>
       <c r="C334" s="4">
-        <v>536.76</v>
+        <v>528.53</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4">
-        <v>0.7999999999999545</v>
+        <v>-7.430000000000064</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -13039,11 +13039,11 @@
         <v>503.33</v>
       </c>
       <c r="C335" s="4">
-        <v>536.79</v>
+        <v>528.64</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4">
-        <v>33.45999999999998</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -13054,11 +13054,11 @@
         <v>536.52</v>
       </c>
       <c r="C336" s="4">
-        <v>536.87</v>
+        <v>528.74</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="4">
-        <v>0.3500000000000227</v>
+        <v>-7.779999999999973</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -13066,14 +13066,14 @@
         <v>46281.25138888889</v>
       </c>
       <c r="B337" s="4">
-        <v>540.8</v>
+        <v>555.75</v>
       </c>
       <c r="C337" s="4">
-        <v>536.88</v>
+        <v>528.83</v>
       </c>
       <c r="D337" s="4"/>
       <c r="E337" s="4">
-        <v>-3.919999999999959</v>
+        <v>-26.91999999999996</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -13084,11 +13084,11 @@
         <v>536.3</v>
       </c>
       <c r="C338" s="4">
-        <v>537.17</v>
+        <v>529.0700000000001</v>
       </c>
       <c r="D338" s="4"/>
       <c r="E338" s="4">
-        <v>0.8700000000000045</v>
+        <v>-7.229999999999905</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -13099,11 +13099,11 @@
         <v>535.1</v>
       </c>
       <c r="C339" s="4">
-        <v>537.27</v>
+        <v>529.16</v>
       </c>
       <c r="D339" s="4"/>
       <c r="E339" s="4">
-        <v>2.169999999999959</v>
+        <v>-5.940000000000055</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -13114,11 +13114,11 @@
         <v>532.08</v>
       </c>
       <c r="C340" s="4">
-        <v>537.3200000000001</v>
+        <v>529.26</v>
       </c>
       <c r="D340" s="4"/>
       <c r="E340" s="4">
-        <v>5.240000000000009</v>
+        <v>-2.82000000000005</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -13129,11 +13129,11 @@
         <v>550.52</v>
       </c>
       <c r="C341" s="4">
-        <v>537.46</v>
+        <v>529.37</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4">
-        <v>-13.05999999999995</v>
+        <v>-21.14999999999998</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -13144,11 +13144,11 @@
         <v>531.95</v>
       </c>
       <c r="C342" s="4">
-        <v>537.46</v>
+        <v>529.38</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4">
-        <v>5.509999999999991</v>
+        <v>-2.57000000000005</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -13156,14 +13156,14 @@
         <v>46281.25763888889</v>
       </c>
       <c r="B343" s="4">
-        <v>533.6</v>
+        <v>571.09</v>
       </c>
       <c r="C343" s="4">
-        <v>537.52</v>
+        <v>529.4</v>
       </c>
       <c r="D343" s="4"/>
       <c r="E343" s="4">
-        <v>3.919999999999959</v>
+        <v>-41.69000000000005</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -13174,11 +13174,11 @@
         <v>533.37</v>
       </c>
       <c r="C344" s="4">
-        <v>537.64</v>
+        <v>529.47</v>
       </c>
       <c r="D344" s="4"/>
       <c r="E344" s="4">
-        <v>4.269999999999982</v>
+        <v>-3.899999999999977</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -13189,11 +13189,11 @@
         <v>557.4299999999999</v>
       </c>
       <c r="C345" s="4">
-        <v>537.66</v>
+        <v>529.53</v>
       </c>
       <c r="D345" s="4"/>
       <c r="E345" s="4">
-        <v>-19.76999999999998</v>
+        <v>-27.89999999999998</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -13204,11 +13204,11 @@
         <v>533.64</v>
       </c>
       <c r="C346" s="4">
-        <v>537.7</v>
+        <v>529.5700000000001</v>
       </c>
       <c r="D346" s="4"/>
       <c r="E346" s="4">
-        <v>4.060000000000059</v>
+        <v>-4.069999999999936</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -13219,11 +13219,11 @@
         <v>559.15</v>
       </c>
       <c r="C347" s="4">
-        <v>537.8</v>
+        <v>529.77</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4">
-        <v>-21.35000000000002</v>
+        <v>-29.38</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -13234,11 +13234,11 @@
         <v>530.87</v>
       </c>
       <c r="C348" s="4">
-        <v>537.8099999999999</v>
+        <v>529.8</v>
       </c>
       <c r="D348" s="4"/>
       <c r="E348" s="4">
-        <v>6.939999999999941</v>
+        <v>-1.07000000000005</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -13249,11 +13249,11 @@
         <v>533.4</v>
       </c>
       <c r="C349" s="4">
-        <v>537.9</v>
+        <v>530.05</v>
       </c>
       <c r="D349" s="4"/>
       <c r="E349" s="4">
-        <v>4.5</v>
+        <v>-3.350000000000023</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -13264,11 +13264,11 @@
         <v>534.59</v>
       </c>
       <c r="C350" s="4">
-        <v>537.91</v>
+        <v>530.1</v>
       </c>
       <c r="D350" s="4"/>
       <c r="E350" s="4">
-        <v>3.319999999999936</v>
+        <v>-4.490000000000009</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -13279,11 +13279,11 @@
         <v>536.8</v>
       </c>
       <c r="C351" s="4">
-        <v>537.92</v>
+        <v>530.1799999999999</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4">
-        <v>1.120000000000005</v>
+        <v>-6.620000000000005</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -13294,11 +13294,11 @@
         <v>539.65</v>
       </c>
       <c r="C352" s="4">
-        <v>538.12</v>
+        <v>530.3099999999999</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4">
-        <v>-1.529999999999973</v>
+        <v>-9.340000000000032</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -13309,11 +13309,11 @@
         <v>555.92</v>
       </c>
       <c r="C353" s="4">
-        <v>538.33</v>
+        <v>530.46</v>
       </c>
       <c r="D353" s="4"/>
       <c r="E353" s="4">
-        <v>-17.58999999999992</v>
+        <v>-25.45999999999992</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -13324,11 +13324,11 @@
         <v>530.52</v>
       </c>
       <c r="C354" s="4">
-        <v>538.3200000000001</v>
+        <v>530.45</v>
       </c>
       <c r="D354" s="4"/>
       <c r="E354" s="4">
-        <v>7.800000000000068</v>
+        <v>-0.06999999999993634</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -13339,11 +13339,11 @@
         <v>529.4</v>
       </c>
       <c r="C355" s="4">
-        <v>538.51</v>
+        <v>530.46</v>
       </c>
       <c r="D355" s="4"/>
       <c r="E355" s="4">
-        <v>9.110000000000014</v>
+        <v>1.060000000000059</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -13354,11 +13354,11 @@
         <v>528.64</v>
       </c>
       <c r="C356" s="4">
-        <v>538.65</v>
+        <v>530.58</v>
       </c>
       <c r="D356" s="4"/>
       <c r="E356" s="4">
-        <v>10.00999999999999</v>
+        <v>1.940000000000055</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -13369,11 +13369,11 @@
         <v>529.4</v>
       </c>
       <c r="C357" s="4">
-        <v>538.89</v>
+        <v>530.76</v>
       </c>
       <c r="D357" s="4"/>
       <c r="E357" s="4">
-        <v>9.490000000000009</v>
+        <v>1.360000000000014</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -13384,11 +13384,11 @@
         <v>527.42</v>
       </c>
       <c r="C358" s="4">
-        <v>538.97</v>
+        <v>531.02</v>
       </c>
       <c r="D358" s="4"/>
       <c r="E358" s="4">
-        <v>11.55000000000007</v>
+        <v>3.600000000000023</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -13399,11 +13399,11 @@
         <v>550.58</v>
       </c>
       <c r="C359" s="4">
-        <v>539.0700000000001</v>
+        <v>531.02</v>
       </c>
       <c r="D359" s="4"/>
       <c r="E359" s="4">
-        <v>-11.50999999999999</v>
+        <v>-19.56000000000006</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -13414,11 +13414,11 @@
         <v>524.08</v>
       </c>
       <c r="C360" s="4">
-        <v>539.22</v>
+        <v>531.29</v>
       </c>
       <c r="D360" s="4"/>
       <c r="E360" s="4">
-        <v>15.13999999999999</v>
+        <v>7.209999999999923</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -13426,14 +13426,14 @@
         <v>46281.27638888889</v>
       </c>
       <c r="B361" s="4">
-        <v>462.29</v>
+        <v>524.6</v>
       </c>
       <c r="C361" s="4">
-        <v>539.3</v>
+        <v>531.51</v>
       </c>
       <c r="D361" s="4"/>
       <c r="E361" s="4">
-        <v>77.00999999999993</v>
+        <v>6.909999999999968</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -13444,11 +13444,11 @@
         <v>522.1</v>
       </c>
       <c r="C362" s="4">
-        <v>539.49</v>
+        <v>531.59</v>
       </c>
       <c r="D362" s="4"/>
       <c r="E362" s="4">
-        <v>17.38999999999999</v>
+        <v>9.490000000000009</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -13456,14 +13456,14 @@
         <v>46281.27847222222</v>
       </c>
       <c r="B363" s="4">
-        <v>535.3099999999999</v>
+        <v>528.3</v>
       </c>
       <c r="C363" s="4">
-        <v>539.54</v>
+        <v>531.65</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4">
-        <v>4.230000000000018</v>
+        <v>3.350000000000023</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -13474,11 +13474,11 @@
         <v>520.7</v>
       </c>
       <c r="C364" s="4">
-        <v>539.62</v>
+        <v>531.73</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4">
-        <v>18.91999999999996</v>
+        <v>11.02999999999997</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -13489,11 +13489,11 @@
         <v>565.09</v>
       </c>
       <c r="C365" s="4">
-        <v>539.61</v>
+        <v>531.84</v>
       </c>
       <c r="D365" s="4"/>
       <c r="E365" s="4">
-        <v>-25.48000000000002</v>
+        <v>-33.25</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -13504,11 +13504,11 @@
         <v>523.4299999999999</v>
       </c>
       <c r="C366" s="4">
-        <v>539.73</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4">
-        <v>16.30000000000007</v>
+        <v>8.629999999999995</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -13519,11 +13519,11 @@
         <v>548.49</v>
       </c>
       <c r="C367" s="4">
-        <v>539.74</v>
+        <v>532.11</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4">
-        <v>-8.75</v>
+        <v>-16.38</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -13534,11 +13534,11 @@
         <v>518.79</v>
       </c>
       <c r="C368" s="4">
-        <v>540.03</v>
+        <v>532.23</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4">
-        <v>21.24000000000001</v>
+        <v>13.44000000000005</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -13549,11 +13549,11 @@
         <v>532.1</v>
       </c>
       <c r="C369" s="4">
-        <v>540.14</v>
+        <v>532.4</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4">
-        <v>8.039999999999964</v>
+        <v>0.2999999999999545</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -13564,11 +13564,11 @@
         <v>522.37</v>
       </c>
       <c r="C370" s="4">
-        <v>540.16</v>
+        <v>532.4299999999999</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4">
-        <v>17.78999999999996</v>
+        <v>10.05999999999995</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -13579,11 +13579,11 @@
         <v>552.79</v>
       </c>
       <c r="C371" s="4">
-        <v>540.15</v>
+        <v>532.45</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4">
-        <v>-12.63999999999999</v>
+        <v>-20.33999999999992</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -13594,11 +13594,11 @@
         <v>516.04</v>
       </c>
       <c r="C372" s="4">
-        <v>540.27</v>
+        <v>532.37</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4">
-        <v>24.23000000000002</v>
+        <v>16.33000000000004</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -13609,11 +13609,11 @@
         <v>539.2</v>
       </c>
       <c r="C373" s="4">
-        <v>540.23</v>
+        <v>532.34</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4">
-        <v>1.029999999999973</v>
+        <v>-6.860000000000014</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -13624,11 +13624,11 @@
         <v>526.3099999999999</v>
       </c>
       <c r="C374" s="4">
-        <v>540.1900000000001</v>
+        <v>532.34</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4">
-        <v>13.88000000000011</v>
+        <v>6.030000000000086</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -13639,11 +13639,11 @@
         <v>546.84</v>
       </c>
       <c r="C375" s="4">
-        <v>540.2</v>
+        <v>532.36</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4">
-        <v>-6.639999999999986</v>
+        <v>-14.48000000000002</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -13654,11 +13654,11 @@
         <v>521.63</v>
       </c>
       <c r="C376" s="4">
-        <v>540.1</v>
+        <v>532.34</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4">
-        <v>18.47000000000003</v>
+        <v>10.71000000000004</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -13669,11 +13669,11 @@
         <v>534.3</v>
       </c>
       <c r="C377" s="4">
-        <v>540.23</v>
+        <v>532.39</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4">
-        <v>5.930000000000064</v>
+        <v>-1.909999999999968</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -13684,11 +13684,11 @@
         <v>515.02</v>
       </c>
       <c r="C378" s="4">
-        <v>540.14</v>
+        <v>532.24</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4">
-        <v>25.12</v>
+        <v>17.22000000000003</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -13696,14 +13696,14 @@
         <v>46281.29513888889</v>
       </c>
       <c r="B379" s="4">
-        <v>536.6</v>
+        <v>519.42</v>
       </c>
       <c r="C379" s="4">
-        <v>540.14</v>
+        <v>532.21</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4">
-        <v>3.539999999999964</v>
+        <v>12.79000000000008</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -13714,11 +13714,11 @@
         <v>502.55</v>
       </c>
       <c r="C380" s="4">
-        <v>540.0599999999999</v>
+        <v>532.23</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4">
-        <v>37.50999999999993</v>
+        <v>29.68000000000001</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -13726,14 +13726,14 @@
         <v>46281.29722222222</v>
       </c>
       <c r="B381" s="4">
-        <v>519.6</v>
+        <v>454.59</v>
       </c>
       <c r="C381" s="4">
-        <v>540.1</v>
+        <v>532.41</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4">
-        <v>20.5</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -13744,11 +13744,11 @@
         <v>518.53</v>
       </c>
       <c r="C382" s="4">
-        <v>540.12</v>
+        <v>532.39</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4">
-        <v>21.59000000000003</v>
+        <v>13.86000000000001</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -13759,11 +13759,11 @@
         <v>550.28</v>
       </c>
       <c r="C383" s="4">
-        <v>540.17</v>
+        <v>532.33</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4">
-        <v>-10.11000000000001</v>
+        <v>-17.94999999999993</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -13774,11 +13774,11 @@
         <v>511.4</v>
       </c>
       <c r="C384" s="4">
-        <v>540.25</v>
+        <v>532.35</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4">
-        <v>28.85000000000002</v>
+        <v>20.95000000000005</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -13786,14 +13786,14 @@
         <v>46281.30138888889</v>
       </c>
       <c r="B385" s="4">
-        <v>513.6</v>
+        <v>523.2</v>
       </c>
       <c r="C385" s="4">
-        <v>540.15</v>
+        <v>532.33</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4">
-        <v>26.54999999999995</v>
+        <v>9.129999999999995</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -13804,11 +13804,11 @@
         <v>503.14</v>
       </c>
       <c r="C386" s="4">
-        <v>540.1799999999999</v>
+        <v>532.33</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4">
-        <v>37.03999999999996</v>
+        <v>29.19000000000005</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -13819,11 +13819,11 @@
         <v>525.3</v>
       </c>
       <c r="C387" s="4">
-        <v>540.17</v>
+        <v>532.33</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4">
-        <v>14.87</v>
+        <v>7.030000000000086</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -13834,11 +13834,11 @@
         <v>532.88</v>
       </c>
       <c r="C388" s="4">
-        <v>540.1799999999999</v>
+        <v>532.4299999999999</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4">
-        <v>7.299999999999955</v>
+        <v>-0.4500000000000455</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -13849,11 +13849,11 @@
         <v>532.74</v>
       </c>
       <c r="C389" s="4">
-        <v>540.17</v>
+        <v>532.53</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4">
-        <v>7.42999999999995</v>
+        <v>-0.2100000000000364</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -13864,11 +13864,11 @@
         <v>515.45</v>
       </c>
       <c r="C390" s="4">
-        <v>540.12</v>
+        <v>532.55</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4">
-        <v>24.66999999999996</v>
+        <v>17.09999999999991</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -13876,14 +13876,14 @@
         <v>46281.30763888889</v>
       </c>
       <c r="B391" s="4">
-        <v>516.37</v>
+        <v>516</v>
       </c>
       <c r="C391" s="4">
-        <v>540.12</v>
+        <v>532.53</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4">
-        <v>23.75</v>
+        <v>16.52999999999997</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -13894,11 +13894,11 @@
         <v>509.33</v>
       </c>
       <c r="C392" s="4">
-        <v>540.2</v>
+        <v>532.53</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4">
-        <v>30.87000000000006</v>
+        <v>23.19999999999999</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -13909,11 +13909,11 @@
         <v>535.72</v>
       </c>
       <c r="C393" s="4">
-        <v>540.1900000000001</v>
+        <v>532.5</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4">
-        <v>4.470000000000027</v>
+        <v>-3.220000000000027</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -13924,11 +13924,11 @@
         <v>513.78</v>
       </c>
       <c r="C394" s="4">
-        <v>540.3</v>
+        <v>532.5</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4">
-        <v>26.51999999999998</v>
+        <v>18.72000000000003</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -13939,11 +13939,11 @@
         <v>499.28</v>
       </c>
       <c r="C395" s="4">
-        <v>540.24</v>
+        <v>532.47</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4">
-        <v>40.96000000000004</v>
+        <v>33.19000000000005</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -13954,11 +13954,11 @@
         <v>520.5</v>
       </c>
       <c r="C396" s="4">
-        <v>540.26</v>
+        <v>532.58</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4">
-        <v>19.75999999999999</v>
+        <v>12.08000000000004</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -13969,11 +13969,11 @@
         <v>524.8</v>
       </c>
       <c r="C397" s="4">
-        <v>540.28</v>
+        <v>532.63</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4">
-        <v>15.48000000000002</v>
+        <v>7.830000000000041</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -13984,11 +13984,11 @@
         <v>532.75</v>
       </c>
       <c r="C398" s="4">
-        <v>540.38</v>
+        <v>532.6</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4">
-        <v>7.629999999999995</v>
+        <v>-0.1499999999999773</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -13999,11 +13999,11 @@
         <v>557.33</v>
       </c>
       <c r="C399" s="4">
-        <v>540.35</v>
+        <v>532.5599999999999</v>
       </c>
       <c r="D399" s="4"/>
       <c r="E399" s="4">
-        <v>-16.98000000000002</v>
+        <v>-24.7700000000001</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -14014,11 +14014,11 @@
         <v>504.44</v>
       </c>
       <c r="C400" s="4">
-        <v>540.34</v>
+        <v>532.47</v>
       </c>
       <c r="D400" s="4"/>
       <c r="E400" s="4">
-        <v>35.90000000000003</v>
+        <v>28.03000000000003</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -14029,11 +14029,11 @@
         <v>529.72</v>
       </c>
       <c r="C401" s="4">
-        <v>540.28</v>
+        <v>532.46</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4">
-        <v>10.55999999999995</v>
+        <v>2.740000000000009</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -14044,11 +14044,11 @@
         <v>515.0700000000001</v>
       </c>
       <c r="C402" s="4">
-        <v>540.37</v>
+        <v>532.62</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4">
-        <v>25.29999999999995</v>
+        <v>17.54999999999995</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -14059,11 +14059,11 @@
         <v>526.4</v>
       </c>
       <c r="C403" s="4">
-        <v>540.26</v>
+        <v>532.6</v>
       </c>
       <c r="D403" s="4"/>
       <c r="E403" s="4">
-        <v>13.86000000000001</v>
+        <v>6.200000000000045</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -14074,11 +14074,11 @@
         <v>522.03</v>
       </c>
       <c r="C404" s="4">
-        <v>540.1900000000001</v>
+        <v>532.55</v>
       </c>
       <c r="D404" s="4"/>
       <c r="E404" s="4">
-        <v>18.16000000000008</v>
+        <v>10.51999999999998</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -14089,11 +14089,11 @@
         <v>532.26</v>
       </c>
       <c r="C405" s="4">
-        <v>540.0700000000001</v>
+        <v>532.33</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="4">
-        <v>7.810000000000059</v>
+        <v>0.07000000000005002</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -14104,11 +14104,11 @@
         <v>515.75</v>
       </c>
       <c r="C406" s="4">
-        <v>540.08</v>
+        <v>532.23</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4">
-        <v>24.33000000000004</v>
+        <v>16.48000000000002</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -14116,14 +14116,14 @@
         <v>46281.32430555556</v>
       </c>
       <c r="B407" s="4">
-        <v>530.5</v>
+        <v>538.75</v>
       </c>
       <c r="C407" s="4">
-        <v>539.99</v>
+        <v>531.98</v>
       </c>
       <c r="D407" s="4"/>
       <c r="E407" s="4">
-        <v>9.490000000000009</v>
+        <v>-6.769999999999982</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -14134,11 +14134,11 @@
         <v>537.29</v>
       </c>
       <c r="C408" s="4">
-        <v>539.96</v>
+        <v>531.89</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4">
-        <v>2.670000000000073</v>
+        <v>-5.399999999999977</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -14146,14 +14146,14 @@
         <v>46281.32638888889</v>
       </c>
       <c r="B409" s="4">
-        <v>542.78</v>
+        <v>532.3</v>
       </c>
       <c r="C409" s="4">
-        <v>539.8099999999999</v>
+        <v>531.79</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4">
-        <v>-2.970000000000027</v>
+        <v>-0.5099999999999909</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -14164,11 +14164,11 @@
         <v>543.8099999999999</v>
       </c>
       <c r="C410" s="4">
-        <v>539.65</v>
+        <v>531.61</v>
       </c>
       <c r="D410" s="4"/>
       <c r="E410" s="4">
-        <v>-4.159999999999968</v>
+        <v>-12.19999999999993</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -14179,11 +14179,11 @@
         <v>535.2</v>
       </c>
       <c r="C411" s="4">
-        <v>539.62</v>
+        <v>531.59</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4">
-        <v>4.419999999999959</v>
+        <v>-3.610000000000014</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -14194,11 +14194,11 @@
         <v>525.26</v>
       </c>
       <c r="C412" s="4">
-        <v>539.63</v>
+        <v>531.5599999999999</v>
       </c>
       <c r="D412" s="4"/>
       <c r="E412" s="4">
-        <v>14.37</v>
+        <v>6.299999999999955</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -14206,14 +14206,14 @@
         <v>46281.33055555556</v>
       </c>
       <c r="B413" s="4">
-        <v>545.6</v>
+        <v>495.22</v>
       </c>
       <c r="C413" s="4">
-        <v>539.63</v>
+        <v>531.65</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4">
-        <v>-5.970000000000027</v>
+        <v>36.42999999999995</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -14224,11 +14224,11 @@
         <v>557.2</v>
       </c>
       <c r="C414" s="4">
-        <v>539.67</v>
+        <v>531.79</v>
       </c>
       <c r="D414" s="4"/>
       <c r="E414" s="4">
-        <v>-17.53000000000009</v>
+        <v>-25.41000000000008</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -14239,11 +14239,11 @@
         <v>537.8</v>
       </c>
       <c r="C415" s="4">
-        <v>539.5599999999999</v>
+        <v>531.75</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4">
-        <v>1.759999999999991</v>
+        <v>-6.049999999999955</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -14254,11 +14254,11 @@
         <v>552.5</v>
       </c>
       <c r="C416" s="4">
-        <v>539.53</v>
+        <v>531.59</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4">
-        <v>-12.97000000000003</v>
+        <v>-20.90999999999997</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -14269,11 +14269,11 @@
         <v>513.0599999999999</v>
       </c>
       <c r="C417" s="4">
-        <v>539.46</v>
+        <v>531.48</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4">
-        <v>26.40000000000009</v>
+        <v>18.42000000000007</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -14284,11 +14284,11 @@
         <v>539.25</v>
       </c>
       <c r="C418" s="4">
-        <v>539.46</v>
+        <v>531.55</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4">
-        <v>0.2100000000000364</v>
+        <v>-7.700000000000045</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -14296,14 +14296,14 @@
         <v>46281.33680555555</v>
       </c>
       <c r="B419" s="4">
-        <v>538.3</v>
+        <v>503.04</v>
       </c>
       <c r="C419" s="4">
-        <v>539.39</v>
+        <v>531.48</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4">
-        <v>1.090000000000032</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -14314,11 +14314,11 @@
         <v>543.6900000000001</v>
       </c>
       <c r="C420" s="4">
-        <v>539.39</v>
+        <v>531.4299999999999</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4">
-        <v>-4.300000000000068</v>
+        <v>-12.2600000000001</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -14329,11 +14329,11 @@
         <v>544.3</v>
       </c>
       <c r="C421" s="4">
-        <v>539.35</v>
+        <v>531.37</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4">
-        <v>-4.949999999999932</v>
+        <v>-12.92999999999995</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -14344,11 +14344,11 @@
         <v>544.87</v>
       </c>
       <c r="C422" s="4">
-        <v>539.39</v>
+        <v>531.4</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4">
-        <v>-5.480000000000018</v>
+        <v>-13.47000000000003</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -14359,11 +14359,11 @@
         <v>535.89</v>
       </c>
       <c r="C423" s="4">
-        <v>539.4400000000001</v>
+        <v>531.3099999999999</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4">
-        <v>3.550000000000068</v>
+        <v>-4.580000000000041</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -14374,11 +14374,11 @@
         <v>541.46</v>
       </c>
       <c r="C424" s="4">
-        <v>539.53</v>
+        <v>531.35</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4">
-        <v>-1.930000000000064</v>
+        <v>-10.11000000000001</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -14389,11 +14389,11 @@
         <v>543.4</v>
       </c>
       <c r="C425" s="4">
-        <v>539.52</v>
+        <v>531.34</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4">
-        <v>-3.879999999999995</v>
+        <v>-12.05999999999995</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -14404,11 +14404,11 @@
         <v>546.01</v>
       </c>
       <c r="C426" s="4">
-        <v>539.49</v>
+        <v>531.38</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4">
-        <v>-6.519999999999982</v>
+        <v>-14.63</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -14419,11 +14419,11 @@
         <v>551.7</v>
       </c>
       <c r="C427" s="4">
-        <v>539.54</v>
+        <v>531.41</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4">
-        <v>-12.16000000000008</v>
+        <v>-20.29000000000008</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -14434,11 +14434,11 @@
         <v>551.9299999999999</v>
       </c>
       <c r="C428" s="4">
-        <v>539.54</v>
+        <v>531.39</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4">
-        <v>-12.38999999999999</v>
+        <v>-20.53999999999996</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -14446,14 +14446,14 @@
         <v>46281.34722222222</v>
       </c>
       <c r="B429" s="4">
-        <v>555.0599999999999</v>
+        <v>549.4</v>
       </c>
       <c r="C429" s="4">
-        <v>539.5</v>
+        <v>531.33</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4">
-        <v>-15.55999999999995</v>
+        <v>-18.06999999999994</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -14464,11 +14464,11 @@
         <v>542.5</v>
       </c>
       <c r="C430" s="4">
-        <v>539.51</v>
+        <v>531.41</v>
       </c>
       <c r="D430" s="4"/>
       <c r="E430" s="4">
-        <v>-2.990000000000009</v>
+        <v>-11.09000000000003</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -14479,11 +14479,11 @@
         <v>558.28</v>
       </c>
       <c r="C431" s="4">
-        <v>539.45</v>
+        <v>531.36</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4">
-        <v>-18.82999999999993</v>
+        <v>-26.91999999999996</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -14494,11 +14494,11 @@
         <v>534.39</v>
       </c>
       <c r="C432" s="4">
-        <v>539.54</v>
+        <v>531.41</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4">
-        <v>5.149999999999977</v>
+        <v>-2.980000000000018</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -14509,11 +14509,11 @@
         <v>545.3</v>
       </c>
       <c r="C433" s="4">
-        <v>539.5599999999999</v>
+        <v>531.3200000000001</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4">
-        <v>-5.740000000000009</v>
+        <v>-13.9799999999999</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -14521,14 +14521,14 @@
         <v>46281.35277777778</v>
       </c>
       <c r="B434" s="4">
-        <v>546.8</v>
+        <v>554.92</v>
       </c>
       <c r="C434" s="4">
-        <v>539.52</v>
+        <v>531.35</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4">
-        <v>-7.279999999999973</v>
+        <v>-23.56999999999994</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -14536,14 +14536,14 @@
         <v>46281.35486111111</v>
       </c>
       <c r="B435" s="4">
-        <v>543.22</v>
+        <v>539.4</v>
       </c>
       <c r="C435" s="4">
-        <v>539.41</v>
+        <v>531.42</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4">
-        <v>-3.810000000000059</v>
+        <v>-7.980000000000018</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -14554,11 +14554,11 @@
         <v>540.4</v>
       </c>
       <c r="C436" s="4">
-        <v>539.36</v>
+        <v>531.34</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4">
-        <v>-1.039999999999964</v>
+        <v>-9.059999999999945</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -14566,14 +14566,14 @@
         <v>46281.35902777778</v>
       </c>
       <c r="B437" s="4">
-        <v>543.5</v>
+        <v>525.36</v>
       </c>
       <c r="C437" s="4">
-        <v>539.3</v>
+        <v>531.1900000000001</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4">
-        <v>-4.200000000000045</v>
+        <v>5.830000000000041</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -14584,11 +14584,11 @@
         <v>543.8</v>
       </c>
       <c r="C438" s="4">
-        <v>539.2</v>
+        <v>531.05</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4">
-        <v>-4.599999999999909</v>
+        <v>-12.75</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -14596,14 +14596,14 @@
         <v>46281.36319444444</v>
       </c>
       <c r="B439" s="4">
-        <v>542.6</v>
+        <v>541.08</v>
       </c>
       <c r="C439" s="4">
-        <v>539.11</v>
+        <v>530.89</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4">
-        <v>-3.490000000000009</v>
+        <v>-10.19000000000005</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -14611,14 +14611,14 @@
         <v>46281.36527777778</v>
       </c>
       <c r="B440" s="4">
-        <v>543.2</v>
+        <v>550.15</v>
       </c>
       <c r="C440" s="4">
-        <v>538.96</v>
+        <v>530.75</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4">
-        <v>-4.240000000000009</v>
+        <v>-19.39999999999998</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -14629,11 +14629,11 @@
         <v>539.28</v>
       </c>
       <c r="C441" s="4">
-        <v>538.8</v>
+        <v>530.61</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4">
-        <v>-0.4800000000000182</v>
+        <v>-8.669999999999959</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -14644,11 +14644,11 @@
         <v>544.9</v>
       </c>
       <c r="C442" s="4">
-        <v>538.65</v>
+        <v>530.47</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4">
-        <v>-6.25</v>
+        <v>-14.42999999999995</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -14656,14 +14656,14 @@
         <v>46281.37152777778</v>
       </c>
       <c r="B443" s="4">
-        <v>535.37</v>
+        <v>541.3</v>
       </c>
       <c r="C443" s="4">
-        <v>538.5599999999999</v>
+        <v>530.42</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4">
-        <v>3.189999999999941</v>
+        <v>-10.88</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -14671,14 +14671,14 @@
         <v>46281.37361111111</v>
       </c>
       <c r="B444" s="4">
-        <v>538.7</v>
+        <v>536.03</v>
       </c>
       <c r="C444" s="4">
-        <v>538.4299999999999</v>
+        <v>530.25</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4">
-        <v>-0.2700000000000955</v>
+        <v>-5.779999999999973</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -14686,14 +14686,14 @@
         <v>46281.37569444445</v>
       </c>
       <c r="B445" s="4">
-        <v>541.66</v>
+        <v>551.4</v>
       </c>
       <c r="C445" s="4">
-        <v>538.41</v>
+        <v>530.2</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4">
-        <v>-3.25</v>
+        <v>-21.19999999999993</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -14701,14 +14701,14 @@
         <v>46281.37777777778</v>
       </c>
       <c r="B446" s="4">
-        <v>539.5</v>
+        <v>543.02</v>
       </c>
       <c r="C446" s="4">
-        <v>538.37</v>
+        <v>530.0700000000001</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4">
-        <v>-1.129999999999995</v>
+        <v>-12.94999999999993</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -14719,11 +14719,11 @@
         <v>536.77</v>
       </c>
       <c r="C447" s="4">
-        <v>538.3099999999999</v>
+        <v>530.11</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4">
-        <v>1.539999999999964</v>
+        <v>-6.659999999999968</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -14731,14 +14731,14 @@
         <v>46281.38194444445</v>
       </c>
       <c r="B448" s="4">
-        <v>548.23</v>
+        <v>538</v>
       </c>
       <c r="C448" s="4">
-        <v>538.22</v>
+        <v>530.21</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4">
-        <v>-10.00999999999999</v>
+        <v>-7.789999999999964</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -14749,11 +14749,11 @@
         <v>549.02</v>
       </c>
       <c r="C449" s="4">
-        <v>538.1</v>
+        <v>530.08</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4">
-        <v>-10.91999999999996</v>
+        <v>-18.93999999999994</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -14764,11 +14764,11 @@
         <v>552.51</v>
       </c>
       <c r="C450" s="4">
-        <v>538.03</v>
+        <v>530.01</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4">
-        <v>-14.48000000000002</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -14779,11 +14779,11 @@
         <v>539</v>
       </c>
       <c r="C451" s="4">
-        <v>538.01</v>
+        <v>529.92</v>
       </c>
       <c r="D451" s="4"/>
       <c r="E451" s="4">
-        <v>-0.9900000000000091</v>
+        <v>-9.080000000000041</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -14791,14 +14791,14 @@
         <v>46281.39027777778</v>
       </c>
       <c r="B452" s="4">
-        <v>540</v>
+        <v>539.28</v>
       </c>
       <c r="C452" s="4">
-        <v>537.9</v>
+        <v>529.83</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4">
-        <v>-2.100000000000023</v>
+        <v>-9.449999999999932</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -14806,14 +14806,14 @@
         <v>46281.39236111111</v>
       </c>
       <c r="B453" s="4">
-        <v>551.5700000000001</v>
+        <v>536</v>
       </c>
       <c r="C453" s="4">
-        <v>537.86</v>
+        <v>529.72</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4">
-        <v>-13.71000000000004</v>
+        <v>-6.279999999999973</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -14824,11 +14824,11 @@
         <v>552.1</v>
       </c>
       <c r="C454" s="4">
-        <v>537.8</v>
+        <v>529.74</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4">
-        <v>-14.30000000000007</v>
+        <v>-22.36000000000001</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -14839,11 +14839,11 @@
         <v>542.35</v>
       </c>
       <c r="C455" s="4">
-        <v>537.75</v>
+        <v>529.73</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4">
-        <v>-4.600000000000023</v>
+        <v>-12.62</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -14854,11 +14854,11 @@
         <v>539.8</v>
       </c>
       <c r="C456" s="4">
-        <v>537.58</v>
+        <v>529.5599999999999</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4">
-        <v>-2.219999999999914</v>
+        <v>-10.24000000000001</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -14869,11 +14869,11 @@
         <v>529.22</v>
       </c>
       <c r="C457" s="4">
-        <v>537.49</v>
+        <v>529.49</v>
       </c>
       <c r="D457" s="4"/>
       <c r="E457" s="4">
-        <v>8.269999999999982</v>
+        <v>0.2699999999999818</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -14884,11 +14884,11 @@
         <v>529.3099999999999</v>
       </c>
       <c r="C458" s="4">
-        <v>537.37</v>
+        <v>529.34</v>
       </c>
       <c r="D458" s="4"/>
       <c r="E458" s="4">
-        <v>8.060000000000059</v>
+        <v>0.0300000000000864</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -14899,11 +14899,11 @@
         <v>540.3099999999999</v>
       </c>
       <c r="C459" s="4">
-        <v>537.1</v>
+        <v>529.0599999999999</v>
       </c>
       <c r="D459" s="4"/>
       <c r="E459" s="4">
-        <v>-3.209999999999923</v>
+        <v>-11.25</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -14911,14 +14911,14 @@
         <v>46281.40694444445</v>
       </c>
       <c r="B460" s="4">
-        <v>528.36</v>
+        <v>543.4</v>
       </c>
       <c r="C460" s="4">
-        <v>536.88</v>
+        <v>528.87</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4">
-        <v>8.519999999999982</v>
+        <v>-14.52999999999997</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -14929,11 +14929,11 @@
         <v>532.9</v>
       </c>
       <c r="C461" s="4">
-        <v>536.59</v>
+        <v>528.7</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4">
-        <v>3.690000000000055</v>
+        <v>-4.199999999999932</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -14941,14 +14941,14 @@
         <v>46281.41111111111</v>
       </c>
       <c r="B462" s="4">
-        <v>548.0700000000001</v>
+        <v>538.9</v>
       </c>
       <c r="C462" s="4">
-        <v>536.42</v>
+        <v>528.48</v>
       </c>
       <c r="D462" s="4"/>
       <c r="E462" s="4">
-        <v>-11.65000000000009</v>
+        <v>-10.41999999999996</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -14956,14 +14956,14 @@
         <v>46281.41319444445</v>
       </c>
       <c r="B463" s="4">
-        <v>541.3</v>
+        <v>542.75</v>
       </c>
       <c r="C463" s="4">
-        <v>536.17</v>
+        <v>528.21</v>
       </c>
       <c r="D463" s="4"/>
       <c r="E463" s="4">
-        <v>-5.129999999999995</v>
+        <v>-14.53999999999996</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -14971,14 +14971,14 @@
         <v>46281.41527777778</v>
       </c>
       <c r="B464" s="4">
-        <v>537.7</v>
+        <v>550.8099999999999</v>
       </c>
       <c r="C464" s="4">
-        <v>535.95</v>
+        <v>527.98</v>
       </c>
       <c r="D464" s="4"/>
       <c r="E464" s="4">
-        <v>-1.75</v>
+        <v>-22.82999999999993</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -14986,14 +14986,14 @@
         <v>46281.41736111111</v>
       </c>
       <c r="B465" s="4">
-        <v>543.3</v>
+        <v>531.1</v>
       </c>
       <c r="C465" s="4">
-        <v>535.73</v>
+        <v>527.6900000000001</v>
       </c>
       <c r="D465" s="4"/>
       <c r="E465" s="4">
-        <v>-7.569999999999936</v>
+        <v>-3.409999999999968</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -15004,11 +15004,11 @@
         <v>539.3200000000001</v>
       </c>
       <c r="C466" s="4">
-        <v>535.54</v>
+        <v>527.54</v>
       </c>
       <c r="D466" s="4"/>
       <c r="E466" s="4">
-        <v>-3.780000000000086</v>
+        <v>-11.78000000000009</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -15019,11 +15019,11 @@
         <v>553.5599999999999</v>
       </c>
       <c r="C467" s="4">
-        <v>535.25</v>
+        <v>527.1900000000001</v>
       </c>
       <c r="D467" s="4"/>
       <c r="E467" s="4">
-        <v>-18.30999999999995</v>
+        <v>-26.36999999999989</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -15031,14 +15031,14 @@
         <v>46281.42361111111</v>
       </c>
       <c r="B468" s="4">
-        <v>528.7</v>
+        <v>545.02</v>
       </c>
       <c r="C468" s="4">
-        <v>534.79</v>
+        <v>526.66</v>
       </c>
       <c r="D468" s="4"/>
       <c r="E468" s="4">
-        <v>6.089999999999918</v>
+        <v>-18.36000000000001</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -15049,11 +15049,11 @@
         <v>543.3200000000001</v>
       </c>
       <c r="C469" s="4">
-        <v>534.26</v>
+        <v>526.36</v>
       </c>
       <c r="D469" s="4"/>
       <c r="E469" s="4">
-        <v>-9.060000000000059</v>
+        <v>-16.96000000000004</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -15064,11 +15064,11 @@
         <v>533.3</v>
       </c>
       <c r="C470" s="4">
-        <v>533.89</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="D470" s="4"/>
       <c r="E470" s="4">
-        <v>0.5900000000000318</v>
+        <v>-7.240000000000009</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -15079,11 +15079,11 @@
         <v>545.4400000000001</v>
       </c>
       <c r="C471" s="4">
-        <v>533.3</v>
+        <v>525.1</v>
       </c>
       <c r="D471" s="4"/>
       <c r="E471" s="4">
-        <v>-12.1400000000001</v>
+        <v>-20.34000000000003</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -15094,11 +15094,11 @@
         <v>543.64</v>
       </c>
       <c r="C472" s="4">
-        <v>532.49</v>
+        <v>524.5</v>
       </c>
       <c r="D472" s="4"/>
       <c r="E472" s="4">
-        <v>-11.14999999999998</v>
+        <v>-19.13999999999999</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -15106,14 +15106,14 @@
         <v>46281.43402777778</v>
       </c>
       <c r="B473" s="4">
-        <v>537.61</v>
+        <v>533.5</v>
       </c>
       <c r="C473" s="4">
-        <v>531.6900000000001</v>
+        <v>523.8200000000001</v>
       </c>
       <c r="D473" s="4"/>
       <c r="E473" s="4">
-        <v>-5.919999999999959</v>
+        <v>-9.67999999999995</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -15124,11 +15124,11 @@
         <v>544.61</v>
       </c>
       <c r="C474" s="4">
-        <v>531.42</v>
+        <v>523.61</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4">
-        <v>-13.19000000000005</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -15139,11 +15139,11 @@
         <v>529.7</v>
       </c>
       <c r="C475" s="4">
-        <v>531.03</v>
+        <v>523.04</v>
       </c>
       <c r="D475" s="4"/>
       <c r="E475" s="4">
-        <v>1.329999999999927</v>
+        <v>-6.660000000000082</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -15154,11 +15154,11 @@
         <v>538.88</v>
       </c>
       <c r="C476" s="4">
-        <v>530.38</v>
+        <v>522.59</v>
       </c>
       <c r="D476" s="4"/>
       <c r="E476" s="4">
-        <v>-8.5</v>
+        <v>-16.28999999999996</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -15169,11 +15169,11 @@
         <v>540.87</v>
       </c>
       <c r="C477" s="4">
-        <v>530.13</v>
+        <v>522.29</v>
       </c>
       <c r="D477" s="4"/>
       <c r="E477" s="4">
-        <v>-10.74000000000001</v>
+        <v>-18.58000000000004</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -15181,14 +15181,14 @@
         <v>46281.44444444445</v>
       </c>
       <c r="B478" s="4">
-        <v>556.7</v>
+        <v>552.25</v>
       </c>
       <c r="C478" s="4">
-        <v>530.1</v>
+        <v>522.12</v>
       </c>
       <c r="D478" s="4"/>
       <c r="E478" s="4">
-        <v>-26.60000000000002</v>
+        <v>-30.13</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -15199,11 +15199,11 @@
         <v>543.92</v>
       </c>
       <c r="C479" s="4">
-        <v>529.9</v>
+        <v>522.05</v>
       </c>
       <c r="D479" s="4"/>
       <c r="E479" s="4">
-        <v>-14.01999999999998</v>
+        <v>-21.87</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -15211,14 +15211,14 @@
         <v>46281.44861111111</v>
       </c>
       <c r="B480" s="4">
-        <v>543.25</v>
+        <v>523</v>
       </c>
       <c r="C480" s="4">
-        <v>529.78</v>
+        <v>521.91</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="4">
-        <v>-13.47000000000003</v>
+        <v>-1.090000000000032</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -15229,11 +15229,11 @@
         <v>548.6</v>
       </c>
       <c r="C481" s="4">
-        <v>529.59</v>
+        <v>521.77</v>
       </c>
       <c r="D481" s="4"/>
       <c r="E481" s="4">
-        <v>-19.00999999999999</v>
+        <v>-26.83000000000004</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -15241,14 +15241,14 @@
         <v>46281.45277777778</v>
       </c>
       <c r="B482" s="4">
-        <v>545.9299999999999</v>
+        <v>529.7</v>
       </c>
       <c r="C482" s="4">
-        <v>529.55</v>
+        <v>521.4400000000001</v>
       </c>
       <c r="D482" s="4"/>
       <c r="E482" s="4">
-        <v>-16.38</v>
+        <v>-8.259999999999991</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -15259,11 +15259,11 @@
         <v>544.1900000000001</v>
       </c>
       <c r="C483" s="4">
-        <v>529.3</v>
+        <v>521.28</v>
       </c>
       <c r="D483" s="4"/>
       <c r="E483" s="4">
-        <v>-14.8900000000001</v>
+        <v>-22.91000000000008</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -15274,11 +15274,11 @@
         <v>535.24</v>
       </c>
       <c r="C484" s="4">
-        <v>529.14</v>
+        <v>521.12</v>
       </c>
       <c r="D484" s="4"/>
       <c r="E484" s="4">
-        <v>-6.100000000000023</v>
+        <v>-14.12</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -15289,11 +15289,11 @@
         <v>529.04</v>
       </c>
       <c r="C485" s="4">
-        <v>528.92</v>
+        <v>520.86</v>
       </c>
       <c r="D485" s="4"/>
       <c r="E485" s="4">
-        <v>-0.1200000000000045</v>
+        <v>-8.17999999999995</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -15304,11 +15304,11 @@
         <v>529.76</v>
       </c>
       <c r="C486" s="4">
-        <v>528.75</v>
+        <v>520.73</v>
       </c>
       <c r="D486" s="4"/>
       <c r="E486" s="4">
-        <v>-1.009999999999991</v>
+        <v>-9.029999999999973</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -15319,11 +15319,11 @@
         <v>529.3</v>
       </c>
       <c r="C487" s="4">
-        <v>528.52</v>
+        <v>520.53</v>
       </c>
       <c r="D487" s="4"/>
       <c r="E487" s="4">
-        <v>-0.7799999999999727</v>
+        <v>-8.769999999999982</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -15331,14 +15331,14 @@
         <v>46281.46527777778</v>
       </c>
       <c r="B488" s="4">
-        <v>536.4</v>
+        <v>537</v>
       </c>
       <c r="C488" s="4">
-        <v>528.36</v>
+        <v>520.35</v>
       </c>
       <c r="D488" s="4"/>
       <c r="E488" s="4">
-        <v>-8.039999999999964</v>
+        <v>-16.64999999999998</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -15349,11 +15349,11 @@
         <v>553.5700000000001</v>
       </c>
       <c r="C489" s="4">
-        <v>528.21</v>
+        <v>520.14</v>
       </c>
       <c r="D489" s="4"/>
       <c r="E489" s="4">
-        <v>-25.36000000000001</v>
+        <v>-33.43000000000006</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -15361,14 +15361,14 @@
         <v>46281.46944444445</v>
       </c>
       <c r="B490" s="4">
-        <v>535.04</v>
+        <v>537.9</v>
       </c>
       <c r="C490" s="4">
-        <v>528.09</v>
+        <v>519.9400000000001</v>
       </c>
       <c r="D490" s="4"/>
       <c r="E490" s="4">
-        <v>-6.949999999999932</v>
+        <v>-17.95999999999992</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -15379,11 +15379,11 @@
         <v>538.77</v>
       </c>
       <c r="C491" s="4">
-        <v>527.98</v>
+        <v>519.9</v>
       </c>
       <c r="D491" s="4"/>
       <c r="E491" s="4">
-        <v>-10.78999999999996</v>
+        <v>-18.87</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -15391,14 +15391,14 @@
         <v>46281.47361111111</v>
       </c>
       <c r="B492" s="4">
-        <v>538.5</v>
+        <v>534.74</v>
       </c>
       <c r="C492" s="4">
-        <v>527.85</v>
+        <v>519.73</v>
       </c>
       <c r="D492" s="4"/>
       <c r="E492" s="4">
-        <v>-10.64999999999998</v>
+        <v>-15.00999999999999</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -15406,14 +15406,14 @@
         <v>46281.47569444445</v>
       </c>
       <c r="B493" s="4">
-        <v>540.3</v>
+        <v>539.33</v>
       </c>
       <c r="C493" s="4">
-        <v>527.6799999999999</v>
+        <v>519.71</v>
       </c>
       <c r="D493" s="4"/>
       <c r="E493" s="4">
-        <v>-12.62</v>
+        <v>-19.62</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -15424,11 +15424,11 @@
         <v>534.1799999999999</v>
       </c>
       <c r="C494" s="4">
-        <v>527.58</v>
+        <v>519.54</v>
       </c>
       <c r="D494" s="4"/>
       <c r="E494" s="4">
-        <v>-6.599999999999909</v>
+        <v>-14.63999999999999</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -15436,14 +15436,14 @@
         <v>46281.47986111111</v>
       </c>
       <c r="B495" s="4">
-        <v>531.6</v>
+        <v>550.78</v>
       </c>
       <c r="C495" s="4">
-        <v>527.42</v>
+        <v>519.35</v>
       </c>
       <c r="D495" s="4"/>
       <c r="E495" s="4">
-        <v>-4.180000000000064</v>
+        <v>-31.42999999999995</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -15454,11 +15454,11 @@
         <v>540.48</v>
       </c>
       <c r="C496" s="4">
-        <v>527.14</v>
+        <v>519.12</v>
       </c>
       <c r="D496" s="4"/>
       <c r="E496" s="4">
-        <v>-13.34000000000003</v>
+        <v>-21.36000000000001</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -15466,14 +15466,14 @@
         <v>46281.48402777778</v>
       </c>
       <c r="B497" s="4">
-        <v>530.7</v>
+        <v>561.4400000000001</v>
       </c>
       <c r="C497" s="4">
-        <v>526.87</v>
+        <v>518.78</v>
       </c>
       <c r="D497" s="4"/>
       <c r="E497" s="4">
-        <v>-3.830000000000041</v>
+        <v>-42.66000000000008</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -15484,11 +15484,11 @@
         <v>528.47</v>
       </c>
       <c r="C498" s="4">
-        <v>526.67</v>
+        <v>518.6</v>
       </c>
       <c r="D498" s="4"/>
       <c r="E498" s="4">
-        <v>-1.800000000000068</v>
+        <v>-9.870000000000005</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -15496,14 +15496,14 @@
         <v>46281.48819444444</v>
       </c>
       <c r="B499" s="4">
-        <v>471.1</v>
+        <v>534.4</v>
       </c>
       <c r="C499" s="4">
-        <v>526.3</v>
+        <v>518.42</v>
       </c>
       <c r="D499" s="4"/>
       <c r="E499" s="4">
-        <v>55.19999999999993</v>
+        <v>-15.98000000000002</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -15514,11 +15514,11 @@
         <v>570.34</v>
       </c>
       <c r="C500" s="4">
-        <v>526.11</v>
+        <v>518.22</v>
       </c>
       <c r="D500" s="4"/>
       <c r="E500" s="4">
-        <v>-44.23000000000002</v>
+        <v>-52.12</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -15529,11 +15529,11 @@
         <v>558.75</v>
       </c>
       <c r="C501" s="4">
-        <v>526.02</v>
+        <v>518.08</v>
       </c>
       <c r="D501" s="4"/>
       <c r="E501" s="4">
-        <v>-32.73000000000002</v>
+        <v>-40.66999999999996</v>
       </c>
     </row>
     <row r="502" spans="1:5">
@@ -15544,11 +15544,11 @@
         <v>530.6</v>
       </c>
       <c r="C502" s="4">
-        <v>525.98</v>
+        <v>517.99</v>
       </c>
       <c r="D502" s="4"/>
       <c r="E502" s="4">
-        <v>-4.620000000000005</v>
+        <v>-12.61000000000001</v>
       </c>
     </row>
     <row r="503" spans="1:5">
@@ -15559,11 +15559,11 @@
         <v>528.24</v>
       </c>
       <c r="C503" s="4">
-        <v>525.89</v>
+        <v>517.89</v>
       </c>
       <c r="D503" s="4"/>
       <c r="E503" s="4">
-        <v>-2.350000000000023</v>
+        <v>-10.35000000000002</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -15574,11 +15574,11 @@
         <v>532.9</v>
       </c>
       <c r="C504" s="4">
-        <v>525.71</v>
+        <v>517.67</v>
       </c>
       <c r="D504" s="4"/>
       <c r="E504" s="4">
-        <v>-7.189999999999941</v>
+        <v>-15.23000000000002</v>
       </c>
     </row>
     <row r="505" spans="1:5">
@@ -15586,14 +15586,14 @@
         <v>46281.50069444445</v>
       </c>
       <c r="B505" s="4">
-        <v>536.1</v>
+        <v>528.67</v>
       </c>
       <c r="C505" s="4">
-        <v>525.45</v>
+        <v>517.5</v>
       </c>
       <c r="D505" s="4"/>
       <c r="E505" s="4">
-        <v>-10.64999999999998</v>
+        <v>-11.16999999999996</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -15604,11 +15604,11 @@
         <v>516.83</v>
       </c>
       <c r="C506" s="4">
-        <v>524.95</v>
+        <v>517.04</v>
       </c>
       <c r="D506" s="4"/>
       <c r="E506" s="4">
-        <v>8.120000000000005</v>
+        <v>0.2099999999999227</v>
       </c>
     </row>
     <row r="507" spans="1:5">
@@ -15616,14 +15616,14 @@
         <v>46281.50486111111</v>
       </c>
       <c r="B507" s="4">
-        <v>531.3</v>
+        <v>513.8</v>
       </c>
       <c r="C507" s="4">
-        <v>524.63</v>
+        <v>516.49</v>
       </c>
       <c r="D507" s="4"/>
       <c r="E507" s="4">
-        <v>-6.669999999999959</v>
+        <v>2.690000000000055</v>
       </c>
     </row>
     <row r="508" spans="1:5">
@@ -15634,11 +15634,11 @@
         <v>534.4</v>
       </c>
       <c r="C508" s="4">
-        <v>524.28</v>
+        <v>516.13</v>
       </c>
       <c r="D508" s="4"/>
       <c r="E508" s="4">
-        <v>-10.12</v>
+        <v>-18.26999999999998</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -15646,14 +15646,14 @@
         <v>46281.50902777778</v>
       </c>
       <c r="B509" s="4">
-        <v>565.1</v>
+        <v>510.5</v>
       </c>
       <c r="C509" s="4">
-        <v>524.0599999999999</v>
+        <v>515.72</v>
       </c>
       <c r="D509" s="4"/>
       <c r="E509" s="4">
-        <v>-41.04000000000008</v>
+        <v>5.220000000000027</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -15664,11 +15664,11 @@
         <v>535.29</v>
       </c>
       <c r="C510" s="4">
-        <v>523.64</v>
+        <v>515.39</v>
       </c>
       <c r="D510" s="4"/>
       <c r="E510" s="4">
-        <v>-11.64999999999998</v>
+        <v>-19.89999999999998</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -15679,11 +15679,11 @@
         <v>532.52</v>
       </c>
       <c r="C511" s="4">
-        <v>523.54</v>
+        <v>515.03</v>
       </c>
       <c r="D511" s="4"/>
       <c r="E511" s="4">
-        <v>-8.980000000000018</v>
+        <v>-17.49000000000001</v>
       </c>
     </row>
     <row r="512" spans="1:5">
@@ -15691,14 +15691,14 @@
         <v>46281.51527777778</v>
       </c>
       <c r="B512" s="4">
-        <v>550.5</v>
+        <v>534.91</v>
       </c>
       <c r="C512" s="4">
-        <v>523.26</v>
+        <v>514.78</v>
       </c>
       <c r="D512" s="4"/>
       <c r="E512" s="4">
-        <v>-27.24000000000001</v>
+        <v>-20.13</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -15706,14 +15706,14 @@
         <v>46281.51736111111</v>
       </c>
       <c r="B513" s="4">
-        <v>545.2</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="C513" s="4">
-        <v>522.95</v>
+        <v>514.45</v>
       </c>
       <c r="D513" s="4"/>
       <c r="E513" s="4">
-        <v>-22.25</v>
+        <v>-78.6099999999999</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -15724,11 +15724,11 @@
         <v>554.28</v>
       </c>
       <c r="C514" s="4">
-        <v>522.71</v>
+        <v>514.1</v>
       </c>
       <c r="D514" s="4"/>
       <c r="E514" s="4">
-        <v>-31.56999999999994</v>
+        <v>-40.17999999999995</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -15736,14 +15736,14 @@
         <v>46281.52152777778</v>
       </c>
       <c r="B515" s="4">
-        <v>548.99</v>
+        <v>537.7</v>
       </c>
       <c r="C515" s="4">
-        <v>522.55</v>
+        <v>514.02</v>
       </c>
       <c r="D515" s="4"/>
       <c r="E515" s="4">
-        <v>-26.44000000000005</v>
+        <v>-23.68000000000006</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -15754,11 +15754,11 @@
         <v>549.54</v>
       </c>
       <c r="C516" s="4">
-        <v>522.47</v>
+        <v>514.02</v>
       </c>
       <c r="D516" s="4"/>
       <c r="E516" s="4">
-        <v>-27.06999999999994</v>
+        <v>-35.51999999999998</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -15769,11 +15769,11 @@
         <v>546.6900000000001</v>
       </c>
       <c r="C517" s="4">
-        <v>522.34</v>
+        <v>514.02</v>
       </c>
       <c r="D517" s="4"/>
       <c r="E517" s="4">
-        <v>-24.35000000000002</v>
+        <v>-32.67000000000007</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -15784,11 +15784,11 @@
         <v>533.6900000000001</v>
       </c>
       <c r="C518" s="4">
-        <v>522.37</v>
+        <v>514.02</v>
       </c>
       <c r="D518" s="4"/>
       <c r="E518" s="4">
-        <v>-11.32000000000005</v>
+        <v>-19.67000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -15841,13 +15841,13 @@
         <v>1.62</v>
       </c>
       <c r="C2" s="4">
-        <v>-11.44</v>
+        <v>-11.59</v>
       </c>
       <c r="D2" s="4">
-        <v>12.04</v>
+        <v>12.02</v>
       </c>
       <c r="E2" s="4">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>92</v>
@@ -15864,13 +15864,13 @@
         <v>1.49</v>
       </c>
       <c r="C3" s="4">
-        <v>-10.46</v>
+        <v>-10.62</v>
       </c>
       <c r="D3" s="4">
-        <v>11.11</v>
+        <v>11.09</v>
       </c>
       <c r="E3" s="4">
-        <v>78.8</v>
+        <v>80.3</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>92</v>
@@ -15887,13 +15887,13 @@
         <v>1.37</v>
       </c>
       <c r="C4" s="4">
-        <v>-10.62</v>
+        <v>-10.78</v>
       </c>
       <c r="D4" s="4">
-        <v>11.3</v>
+        <v>11.28</v>
       </c>
       <c r="E4" s="4">
-        <v>83.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>92</v>
@@ -15910,13 +15910,13 @@
         <v>1.26</v>
       </c>
       <c r="C5" s="4">
-        <v>-11.47</v>
+        <v>-11.63</v>
       </c>
       <c r="D5" s="4">
-        <v>12.11</v>
+        <v>12.08</v>
       </c>
       <c r="E5" s="4">
-        <v>86.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>92</v>
@@ -15933,13 +15933,13 @@
         <v>1.16</v>
       </c>
       <c r="C6" s="4">
-        <v>-11</v>
+        <v>-11.16</v>
       </c>
       <c r="D6" s="4">
-        <v>11.67</v>
+        <v>11.65</v>
       </c>
       <c r="E6" s="4">
-        <v>84.5</v>
+        <v>87</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>92</v>
@@ -15956,13 +15956,13 @@
         <v>1.07</v>
       </c>
       <c r="C7" s="4">
-        <v>-11.75</v>
+        <v>-11.91</v>
       </c>
       <c r="D7" s="4">
-        <v>12.25</v>
+        <v>12.23</v>
       </c>
       <c r="E7" s="4">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>92</v>
@@ -15979,13 +15979,13 @@
         <v>0.98</v>
       </c>
       <c r="C8" s="4">
-        <v>-12.07</v>
+        <v>-12.23</v>
       </c>
       <c r="D8" s="4">
-        <v>12.48</v>
+        <v>12.46</v>
       </c>
       <c r="E8" s="4">
-        <v>88.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>92</v>
@@ -16002,13 +16002,13 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="4">
-        <v>-12.21</v>
+        <v>-12.37</v>
       </c>
       <c r="D9" s="4">
-        <v>12.51</v>
+        <v>12.49</v>
       </c>
       <c r="E9" s="4">
-        <v>88.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>92</v>
@@ -16025,13 +16025,13 @@
         <v>0.83</v>
       </c>
       <c r="C10" s="4">
-        <v>-12.22</v>
+        <v>-12.38</v>
       </c>
       <c r="D10" s="4">
-        <v>12.39</v>
+        <v>12.37</v>
       </c>
       <c r="E10" s="4">
-        <v>88.8</v>
+        <v>91.3</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>92</v>
@@ -16048,13 +16048,13 @@
         <v>0.76</v>
       </c>
       <c r="C11" s="4">
-        <v>-11.19</v>
+        <v>-11.34</v>
       </c>
       <c r="D11" s="4">
-        <v>11.31</v>
+        <v>11.28</v>
       </c>
       <c r="E11" s="4">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>92</v>
@@ -16071,13 +16071,13 @@
         <v>0.7</v>
       </c>
       <c r="C12" s="4">
-        <v>-9.33</v>
+        <v>-9.49</v>
       </c>
       <c r="D12" s="4">
-        <v>9.51</v>
+        <v>9.49</v>
       </c>
       <c r="E12" s="4">
-        <v>73</v>
+        <v>74.5</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>97</v>
@@ -16094,13 +16094,13 @@
         <v>0.65</v>
       </c>
       <c r="C13" s="4">
-        <v>-7.43</v>
+        <v>-7.58</v>
       </c>
       <c r="D13" s="4">
-        <v>7.69</v>
+        <v>7.67</v>
       </c>
       <c r="E13" s="4">
-        <v>58.9</v>
+        <v>60.3</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>97</v>
@@ -16117,13 +16117,13 @@
         <v>0.59</v>
       </c>
       <c r="C14" s="4">
-        <v>-6.01</v>
+        <v>-6.17</v>
       </c>
       <c r="D14" s="4">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="E14" s="4">
-        <v>48</v>
+        <v>49.4</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>98</v>
@@ -16140,13 +16140,13 @@
         <v>0.55</v>
       </c>
       <c r="C15" s="4">
-        <v>-5.93</v>
+        <v>-6.08</v>
       </c>
       <c r="D15" s="4">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="E15" s="4">
-        <v>44.6</v>
+        <v>46.9</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>98</v>
@@ -16163,13 +16163,13 @@
         <v>0.5</v>
       </c>
       <c r="C16" s="4">
-        <v>-7.33</v>
+        <v>-7.49</v>
       </c>
       <c r="D16" s="4">
         <v>7.34</v>
       </c>
       <c r="E16" s="4">
-        <v>50.4</v>
+        <v>52.9</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>98</v>
@@ -16186,13 +16186,13 @@
         <v>0.46</v>
       </c>
       <c r="C17" s="4">
-        <v>-9.220000000000001</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="D17" s="4">
         <v>8.949999999999999</v>
       </c>
       <c r="E17" s="4">
-        <v>58.5</v>
+        <v>61.1</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>97</v>
@@ -16209,13 +16209,13 @@
         <v>0.43</v>
       </c>
       <c r="C18" s="4">
-        <v>-11.1</v>
+        <v>-11.25</v>
       </c>
       <c r="D18" s="4">
-        <v>10.63</v>
+        <v>10.6</v>
       </c>
       <c r="E18" s="4">
-        <v>69.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>97</v>
@@ -16232,13 +16232,13 @@
         <v>0.39</v>
       </c>
       <c r="C19" s="4">
-        <v>-12.24</v>
+        <v>-12.39</v>
       </c>
       <c r="D19" s="4">
-        <v>11.73</v>
+        <v>11.71</v>
       </c>
       <c r="E19" s="4">
-        <v>81.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>92</v>
@@ -16255,13 +16255,13 @@
         <v>0.36</v>
       </c>
       <c r="C20" s="4">
-        <v>-12.12</v>
+        <v>-12.27</v>
       </c>
       <c r="D20" s="4">
-        <v>11.62</v>
+        <v>11.6</v>
       </c>
       <c r="E20" s="4">
-        <v>81.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>92</v>
@@ -16278,13 +16278,13 @@
         <v>0.33</v>
       </c>
       <c r="C21" s="4">
-        <v>-10.81</v>
+        <v>-10.97</v>
       </c>
       <c r="D21" s="4">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="E21" s="4">
-        <v>72</v>
+        <v>73.5</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>97</v>
@@ -16301,13 +16301,13 @@
         <v>0.32</v>
       </c>
       <c r="C22" s="4">
-        <v>-8.92</v>
+        <v>-9.08</v>
       </c>
       <c r="D22" s="4">
-        <v>8.630000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E22" s="4">
-        <v>59.4</v>
+        <v>60.8</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>97</v>
@@ -16324,13 +16324,13 @@
         <v>0.32</v>
       </c>
       <c r="C23" s="4">
-        <v>-7.16</v>
+        <v>-7.31</v>
       </c>
       <c r="D23" s="4">
         <v>7.04</v>
       </c>
       <c r="E23" s="4">
-        <v>49.1</v>
+        <v>51.6</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>98</v>
@@ -16347,13 +16347,13 @@
         <v>0.32</v>
       </c>
       <c r="C24" s="4">
-        <v>-5.93</v>
+        <v>-6.08</v>
       </c>
       <c r="D24" s="4">
         <v>5.96</v>
       </c>
       <c r="E24" s="4">
-        <v>43.7</v>
+        <v>46.2</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>98</v>
@@ -16370,13 +16370,13 @@
         <v>0.32</v>
       </c>
       <c r="C25" s="4">
-        <v>-5.25</v>
+        <v>-5.41</v>
       </c>
       <c r="D25" s="4">
         <v>5.37</v>
       </c>
       <c r="E25" s="4">
-        <v>40.7</v>
+        <v>43.3</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>98</v>
@@ -16393,13 +16393,13 @@
         <v>0.32</v>
       </c>
       <c r="C26" s="4">
-        <v>-4.96</v>
+        <v>-5.11</v>
       </c>
       <c r="D26" s="4">
         <v>5.11</v>
       </c>
       <c r="E26" s="4">
-        <v>39.4</v>
+        <v>42</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>98</v>

--- a/docs/reports/swift_space_weather_2026-09.xlsx
+++ b/docs/reports/swift_space_weather_2026-09.xlsx
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-16T23:40:05Z</t>
+    <t>2026-09-16T23:41:39Z</t>
   </si>
   <si>
     <t>Workbook</t>
@@ -315,10 +315,10 @@
     <t>MODERATE</t>
   </si>
   <si>
+    <t>LOW-MODERATE</t>
+  </si>
+  <si>
     <t>2026-09-13T10:23:00-CME-001</t>
-  </si>
-  <si>
-    <t>LOW-MODERATE</t>
   </si>
   <si>
     <t>2026-09-15T08:36:00-CME-001</t>
@@ -1209,7 +1209,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.8</c:v>
+                  <c:v>45.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2520,232 +2520,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>688.0599999999999</c:v>
+                  <c:v>649.6799999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>700.55</c:v>
+                  <c:v>662.48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>706.92</c:v>
+                  <c:v>669</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>706</c:v>
+                  <c:v>668.0599999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>706.35</c:v>
+                  <c:v>668.4299999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>704.88</c:v>
+                  <c:v>666.9400000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>703.21</c:v>
+                  <c:v>665.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>701.36</c:v>
+                  <c:v>663.35</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>697.01</c:v>
+                  <c:v>658.89</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>695.23</c:v>
+                  <c:v>657.08</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>695.05</c:v>
+                  <c:v>656.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>695.3099999999999</c:v>
+                  <c:v>657.17</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>691.13</c:v>
+                  <c:v>652.88</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>688.41</c:v>
+                  <c:v>650.09</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>684.65</c:v>
+                  <c:v>646.24</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>678.84</c:v>
+                  <c:v>640.3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>671.08</c:v>
+                  <c:v>632.33</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>660.34</c:v>
+                  <c:v>621.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>648.16</c:v>
+                  <c:v>608.83</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>635.4400000000001</c:v>
+                  <c:v>595.79</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>622.72</c:v>
+                  <c:v>582.75</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>610.3200000000001</c:v>
+                  <c:v>570.03</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>598.41</c:v>
+                  <c:v>557.8200000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>586.96</c:v>
+                  <c:v>546.09</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>574.8099999999999</c:v>
+                  <c:v>533.63</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>563.79</c:v>
+                  <c:v>522.34</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>553.7</c:v>
+                  <c:v>511.99</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>544.39</c:v>
+                  <c:v>502.45</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>535.78</c:v>
+                  <c:v>493.62</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>527.24</c:v>
+                  <c:v>484.87</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>520.48</c:v>
+                  <c:v>477.94</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>515.04</c:v>
+                  <c:v>472.35</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>510.68</c:v>
+                  <c:v>467.89</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>507.37</c:v>
+                  <c:v>464.49</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>505.22</c:v>
+                  <c:v>462.29</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>503.67</c:v>
+                  <c:v>460.7</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>503.48</c:v>
+                  <c:v>460.5</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>505.4</c:v>
+                  <c:v>462.47</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>510.11</c:v>
+                  <c:v>467.3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>513.0700000000001</c:v>
+                  <c:v>470.33</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>521.6</c:v>
+                  <c:v>479.08</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>532.5</c:v>
+                  <c:v>490.24</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>546.8200000000001</c:v>
+                  <c:v>504.92</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>562.2</c:v>
+                  <c:v>520.6900000000001</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>576.16</c:v>
+                  <c:v>535</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>586.39</c:v>
+                  <c:v>545.47</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>589.01</c:v>
+                  <c:v>548.16</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>584.76</c:v>
+                  <c:v>543.8</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>578.37</c:v>
+                  <c:v>537.26</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>570.9</c:v>
+                  <c:v>529.6</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>561.04</c:v>
+                  <c:v>519.49</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>551.98</c:v>
+                  <c:v>510.2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>543.59</c:v>
+                  <c:v>501.6</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>533.91</c:v>
+                  <c:v>491.68</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>525.67</c:v>
+                  <c:v>483.24</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>518.48</c:v>
+                  <c:v>475.86</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>512.0599999999999</c:v>
+                  <c:v>469.29</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>506.26</c:v>
+                  <c:v>463.34</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>500.95</c:v>
+                  <c:v>457.89</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>496.06</c:v>
+                  <c:v>452.88</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>491.54</c:v>
+                  <c:v>448.24</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>487.33</c:v>
+                  <c:v>443.94</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>483.42</c:v>
+                  <c:v>439.93</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>479.77</c:v>
+                  <c:v>436.19</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>476.37</c:v>
+                  <c:v>432.7</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>473.19</c:v>
+                  <c:v>429.44</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>470.22</c:v>
+                  <c:v>426.39</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>467.44</c:v>
+                  <c:v>423.55</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>464.85</c:v>
+                  <c:v>420.89</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>462.42</c:v>
+                  <c:v>418.4</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>460.16</c:v>
+                  <c:v>416.08</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>458.04</c:v>
+                  <c:v>413.91</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>456.06</c:v>
+                  <c:v>411.87</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>454.2</c:v>
+                  <c:v>409.97</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>452.47</c:v>
+                  <c:v>408.2</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>450.85</c:v>
+                  <c:v>406.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3004,232 +3004,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>427.34</c:v>
+                  <c:v>382.44</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>421.91</c:v>
+                  <c:v>376.87</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>416.27</c:v>
+                  <c:v>371.09</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>416.01</c:v>
+                  <c:v>370.82</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>417.06</c:v>
+                  <c:v>371.91</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>416.72</c:v>
+                  <c:v>371.58</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>416.65</c:v>
+                  <c:v>371.52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>415.46</c:v>
+                  <c:v>370.3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>415.76</c:v>
+                  <c:v>370.61</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>414.85</c:v>
+                  <c:v>369.69</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>413.3</c:v>
+                  <c:v>368.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>412.23</c:v>
+                  <c:v>367.01</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>411.49</c:v>
+                  <c:v>366.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>410.98</c:v>
+                  <c:v>365.73</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>410.63</c:v>
+                  <c:v>365.38</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>410.41</c:v>
+                  <c:v>365.15</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>410.38</c:v>
+                  <c:v>365.12</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>410.53</c:v>
+                  <c:v>365.26</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>410.78</c:v>
+                  <c:v>365.51</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>411.08</c:v>
+                  <c:v>365.82</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>411.42</c:v>
+                  <c:v>366.16</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>411.77</c:v>
+                  <c:v>366.52</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>412.12</c:v>
+                  <c:v>366.88</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>412.35</c:v>
+                  <c:v>367.11</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>412.5</c:v>
+                  <c:v>367.27</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>412.6</c:v>
+                  <c:v>367.37</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>412.67</c:v>
+                  <c:v>367.43</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>412.7</c:v>
+                  <c:v>367.47</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>412.72</c:v>
+                  <c:v>367.48</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>413.61</c:v>
+                  <c:v>368.39</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>415.04</c:v>
+                  <c:v>369.85</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>416.79</c:v>
+                  <c:v>371.65</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>418.75</c:v>
+                  <c:v>373.66</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>420.83</c:v>
+                  <c:v>375.79</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>422.98</c:v>
+                  <c:v>378</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>424.32</c:v>
+                  <c:v>379.36</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>425.14</c:v>
+                  <c:v>380.2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>425.64</c:v>
+                  <c:v>380.72</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>425.94</c:v>
+                  <c:v>381.03</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>426.12</c:v>
+                  <c:v>381.21</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>426.21</c:v>
+                  <c:v>381.3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>426.26</c:v>
+                  <c:v>381.34</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>426.27</c:v>
+                  <c:v>381.36</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>426.26</c:v>
+                  <c:v>381.34</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>426.23</c:v>
+                  <c:v>381.31</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>426.19</c:v>
+                  <c:v>381.27</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>426.14</c:v>
+                  <c:v>381.22</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>426.08</c:v>
+                  <c:v>381.16</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>426.02</c:v>
+                  <c:v>381.09</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>425.95</c:v>
+                  <c:v>381.02</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>425.87</c:v>
+                  <c:v>380.94</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>425.79</c:v>
+                  <c:v>380.86</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>425.7</c:v>
+                  <c:v>380.77</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>425.68</c:v>
+                  <c:v>380.75</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>425.7</c:v>
+                  <c:v>380.77</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>425.74</c:v>
+                  <c:v>380.81</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>425.8</c:v>
+                  <c:v>380.87</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>425.86</c:v>
+                  <c:v>380.93</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>425.93</c:v>
+                  <c:v>381</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>425.99</c:v>
+                  <c:v>381.06</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>426.06</c:v>
+                  <c:v>381.13</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>426.12</c:v>
+                  <c:v>381.2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>426.19</c:v>
+                  <c:v>381.26</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>426.25</c:v>
+                  <c:v>381.32</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>426.31</c:v>
+                  <c:v>381.38</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>426.36</c:v>
+                  <c:v>381.44</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>426.42</c:v>
+                  <c:v>381.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>426.47</c:v>
+                  <c:v>381.55</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>426.52</c:v>
+                  <c:v>381.6</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>426.57</c:v>
+                  <c:v>381.65</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>426.61</c:v>
+                  <c:v>381.7</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>426.66</c:v>
+                  <c:v>381.74</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>426.7</c:v>
+                  <c:v>381.78</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>426.74</c:v>
+                  <c:v>381.82</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>426.78</c:v>
+                  <c:v>381.86</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>426.82</c:v>
+                  <c:v>381.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4383,79 +4383,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-8.44</c:v>
+                  <c:v>-8.23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7.83</c:v>
+                  <c:v>-7.63</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.06</c:v>
+                  <c:v>-8.85</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-8.869999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>-9.07</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>-9.279999999999999</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>-9.140000000000001</c:v>
+                  <c:v>-8.93</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7.77</c:v>
+                  <c:v>-7.56</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-5.84</c:v>
+                  <c:v>-5.63</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.08</c:v>
+                  <c:v>-3.87</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-3.16</c:v>
+                  <c:v>-2.95</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-3.56</c:v>
+                  <c:v>-3.35</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-5.16</c:v>
+                  <c:v>-4.96</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-7.13</c:v>
+                  <c:v>-6.93</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-8.859999999999999</c:v>
+                  <c:v>-8.65</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-9.630000000000001</c:v>
+                  <c:v>-9.42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-9.08</c:v>
+                  <c:v>-8.880000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-7.51</c:v>
+                  <c:v>-7.31</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-5.62</c:v>
+                  <c:v>-5.42</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-4.05</c:v>
+                  <c:v>-3.84</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3.05</c:v>
+                  <c:v>-2.84</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2.75</c:v>
+                  <c:v>-2.54</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-2.64</c:v>
+                  <c:v>-2.44</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-2.61</c:v>
+                  <c:v>-2.4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-2.59</c:v>
+                  <c:v>-2.39</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.59</c:v>
+                  <c:v>-2.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4561,76 +4561,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>12.33</c:v>
+                  <c:v>12.22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.68</c:v>
+                  <c:v>11.57</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.62</c:v>
+                  <c:v>12.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.53</c:v>
+                  <c:v>12.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.58</c:v>
+                  <c:v>12.47</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.29</c:v>
+                  <c:v>12.17</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.91</c:v>
+                  <c:v>10.79</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.039999999999999</c:v>
+                  <c:v>8.93</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.35</c:v>
+                  <c:v>7.23</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.18</c:v>
+                  <c:v>6.06</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.68</c:v>
+                  <c:v>6.55</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.02</c:v>
+                  <c:v>7.9</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.73</c:v>
+                  <c:v>9.6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11.29</c:v>
+                  <c:v>11.17</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12.04</c:v>
+                  <c:v>11.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11.5</c:v>
+                  <c:v>11.38</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.02</c:v>
+                  <c:v>9.9</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.26</c:v>
+                  <c:v>8.140000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.8</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.85</c:v>
+                  <c:v>5.73</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.36</c:v>
+                  <c:v>5.27</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.14</c:v>
+                  <c:v>5.09</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.06</c:v>
+                  <c:v>5.02</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.02</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>5</c:v>
@@ -5661,7 +5661,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="4">
-        <v>3.8</v>
+        <v>45.6</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>30</v>
@@ -5690,7 +5690,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>110.34</v>
+        <v>70.84</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="4">
-        <v>110.34</v>
+        <v>70.64</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>15</v>
@@ -5748,7 +5748,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="4">
-        <v>8.300000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>30</v>
@@ -5812,10 +5812,10 @@
         <v>500</v>
       </c>
       <c r="L24" s="4">
-        <v>3.8</v>
+        <v>45.6</v>
       </c>
       <c r="M24" s="4">
-        <v>110.3</v>
+        <v>70.8</v>
       </c>
       <c r="N24" s="4">
         <v>12</v>
@@ -6540,10 +6540,10 @@
         <v>46281.83333333334</v>
       </c>
       <c r="B2" s="4">
-        <v>688.0599999999999</v>
+        <v>649.6799999999999</v>
       </c>
       <c r="C2" s="4">
-        <v>427.34</v>
+        <v>382.44</v>
       </c>
       <c r="D2" s="4">
         <v>505.04</v>
@@ -6561,10 +6561,10 @@
         <v>46281.875</v>
       </c>
       <c r="B3" s="4">
-        <v>700.55</v>
+        <v>662.48</v>
       </c>
       <c r="C3" s="4">
-        <v>421.91</v>
+        <v>376.87</v>
       </c>
       <c r="D3" s="4">
         <v>505.98</v>
@@ -6582,10 +6582,10 @@
         <v>46281.91666666666</v>
       </c>
       <c r="B4" s="4">
-        <v>706.92</v>
+        <v>669</v>
       </c>
       <c r="C4" s="4">
-        <v>416.27</v>
+        <v>371.09</v>
       </c>
       <c r="D4" s="4">
         <v>506.87</v>
@@ -6603,10 +6603,10 @@
         <v>46281.95833333334</v>
       </c>
       <c r="B5" s="4">
-        <v>706</v>
+        <v>668.0599999999999</v>
       </c>
       <c r="C5" s="4">
-        <v>416.01</v>
+        <v>370.82</v>
       </c>
       <c r="D5" s="4">
         <v>512.47</v>
@@ -6624,10 +6624,10 @@
         <v>46282</v>
       </c>
       <c r="B6" s="4">
-        <v>706.35</v>
+        <v>668.4299999999999</v>
       </c>
       <c r="C6" s="4">
-        <v>417.06</v>
+        <v>371.91</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -6643,10 +6643,10 @@
         <v>46282.04166666666</v>
       </c>
       <c r="B7" s="4">
-        <v>704.88</v>
+        <v>666.9400000000001</v>
       </c>
       <c r="C7" s="4">
-        <v>416.72</v>
+        <v>371.58</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4">
@@ -6662,10 +6662,10 @@
         <v>46282.08333333334</v>
       </c>
       <c r="B8" s="4">
-        <v>703.21</v>
+        <v>665.24</v>
       </c>
       <c r="C8" s="4">
-        <v>416.65</v>
+        <v>371.52</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4">
@@ -6681,10 +6681,10 @@
         <v>46282.125</v>
       </c>
       <c r="B9" s="4">
-        <v>701.36</v>
+        <v>663.35</v>
       </c>
       <c r="C9" s="4">
-        <v>415.46</v>
+        <v>370.3</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4">
@@ -6700,10 +6700,10 @@
         <v>46282.16666666666</v>
       </c>
       <c r="B10" s="4">
-        <v>697.01</v>
+        <v>658.89</v>
       </c>
       <c r="C10" s="4">
-        <v>415.76</v>
+        <v>370.61</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4">
@@ -6719,10 +6719,10 @@
         <v>46282.20833333334</v>
       </c>
       <c r="B11" s="4">
-        <v>695.23</v>
+        <v>657.08</v>
       </c>
       <c r="C11" s="4">
-        <v>414.85</v>
+        <v>369.69</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4">
@@ -6738,10 +6738,10 @@
         <v>46282.25</v>
       </c>
       <c r="B12" s="4">
-        <v>695.05</v>
+        <v>656.9</v>
       </c>
       <c r="C12" s="4">
-        <v>413.3</v>
+        <v>368.1</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4">
@@ -6757,10 +6757,10 @@
         <v>46282.29166666666</v>
       </c>
       <c r="B13" s="4">
-        <v>695.3099999999999</v>
+        <v>657.17</v>
       </c>
       <c r="C13" s="4">
-        <v>412.23</v>
+        <v>367.01</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4">
@@ -6776,10 +6776,10 @@
         <v>46282.33333333334</v>
       </c>
       <c r="B14" s="4">
-        <v>691.13</v>
+        <v>652.88</v>
       </c>
       <c r="C14" s="4">
-        <v>411.49</v>
+        <v>366.25</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4">
@@ -6795,10 +6795,10 @@
         <v>46282.375</v>
       </c>
       <c r="B15" s="4">
-        <v>688.41</v>
+        <v>650.09</v>
       </c>
       <c r="C15" s="4">
-        <v>410.98</v>
+        <v>365.73</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4">
@@ -6814,10 +6814,10 @@
         <v>46282.41666666666</v>
       </c>
       <c r="B16" s="4">
-        <v>684.65</v>
+        <v>646.24</v>
       </c>
       <c r="C16" s="4">
-        <v>410.63</v>
+        <v>365.38</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4">
@@ -6833,10 +6833,10 @@
         <v>46282.45833333334</v>
       </c>
       <c r="B17" s="4">
-        <v>678.84</v>
+        <v>640.3</v>
       </c>
       <c r="C17" s="4">
-        <v>410.41</v>
+        <v>365.15</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4">
@@ -6852,10 +6852,10 @@
         <v>46282.5</v>
       </c>
       <c r="B18" s="4">
-        <v>671.08</v>
+        <v>632.33</v>
       </c>
       <c r="C18" s="4">
-        <v>410.38</v>
+        <v>365.12</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4">
@@ -6871,10 +6871,10 @@
         <v>46282.54166666666</v>
       </c>
       <c r="B19" s="4">
-        <v>660.34</v>
+        <v>621.3200000000001</v>
       </c>
       <c r="C19" s="4">
-        <v>410.53</v>
+        <v>365.26</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4">
@@ -6890,10 +6890,10 @@
         <v>46282.58333333334</v>
       </c>
       <c r="B20" s="4">
-        <v>648.16</v>
+        <v>608.83</v>
       </c>
       <c r="C20" s="4">
-        <v>410.78</v>
+        <v>365.51</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4">
@@ -6909,10 +6909,10 @@
         <v>46282.625</v>
       </c>
       <c r="B21" s="4">
-        <v>635.4400000000001</v>
+        <v>595.79</v>
       </c>
       <c r="C21" s="4">
-        <v>411.08</v>
+        <v>365.82</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4">
@@ -6928,10 +6928,10 @@
         <v>46282.66666666666</v>
       </c>
       <c r="B22" s="4">
-        <v>622.72</v>
+        <v>582.75</v>
       </c>
       <c r="C22" s="4">
-        <v>411.42</v>
+        <v>366.16</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4">
@@ -6947,10 +6947,10 @@
         <v>46282.70833333334</v>
       </c>
       <c r="B23" s="4">
-        <v>610.3200000000001</v>
+        <v>570.03</v>
       </c>
       <c r="C23" s="4">
-        <v>411.77</v>
+        <v>366.52</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4">
@@ -6966,10 +6966,10 @@
         <v>46282.75</v>
       </c>
       <c r="B24" s="4">
-        <v>598.41</v>
+        <v>557.8200000000001</v>
       </c>
       <c r="C24" s="4">
-        <v>412.12</v>
+        <v>366.88</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4">
@@ -6985,10 +6985,10 @@
         <v>46282.79166666666</v>
       </c>
       <c r="B25" s="4">
-        <v>586.96</v>
+        <v>546.09</v>
       </c>
       <c r="C25" s="4">
-        <v>412.35</v>
+        <v>367.11</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4">
@@ -7004,10 +7004,10 @@
         <v>46282.83333333334</v>
       </c>
       <c r="B26" s="4">
-        <v>574.8099999999999</v>
+        <v>533.63</v>
       </c>
       <c r="C26" s="4">
-        <v>412.5</v>
+        <v>367.27</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4">
@@ -7023,10 +7023,10 @@
         <v>46282.875</v>
       </c>
       <c r="B27" s="4">
-        <v>563.79</v>
+        <v>522.34</v>
       </c>
       <c r="C27" s="4">
-        <v>412.6</v>
+        <v>367.37</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4">
@@ -7042,10 +7042,10 @@
         <v>46282.91666666666</v>
       </c>
       <c r="B28" s="4">
-        <v>553.7</v>
+        <v>511.99</v>
       </c>
       <c r="C28" s="4">
-        <v>412.67</v>
+        <v>367.43</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4">
@@ -7061,10 +7061,10 @@
         <v>46282.95833333334</v>
       </c>
       <c r="B29" s="4">
-        <v>544.39</v>
+        <v>502.45</v>
       </c>
       <c r="C29" s="4">
-        <v>412.7</v>
+        <v>367.47</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4">
@@ -7080,10 +7080,10 @@
         <v>46283</v>
       </c>
       <c r="B30" s="4">
-        <v>535.78</v>
+        <v>493.62</v>
       </c>
       <c r="C30" s="4">
-        <v>412.72</v>
+        <v>367.48</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4">
@@ -7099,10 +7099,10 @@
         <v>46283.04166666666</v>
       </c>
       <c r="B31" s="4">
-        <v>527.24</v>
+        <v>484.87</v>
       </c>
       <c r="C31" s="4">
-        <v>413.61</v>
+        <v>368.39</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4">
@@ -7118,10 +7118,10 @@
         <v>46283.08333333334</v>
       </c>
       <c r="B32" s="4">
-        <v>520.48</v>
+        <v>477.94</v>
       </c>
       <c r="C32" s="4">
-        <v>415.04</v>
+        <v>369.85</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4">
@@ -7137,10 +7137,10 @@
         <v>46283.125</v>
       </c>
       <c r="B33" s="4">
-        <v>515.04</v>
+        <v>472.35</v>
       </c>
       <c r="C33" s="4">
-        <v>416.79</v>
+        <v>371.65</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4">
@@ -7156,10 +7156,10 @@
         <v>46283.16666666666</v>
       </c>
       <c r="B34" s="4">
-        <v>510.68</v>
+        <v>467.89</v>
       </c>
       <c r="C34" s="4">
-        <v>418.75</v>
+        <v>373.66</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4">
@@ -7175,10 +7175,10 @@
         <v>46283.20833333334</v>
       </c>
       <c r="B35" s="4">
-        <v>507.37</v>
+        <v>464.49</v>
       </c>
       <c r="C35" s="4">
-        <v>420.83</v>
+        <v>375.79</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4">
@@ -7194,10 +7194,10 @@
         <v>46283.25</v>
       </c>
       <c r="B36" s="4">
-        <v>505.22</v>
+        <v>462.29</v>
       </c>
       <c r="C36" s="4">
-        <v>422.98</v>
+        <v>378</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4">
@@ -7213,10 +7213,10 @@
         <v>46283.29166666666</v>
       </c>
       <c r="B37" s="4">
-        <v>503.67</v>
+        <v>460.7</v>
       </c>
       <c r="C37" s="4">
-        <v>424.32</v>
+        <v>379.36</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4">
@@ -7232,10 +7232,10 @@
         <v>46283.33333333334</v>
       </c>
       <c r="B38" s="4">
-        <v>503.48</v>
+        <v>460.5</v>
       </c>
       <c r="C38" s="4">
-        <v>425.14</v>
+        <v>380.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4">
@@ -7251,10 +7251,10 @@
         <v>46283.375</v>
       </c>
       <c r="B39" s="4">
-        <v>505.4</v>
+        <v>462.47</v>
       </c>
       <c r="C39" s="4">
-        <v>425.64</v>
+        <v>380.72</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4">
@@ -7270,10 +7270,10 @@
         <v>46283.41666666666</v>
       </c>
       <c r="B40" s="4">
-        <v>510.11</v>
+        <v>467.3</v>
       </c>
       <c r="C40" s="4">
-        <v>425.94</v>
+        <v>381.03</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4">
@@ -7289,10 +7289,10 @@
         <v>46283.45833333334</v>
       </c>
       <c r="B41" s="4">
-        <v>513.0700000000001</v>
+        <v>470.33</v>
       </c>
       <c r="C41" s="4">
-        <v>426.12</v>
+        <v>381.21</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4">
@@ -7308,10 +7308,10 @@
         <v>46283.5</v>
       </c>
       <c r="B42" s="4">
-        <v>521.6</v>
+        <v>479.08</v>
       </c>
       <c r="C42" s="4">
-        <v>426.21</v>
+        <v>381.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4">
@@ -7327,10 +7327,10 @@
         <v>46283.54166666666</v>
       </c>
       <c r="B43" s="4">
-        <v>532.5</v>
+        <v>490.24</v>
       </c>
       <c r="C43" s="4">
-        <v>426.26</v>
+        <v>381.34</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4">
@@ -7346,10 +7346,10 @@
         <v>46283.58333333334</v>
       </c>
       <c r="B44" s="4">
-        <v>546.8200000000001</v>
+        <v>504.92</v>
       </c>
       <c r="C44" s="4">
-        <v>426.27</v>
+        <v>381.36</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4">
@@ -7365,10 +7365,10 @@
         <v>46283.625</v>
       </c>
       <c r="B45" s="4">
-        <v>562.2</v>
+        <v>520.6900000000001</v>
       </c>
       <c r="C45" s="4">
-        <v>426.26</v>
+        <v>381.34</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4">
@@ -7384,10 +7384,10 @@
         <v>46283.66666666666</v>
       </c>
       <c r="B46" s="4">
-        <v>576.16</v>
+        <v>535</v>
       </c>
       <c r="C46" s="4">
-        <v>426.23</v>
+        <v>381.31</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4">
@@ -7403,10 +7403,10 @@
         <v>46283.70833333334</v>
       </c>
       <c r="B47" s="4">
-        <v>586.39</v>
+        <v>545.47</v>
       </c>
       <c r="C47" s="4">
-        <v>426.19</v>
+        <v>381.27</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4">
@@ -7422,10 +7422,10 @@
         <v>46283.75</v>
       </c>
       <c r="B48" s="4">
-        <v>589.01</v>
+        <v>548.16</v>
       </c>
       <c r="C48" s="4">
-        <v>426.14</v>
+        <v>381.22</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4">
@@ -7441,10 +7441,10 @@
         <v>46283.79166666666</v>
       </c>
       <c r="B49" s="4">
-        <v>584.76</v>
+        <v>543.8</v>
       </c>
       <c r="C49" s="4">
-        <v>426.08</v>
+        <v>381.16</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4">
@@ -7460,10 +7460,10 @@
         <v>46283.83333333334</v>
       </c>
       <c r="B50" s="4">
-        <v>578.37</v>
+        <v>537.26</v>
       </c>
       <c r="C50" s="4">
-        <v>426.02</v>
+        <v>381.09</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4">
@@ -7479,10 +7479,10 @@
         <v>46283.875</v>
       </c>
       <c r="B51" s="4">
-        <v>570.9</v>
+        <v>529.6</v>
       </c>
       <c r="C51" s="4">
-        <v>425.95</v>
+        <v>381.02</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4">
@@ -7498,10 +7498,10 @@
         <v>46283.91666666666</v>
       </c>
       <c r="B52" s="4">
-        <v>561.04</v>
+        <v>519.49</v>
       </c>
       <c r="C52" s="4">
-        <v>425.87</v>
+        <v>380.94</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4">
@@ -7517,10 +7517,10 @@
         <v>46283.95833333334</v>
       </c>
       <c r="B53" s="4">
-        <v>551.98</v>
+        <v>510.2</v>
       </c>
       <c r="C53" s="4">
-        <v>425.79</v>
+        <v>380.86</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
@@ -7536,10 +7536,10 @@
         <v>46284</v>
       </c>
       <c r="B54" s="4">
-        <v>543.59</v>
+        <v>501.6</v>
       </c>
       <c r="C54" s="4">
-        <v>425.7</v>
+        <v>380.77</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4">
@@ -7555,10 +7555,10 @@
         <v>46284.04166666666</v>
       </c>
       <c r="B55" s="4">
-        <v>533.91</v>
+        <v>491.68</v>
       </c>
       <c r="C55" s="4">
-        <v>425.68</v>
+        <v>380.75</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4">
@@ -7574,10 +7574,10 @@
         <v>46284.08333333334</v>
       </c>
       <c r="B56" s="4">
-        <v>525.67</v>
+        <v>483.24</v>
       </c>
       <c r="C56" s="4">
-        <v>425.7</v>
+        <v>380.77</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4">
@@ -7593,10 +7593,10 @@
         <v>46284.125</v>
       </c>
       <c r="B57" s="4">
-        <v>518.48</v>
+        <v>475.86</v>
       </c>
       <c r="C57" s="4">
-        <v>425.74</v>
+        <v>380.81</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4">
@@ -7612,10 +7612,10 @@
         <v>46284.16666666666</v>
       </c>
       <c r="B58" s="4">
-        <v>512.0599999999999</v>
+        <v>469.29</v>
       </c>
       <c r="C58" s="4">
-        <v>425.8</v>
+        <v>380.87</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4">
@@ -7631,10 +7631,10 @@
         <v>46284.20833333334</v>
       </c>
       <c r="B59" s="4">
-        <v>506.26</v>
+        <v>463.34</v>
       </c>
       <c r="C59" s="4">
-        <v>425.86</v>
+        <v>380.93</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4">
@@ -7650,10 +7650,10 @@
         <v>46284.25</v>
       </c>
       <c r="B60" s="4">
-        <v>500.95</v>
+        <v>457.89</v>
       </c>
       <c r="C60" s="4">
-        <v>425.93</v>
+        <v>381</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4">
@@ -7669,10 +7669,10 @@
         <v>46284.29166666666</v>
       </c>
       <c r="B61" s="4">
-        <v>496.06</v>
+        <v>452.88</v>
       </c>
       <c r="C61" s="4">
-        <v>425.99</v>
+        <v>381.06</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4">
@@ -7688,10 +7688,10 @@
         <v>46284.33333333334</v>
       </c>
       <c r="B62" s="4">
-        <v>491.54</v>
+        <v>448.24</v>
       </c>
       <c r="C62" s="4">
-        <v>426.06</v>
+        <v>381.13</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4">
@@ -7707,10 +7707,10 @@
         <v>46284.375</v>
       </c>
       <c r="B63" s="4">
-        <v>487.33</v>
+        <v>443.94</v>
       </c>
       <c r="C63" s="4">
-        <v>426.12</v>
+        <v>381.2</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4">
@@ -7726,10 +7726,10 @@
         <v>46284.41666666666</v>
       </c>
       <c r="B64" s="4">
-        <v>483.42</v>
+        <v>439.93</v>
       </c>
       <c r="C64" s="4">
-        <v>426.19</v>
+        <v>381.26</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4">
@@ -7745,10 +7745,10 @@
         <v>46284.45833333334</v>
       </c>
       <c r="B65" s="4">
-        <v>479.77</v>
+        <v>436.19</v>
       </c>
       <c r="C65" s="4">
-        <v>426.25</v>
+        <v>381.32</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4">
@@ -7764,10 +7764,10 @@
         <v>46284.5</v>
       </c>
       <c r="B66" s="4">
-        <v>476.37</v>
+        <v>432.7</v>
       </c>
       <c r="C66" s="4">
-        <v>426.31</v>
+        <v>381.38</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4">
@@ -7783,10 +7783,10 @@
         <v>46284.54166666666</v>
       </c>
       <c r="B67" s="4">
-        <v>473.19</v>
+        <v>429.44</v>
       </c>
       <c r="C67" s="4">
-        <v>426.36</v>
+        <v>381.44</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4">
@@ -7802,10 +7802,10 @@
         <v>46284.58333333334</v>
       </c>
       <c r="B68" s="4">
-        <v>470.22</v>
+        <v>426.39</v>
       </c>
       <c r="C68" s="4">
-        <v>426.42</v>
+        <v>381.5</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4">
@@ -7821,10 +7821,10 @@
         <v>46284.625</v>
       </c>
       <c r="B69" s="4">
-        <v>467.44</v>
+        <v>423.55</v>
       </c>
       <c r="C69" s="4">
-        <v>426.47</v>
+        <v>381.55</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4">
@@ -7840,10 +7840,10 @@
         <v>46284.66666666666</v>
       </c>
       <c r="B70" s="4">
-        <v>464.85</v>
+        <v>420.89</v>
       </c>
       <c r="C70" s="4">
-        <v>426.52</v>
+        <v>381.6</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4">
@@ -7859,10 +7859,10 @@
         <v>46284.70833333334</v>
       </c>
       <c r="B71" s="4">
-        <v>462.42</v>
+        <v>418.4</v>
       </c>
       <c r="C71" s="4">
-        <v>426.57</v>
+        <v>381.65</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4">
@@ -7878,10 +7878,10 @@
         <v>46284.75</v>
       </c>
       <c r="B72" s="4">
-        <v>460.16</v>
+        <v>416.08</v>
       </c>
       <c r="C72" s="4">
-        <v>426.61</v>
+        <v>381.7</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4">
@@ -7897,10 +7897,10 @@
         <v>46284.79166666666</v>
       </c>
       <c r="B73" s="4">
-        <v>458.04</v>
+        <v>413.91</v>
       </c>
       <c r="C73" s="4">
-        <v>426.66</v>
+        <v>381.74</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4">
@@ -7916,10 +7916,10 @@
         <v>46284.83333333334</v>
       </c>
       <c r="B74" s="4">
-        <v>456.06</v>
+        <v>411.87</v>
       </c>
       <c r="C74" s="4">
-        <v>426.7</v>
+        <v>381.78</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4">
@@ -7935,10 +7935,10 @@
         <v>46284.875</v>
       </c>
       <c r="B75" s="4">
-        <v>454.2</v>
+        <v>409.97</v>
       </c>
       <c r="C75" s="4">
-        <v>426.74</v>
+        <v>381.82</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4">
@@ -7954,10 +7954,10 @@
         <v>46284.91666666666</v>
       </c>
       <c r="B76" s="4">
-        <v>452.47</v>
+        <v>408.2</v>
       </c>
       <c r="C76" s="4">
-        <v>426.78</v>
+        <v>381.86</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4">
@@ -7973,10 +7973,10 @@
         <v>46284.95833333334</v>
       </c>
       <c r="B77" s="4">
-        <v>450.85</v>
+        <v>406.54</v>
       </c>
       <c r="C77" s="4">
-        <v>426.82</v>
+        <v>381.9</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4">
@@ -8444,19 +8444,19 @@
         <v>500</v>
       </c>
       <c r="D4" s="4">
-        <v>110.336</v>
+        <v>70.83799999999999</v>
       </c>
       <c r="E4" s="4">
-        <v>119.804</v>
+        <v>85.11499999999999</v>
       </c>
       <c r="F4" s="4">
-        <v>110.336</v>
+        <v>70.642</v>
       </c>
       <c r="G4" s="4">
-        <v>3.8</v>
+        <v>45.6</v>
       </c>
       <c r="H4" s="4">
-        <v>58</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8470,19 +8470,19 @@
         <v>500</v>
       </c>
       <c r="D5" s="4">
-        <v>110.336</v>
+        <v>70.83799999999999</v>
       </c>
       <c r="E5" s="4">
-        <v>119.804</v>
+        <v>85.11499999999999</v>
       </c>
       <c r="F5" s="4">
-        <v>110.336</v>
+        <v>70.642</v>
       </c>
       <c r="G5" s="4">
-        <v>3.8</v>
+        <v>45.6</v>
       </c>
       <c r="H5" s="4">
-        <v>58</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -8496,19 +8496,19 @@
         <v>500</v>
       </c>
       <c r="D6" s="4">
-        <v>110.336</v>
+        <v>70.83799999999999</v>
       </c>
       <c r="E6" s="4">
-        <v>119.804</v>
+        <v>85.11499999999999</v>
       </c>
       <c r="F6" s="4">
-        <v>110.336</v>
+        <v>70.642</v>
       </c>
       <c r="G6" s="4">
-        <v>3.8</v>
+        <v>45.6</v>
       </c>
       <c r="H6" s="4">
-        <v>58</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -8516,7 +8516,7 @@
         <v>76</v>
       </c>
       <c r="B8" s="4">
-        <v>8.300000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="C8" s="4">
         <v>24</v>
@@ -8645,11 +8645,11 @@
         <v>524.38</v>
       </c>
       <c r="C19" s="4">
-        <v>597.88</v>
+        <v>557.24</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4">
-        <v>73.5</v>
+        <v>32.86000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8660,11 +8660,11 @@
         <v>514.3200000000001</v>
       </c>
       <c r="C20" s="4">
-        <v>597.86</v>
+        <v>557.22</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4">
-        <v>83.53999999999996</v>
+        <v>42.89999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8675,11 +8675,11 @@
         <v>523.23</v>
       </c>
       <c r="C21" s="4">
-        <v>598.35</v>
+        <v>557.72</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4">
-        <v>75.12</v>
+        <v>34.49000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8690,11 +8690,11 @@
         <v>515.5</v>
       </c>
       <c r="C22" s="4">
-        <v>598.73</v>
+        <v>558.11</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4">
-        <v>83.23000000000002</v>
+        <v>42.61000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8705,11 +8705,11 @@
         <v>513.1</v>
       </c>
       <c r="C23" s="4">
-        <v>599.24</v>
+        <v>558.64</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4">
-        <v>86.13999999999999</v>
+        <v>45.53999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8720,11 +8720,11 @@
         <v>515.5700000000001</v>
       </c>
       <c r="C24" s="4">
-        <v>600.08</v>
+        <v>559.49</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4">
-        <v>84.50999999999999</v>
+        <v>43.91999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8735,11 +8735,11 @@
         <v>515.86</v>
       </c>
       <c r="C25" s="4">
-        <v>601.45</v>
+        <v>560.9</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4">
-        <v>85.59000000000003</v>
+        <v>45.03999999999996</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8750,11 +8750,11 @@
         <v>504.61</v>
       </c>
       <c r="C26" s="4">
-        <v>602.1900000000001</v>
+        <v>561.66</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4">
-        <v>97.58000000000004</v>
+        <v>57.04999999999995</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8765,11 +8765,11 @@
         <v>503.42</v>
       </c>
       <c r="C27" s="4">
-        <v>603.12</v>
+        <v>562.61</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4">
-        <v>99.69999999999999</v>
+        <v>59.19</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8780,11 +8780,11 @@
         <v>499.68</v>
       </c>
       <c r="C28" s="4">
-        <v>603.5700000000001</v>
+        <v>563.0700000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4">
-        <v>103.89</v>
+        <v>63.39000000000004</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8795,11 +8795,11 @@
         <v>499.44</v>
       </c>
       <c r="C29" s="4">
-        <v>604.66</v>
+        <v>564.1900000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4">
-        <v>105.22</v>
+        <v>64.75000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8810,11 +8810,11 @@
         <v>499.4</v>
       </c>
       <c r="C30" s="4">
-        <v>605.3099999999999</v>
+        <v>564.86</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4">
-        <v>105.91</v>
+        <v>65.46000000000004</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8825,11 +8825,11 @@
         <v>523.78</v>
       </c>
       <c r="C31" s="4">
-        <v>605.54</v>
+        <v>565.1</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4">
-        <v>81.75999999999999</v>
+        <v>41.32000000000005</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8840,11 +8840,11 @@
         <v>521.11</v>
       </c>
       <c r="C32" s="4">
-        <v>605.8</v>
+        <v>565.36</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4">
-        <v>84.68999999999994</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8855,11 +8855,11 @@
         <v>522.45</v>
       </c>
       <c r="C33" s="4">
-        <v>605.9</v>
+        <v>565.46</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4">
-        <v>83.44999999999993</v>
+        <v>43.00999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8870,11 +8870,11 @@
         <v>510.09</v>
       </c>
       <c r="C34" s="4">
-        <v>605.8099999999999</v>
+        <v>565.37</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4">
-        <v>95.71999999999997</v>
+        <v>55.28000000000003</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8885,11 +8885,11 @@
         <v>516.53</v>
       </c>
       <c r="C35" s="4">
-        <v>605.9400000000001</v>
+        <v>565.51</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4">
-        <v>89.41000000000008</v>
+        <v>48.98000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8900,11 +8900,11 @@
         <v>516.55</v>
       </c>
       <c r="C36" s="4">
-        <v>606.16</v>
+        <v>565.72</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4">
-        <v>89.61000000000001</v>
+        <v>49.17000000000007</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8915,11 +8915,11 @@
         <v>521.5599999999999</v>
       </c>
       <c r="C37" s="4">
-        <v>606.41</v>
+        <v>565.98</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4">
-        <v>84.85000000000002</v>
+        <v>44.42000000000007</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8930,11 +8930,11 @@
         <v>531.13</v>
       </c>
       <c r="C38" s="4">
-        <v>606.9400000000001</v>
+        <v>566.53</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4">
-        <v>75.81000000000006</v>
+        <v>35.39999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8945,11 +8945,11 @@
         <v>522.8</v>
       </c>
       <c r="C39" s="4">
-        <v>607.17</v>
+        <v>566.77</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4">
-        <v>84.37</v>
+        <v>43.97000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8960,11 +8960,11 @@
         <v>530.8</v>
       </c>
       <c r="C40" s="4">
-        <v>607.15</v>
+        <v>566.74</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4">
-        <v>76.35000000000002</v>
+        <v>35.94000000000005</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8975,11 +8975,11 @@
         <v>525.83</v>
       </c>
       <c r="C41" s="4">
-        <v>606.89</v>
+        <v>566.47</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4">
-        <v>81.05999999999995</v>
+        <v>40.63999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8990,11 +8990,11 @@
         <v>503.75</v>
       </c>
       <c r="C42" s="4">
-        <v>606.76</v>
+        <v>566.34</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4">
-        <v>103.01</v>
+        <v>62.59000000000003</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9005,11 +9005,11 @@
         <v>503.9</v>
       </c>
       <c r="C43" s="4">
-        <v>606.8200000000001</v>
+        <v>566.4</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4">
-        <v>102.9200000000001</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9020,11 +9020,11 @@
         <v>487.86</v>
       </c>
       <c r="C44" s="4">
-        <v>606.74</v>
+        <v>566.3200000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4">
-        <v>118.88</v>
+        <v>78.46000000000004</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9035,11 +9035,11 @@
         <v>502.99</v>
       </c>
       <c r="C45" s="4">
-        <v>606.5599999999999</v>
+        <v>566.14</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4">
-        <v>103.5699999999999</v>
+        <v>63.14999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9050,11 +9050,11 @@
         <v>517.1</v>
       </c>
       <c r="C46" s="4">
-        <v>606.58</v>
+        <v>566.16</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4">
-        <v>89.48000000000002</v>
+        <v>49.05999999999995</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9065,11 +9065,11 @@
         <v>515.25</v>
       </c>
       <c r="C47" s="4">
-        <v>606.4</v>
+        <v>565.98</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4">
-        <v>91.14999999999998</v>
+        <v>50.73000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9080,11 +9080,11 @@
         <v>512.5700000000001</v>
       </c>
       <c r="C48" s="4">
-        <v>606.52</v>
+        <v>566.1</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4">
-        <v>93.94999999999993</v>
+        <v>53.52999999999997</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9095,11 +9095,11 @@
         <v>514.34</v>
       </c>
       <c r="C49" s="4">
-        <v>606.8</v>
+        <v>566.39</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4">
-        <v>92.45999999999992</v>
+        <v>52.04999999999995</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9110,11 +9110,11 @@
         <v>512.1799999999999</v>
       </c>
       <c r="C50" s="4">
-        <v>607.84</v>
+        <v>567.45</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4">
-        <v>95.66000000000008</v>
+        <v>55.2700000000001</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9125,11 +9125,11 @@
         <v>493.49</v>
       </c>
       <c r="C51" s="4">
-        <v>607.8</v>
+        <v>567.41</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4">
-        <v>114.3099999999999</v>
+        <v>73.91999999999996</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9140,11 +9140,11 @@
         <v>499.88</v>
       </c>
       <c r="C52" s="4">
-        <v>608.0700000000001</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4">
-        <v>108.1900000000001</v>
+        <v>67.79999999999995</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9155,11 +9155,11 @@
         <v>490.27</v>
       </c>
       <c r="C53" s="4">
-        <v>608.47</v>
+        <v>568.09</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
-        <v>118.2</v>
+        <v>77.82000000000005</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9170,11 +9170,11 @@
         <v>499.96</v>
       </c>
       <c r="C54" s="4">
-        <v>608.3</v>
+        <v>567.92</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4">
-        <v>108.34</v>
+        <v>67.95999999999998</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9185,11 +9185,11 @@
         <v>505.14</v>
       </c>
       <c r="C55" s="4">
-        <v>608.6</v>
+        <v>568.23</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4">
-        <v>103.46</v>
+        <v>63.09000000000003</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9200,11 +9200,11 @@
         <v>506.39</v>
       </c>
       <c r="C56" s="4">
-        <v>609.01</v>
+        <v>568.65</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4">
-        <v>102.62</v>
+        <v>62.25999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9215,11 +9215,11 @@
         <v>513.53</v>
       </c>
       <c r="C57" s="4">
-        <v>609.05</v>
+        <v>568.6900000000001</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4">
-        <v>95.51999999999998</v>
+        <v>55.16000000000008</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -9230,11 +9230,11 @@
         <v>516.79</v>
       </c>
       <c r="C58" s="4">
-        <v>609.12</v>
+        <v>568.76</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4">
-        <v>92.33000000000004</v>
+        <v>51.97000000000003</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -9245,11 +9245,11 @@
         <v>522.96</v>
       </c>
       <c r="C59" s="4">
-        <v>609.24</v>
+        <v>568.88</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4">
-        <v>86.27999999999997</v>
+        <v>45.91999999999996</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -9260,11 +9260,11 @@
         <v>514.38</v>
       </c>
       <c r="C60" s="4">
-        <v>609.37</v>
+        <v>569.02</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4">
-        <v>94.99000000000001</v>
+        <v>54.63999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -9275,11 +9275,11 @@
         <v>521.8099999999999</v>
       </c>
       <c r="C61" s="4">
-        <v>609.42</v>
+        <v>569.0700000000001</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4">
-        <v>87.61000000000001</v>
+        <v>47.2600000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -9290,11 +9290,11 @@
         <v>518.83</v>
       </c>
       <c r="C62" s="4">
-        <v>609.5599999999999</v>
+        <v>569.21</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4">
-        <v>90.7299999999999</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -9305,11 +9305,11 @@
         <v>513.58</v>
       </c>
       <c r="C63" s="4">
-        <v>609.62</v>
+        <v>569.28</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4">
-        <v>96.03999999999996</v>
+        <v>55.69999999999993</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -9320,11 +9320,11 @@
         <v>517.41</v>
       </c>
       <c r="C64" s="4">
-        <v>609.64</v>
+        <v>569.29</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4">
-        <v>92.23000000000002</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -9335,11 +9335,11 @@
         <v>518.5</v>
       </c>
       <c r="C65" s="4">
-        <v>610.27</v>
+        <v>569.9400000000001</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4">
-        <v>91.76999999999998</v>
+        <v>51.44000000000005</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -9350,11 +9350,11 @@
         <v>515.33</v>
       </c>
       <c r="C66" s="4">
-        <v>610.33</v>
+        <v>570.01</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4">
-        <v>95</v>
+        <v>54.67999999999995</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -9365,11 +9365,11 @@
         <v>518.99</v>
       </c>
       <c r="C67" s="4">
-        <v>610.21</v>
+        <v>569.88</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4">
-        <v>91.22000000000003</v>
+        <v>50.88999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -9380,11 +9380,11 @@
         <v>525.5599999999999</v>
       </c>
       <c r="C68" s="4">
-        <v>610.36</v>
+        <v>570.03</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4">
-        <v>84.80000000000007</v>
+        <v>44.47000000000003</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -9395,11 +9395,11 @@
         <v>525.3</v>
       </c>
       <c r="C69" s="4">
-        <v>610.75</v>
+        <v>570.4299999999999</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4">
-        <v>85.45000000000005</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -9410,11 +9410,11 @@
         <v>526.4</v>
       </c>
       <c r="C70" s="4">
-        <v>610.64</v>
+        <v>570.3200000000001</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4">
-        <v>84.24000000000001</v>
+        <v>43.92000000000007</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -9425,11 +9425,11 @@
         <v>527.9</v>
       </c>
       <c r="C71" s="4">
-        <v>610.6799999999999</v>
+        <v>570.36</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4">
-        <v>82.77999999999997</v>
+        <v>42.46000000000004</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -9440,11 +9440,11 @@
         <v>532.33</v>
       </c>
       <c r="C72" s="4">
-        <v>610.74</v>
+        <v>570.42</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4">
-        <v>78.40999999999997</v>
+        <v>38.08999999999992</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -9455,11 +9455,11 @@
         <v>523.04</v>
       </c>
       <c r="C73" s="4">
-        <v>610.87</v>
+        <v>570.5599999999999</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4">
-        <v>87.83000000000004</v>
+        <v>47.51999999999998</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -9470,11 +9470,11 @@
         <v>537.21</v>
       </c>
       <c r="C74" s="4">
-        <v>610.67</v>
+        <v>570.35</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4">
-        <v>73.45999999999992</v>
+        <v>33.13999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -9485,11 +9485,11 @@
         <v>538.3200000000001</v>
       </c>
       <c r="C75" s="4">
-        <v>610.61</v>
+        <v>570.29</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4">
-        <v>72.28999999999996</v>
+        <v>31.96999999999991</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -9500,11 +9500,11 @@
         <v>543.54</v>
       </c>
       <c r="C76" s="4">
-        <v>610.7</v>
+        <v>570.38</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4">
-        <v>67.16000000000008</v>
+        <v>26.84000000000003</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -9515,11 +9515,11 @@
         <v>534.9400000000001</v>
       </c>
       <c r="C77" s="4">
-        <v>611</v>
+        <v>570.6799999999999</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4">
-        <v>76.05999999999995</v>
+        <v>35.7399999999999</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -9530,11 +9530,11 @@
         <v>523.99</v>
       </c>
       <c r="C78" s="4">
-        <v>611.01</v>
+        <v>570.7</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4">
-        <v>87.01999999999998</v>
+        <v>46.71000000000004</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -9545,11 +9545,11 @@
         <v>515.29</v>
       </c>
       <c r="C79" s="4">
-        <v>611</v>
+        <v>570.6900000000001</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4">
-        <v>95.71000000000004</v>
+        <v>55.40000000000009</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -9560,11 +9560,11 @@
         <v>547.36</v>
       </c>
       <c r="C80" s="4">
-        <v>610.98</v>
+        <v>570.67</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4">
-        <v>63.62</v>
+        <v>23.30999999999995</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -9575,11 +9575,11 @@
         <v>562.9</v>
       </c>
       <c r="C81" s="4">
-        <v>610.92</v>
+        <v>570.61</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4">
-        <v>48.01999999999998</v>
+        <v>7.710000000000036</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -9590,11 +9590,11 @@
         <v>531.67</v>
       </c>
       <c r="C82" s="4">
-        <v>610.78</v>
+        <v>570.47</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4">
-        <v>79.11000000000001</v>
+        <v>38.80000000000007</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -9605,11 +9605,11 @@
         <v>530.35</v>
       </c>
       <c r="C83" s="4">
-        <v>611.1799999999999</v>
+        <v>570.87</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4">
-        <v>80.82999999999993</v>
+        <v>40.51999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -9620,11 +9620,11 @@
         <v>516.96</v>
       </c>
       <c r="C84" s="4">
-        <v>611.15</v>
+        <v>570.84</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4">
-        <v>94.18999999999994</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -9635,11 +9635,11 @@
         <v>506.5</v>
       </c>
       <c r="C85" s="4">
-        <v>611.2</v>
+        <v>570.89</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4">
-        <v>104.7</v>
+        <v>64.38999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -9650,11 +9650,11 @@
         <v>524.67</v>
       </c>
       <c r="C86" s="4">
-        <v>611.29</v>
+        <v>570.99</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4">
-        <v>86.62</v>
+        <v>46.32000000000005</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -9665,11 +9665,11 @@
         <v>517.58</v>
       </c>
       <c r="C87" s="4">
-        <v>611.27</v>
+        <v>570.97</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="4">
-        <v>93.68999999999994</v>
+        <v>53.38999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -9680,11 +9680,11 @@
         <v>505.55</v>
       </c>
       <c r="C88" s="4">
-        <v>611.36</v>
+        <v>571.0599999999999</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4">
-        <v>105.81</v>
+        <v>65.50999999999993</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -9695,11 +9695,11 @@
         <v>547.46</v>
       </c>
       <c r="C89" s="4">
-        <v>611.5700000000001</v>
+        <v>571.27</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4">
-        <v>64.11000000000001</v>
+        <v>23.80999999999995</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -9710,11 +9710,11 @@
         <v>530.12</v>
       </c>
       <c r="C90" s="4">
-        <v>611.85</v>
+        <v>571.5599999999999</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4">
-        <v>81.73000000000002</v>
+        <v>41.43999999999994</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -9725,11 +9725,11 @@
         <v>529.24</v>
       </c>
       <c r="C91" s="4">
-        <v>611.99</v>
+        <v>571.7</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4">
-        <v>82.75</v>
+        <v>42.46000000000004</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -9740,11 +9740,11 @@
         <v>533.87</v>
       </c>
       <c r="C92" s="4">
-        <v>611.96</v>
+        <v>571.6799999999999</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4">
-        <v>78.09000000000003</v>
+        <v>37.80999999999995</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -9755,11 +9755,11 @@
         <v>518.26</v>
       </c>
       <c r="C93" s="4">
-        <v>612.13</v>
+        <v>571.85</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4">
-        <v>93.87</v>
+        <v>53.59000000000003</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -9770,11 +9770,11 @@
         <v>396.49</v>
       </c>
       <c r="C94" s="4">
-        <v>612.36</v>
+        <v>572.09</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4">
-        <v>215.87</v>
+        <v>175.6</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -9785,11 +9785,11 @@
         <v>464.19</v>
       </c>
       <c r="C95" s="4">
-        <v>612.4400000000001</v>
+        <v>572.17</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4">
-        <v>148.2500000000001</v>
+        <v>107.98</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -9800,11 +9800,11 @@
         <v>498.33</v>
       </c>
       <c r="C96" s="4">
-        <v>612.67</v>
+        <v>572.4</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4">
-        <v>114.34</v>
+        <v>74.06999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -9815,11 +9815,11 @@
         <v>544.49</v>
       </c>
       <c r="C97" s="4">
-        <v>612.9299999999999</v>
+        <v>572.67</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4">
-        <v>68.43999999999994</v>
+        <v>28.17999999999995</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -9830,11 +9830,11 @@
         <v>525.1</v>
       </c>
       <c r="C98" s="4">
-        <v>613.02</v>
+        <v>572.76</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4">
-        <v>87.91999999999996</v>
+        <v>47.65999999999997</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -9845,11 +9845,11 @@
         <v>538.16</v>
       </c>
       <c r="C99" s="4">
-        <v>613.12</v>
+        <v>572.87</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4">
-        <v>74.96000000000004</v>
+        <v>34.71000000000004</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -9860,11 +9860,11 @@
         <v>508.79</v>
       </c>
       <c r="C100" s="4">
-        <v>613.11</v>
+        <v>572.85</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4">
-        <v>104.32</v>
+        <v>64.06</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -9875,11 +9875,11 @@
         <v>504.36</v>
       </c>
       <c r="C101" s="4">
-        <v>613.1900000000001</v>
+        <v>572.9299999999999</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4">
-        <v>108.83</v>
+        <v>68.56999999999994</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -9890,11 +9890,11 @@
         <v>507.61</v>
       </c>
       <c r="C102" s="4">
-        <v>613.5700000000001</v>
+        <v>573.3200000000001</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4">
-        <v>105.96</v>
+        <v>65.71000000000004</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -9905,11 +9905,11 @@
         <v>498.09</v>
       </c>
       <c r="C103" s="4">
-        <v>613.46</v>
+        <v>573.21</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4">
-        <v>115.3700000000001</v>
+        <v>75.12000000000006</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -9920,11 +9920,11 @@
         <v>495.48</v>
       </c>
       <c r="C104" s="4">
-        <v>613.0700000000001</v>
+        <v>572.8099999999999</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4">
-        <v>117.59</v>
+        <v>77.32999999999993</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -9935,11 +9935,11 @@
         <v>566.86</v>
       </c>
       <c r="C105" s="4">
-        <v>613.13</v>
+        <v>572.88</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4">
-        <v>46.26999999999998</v>
+        <v>6.019999999999982</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -9950,11 +9950,11 @@
         <v>562.83</v>
       </c>
       <c r="C106" s="4">
-        <v>613.17</v>
+        <v>572.91</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4">
-        <v>50.33999999999992</v>
+        <v>10.07999999999993</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -9965,11 +9965,11 @@
         <v>547.9299999999999</v>
       </c>
       <c r="C107" s="4">
-        <v>613.03</v>
+        <v>572.77</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4">
-        <v>65.10000000000002</v>
+        <v>24.84000000000003</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -9980,11 +9980,11 @@
         <v>517.22</v>
       </c>
       <c r="C108" s="4">
-        <v>612.96</v>
+        <v>572.6900000000001</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4">
-        <v>95.74000000000001</v>
+        <v>55.47000000000003</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -9995,11 +9995,11 @@
         <v>534.39</v>
       </c>
       <c r="C109" s="4">
-        <v>613.03</v>
+        <v>572.77</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4">
-        <v>78.63999999999999</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -10010,11 +10010,11 @@
         <v>536.21</v>
       </c>
       <c r="C110" s="4">
-        <v>612.86</v>
+        <v>572.6</v>
       </c>
       <c r="D110" s="4"/>
       <c r="E110" s="4">
-        <v>76.64999999999998</v>
+        <v>36.38999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -10025,11 +10025,11 @@
         <v>541.21</v>
       </c>
       <c r="C111" s="4">
-        <v>612.6</v>
+        <v>572.33</v>
       </c>
       <c r="D111" s="4"/>
       <c r="E111" s="4">
-        <v>71.38999999999999</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -10040,11 +10040,11 @@
         <v>531.48</v>
       </c>
       <c r="C112" s="4">
-        <v>612.3099999999999</v>
+        <v>572.03</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4">
-        <v>80.82999999999993</v>
+        <v>40.54999999999995</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -10055,11 +10055,11 @@
         <v>525.86</v>
       </c>
       <c r="C113" s="4">
-        <v>611.6</v>
+        <v>571.3</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4">
-        <v>85.74000000000001</v>
+        <v>45.43999999999994</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -10070,11 +10070,11 @@
         <v>513.4400000000001</v>
       </c>
       <c r="C114" s="4">
-        <v>611.3</v>
+        <v>571</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4">
-        <v>97.8599999999999</v>
+        <v>57.55999999999995</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -10085,11 +10085,11 @@
         <v>526.25</v>
       </c>
       <c r="C115" s="4">
-        <v>610.8200000000001</v>
+        <v>570.5</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4">
-        <v>84.57000000000005</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -10100,11 +10100,11 @@
         <v>541.3099999999999</v>
       </c>
       <c r="C116" s="4">
-        <v>610.48</v>
+        <v>570.15</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4">
-        <v>69.17000000000007</v>
+        <v>28.84000000000003</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -10115,11 +10115,11 @@
         <v>547.64</v>
       </c>
       <c r="C117" s="4">
-        <v>610.09</v>
+        <v>569.76</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4">
-        <v>62.45000000000005</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -10130,11 +10130,11 @@
         <v>543.41</v>
       </c>
       <c r="C118" s="4">
-        <v>609.42</v>
+        <v>569.0700000000001</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4">
-        <v>66.00999999999999</v>
+        <v>25.66000000000008</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -10145,11 +10145,11 @@
         <v>544.86</v>
       </c>
       <c r="C119" s="4">
-        <v>609.55</v>
+        <v>569.21</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4">
-        <v>64.68999999999994</v>
+        <v>24.35000000000002</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -10160,11 +10160,11 @@
         <v>541.8099999999999</v>
       </c>
       <c r="C120" s="4">
-        <v>609.8099999999999</v>
+        <v>569.47</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4">
-        <v>68</v>
+        <v>27.66000000000008</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -10175,11 +10175,11 @@
         <v>538.67</v>
       </c>
       <c r="C121" s="4">
-        <v>609.78</v>
+        <v>569.4299999999999</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4">
-        <v>71.11000000000001</v>
+        <v>30.75999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -10190,11 +10190,11 @@
         <v>540.48</v>
       </c>
       <c r="C122" s="4">
-        <v>609.89</v>
+        <v>569.55</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4">
-        <v>69.40999999999997</v>
+        <v>29.06999999999994</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -10205,11 +10205,11 @@
         <v>543.11</v>
       </c>
       <c r="C123" s="4">
-        <v>609.78</v>
+        <v>569.4400000000001</v>
       </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4">
-        <v>66.66999999999996</v>
+        <v>26.33000000000004</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -10220,11 +10220,11 @@
         <v>532.59</v>
       </c>
       <c r="C124" s="4">
-        <v>609.67</v>
+        <v>569.33</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4">
-        <v>77.07999999999993</v>
+        <v>36.74000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -10235,11 +10235,11 @@
         <v>534.6</v>
       </c>
       <c r="C125" s="4">
-        <v>609.95</v>
+        <v>569.62</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4">
-        <v>75.35000000000002</v>
+        <v>35.01999999999998</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -10250,11 +10250,11 @@
         <v>534.42</v>
       </c>
       <c r="C126" s="4">
-        <v>610.47</v>
+        <v>570.15</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4">
-        <v>76.05000000000007</v>
+        <v>35.73000000000002</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -10265,11 +10265,11 @@
         <v>533.88</v>
       </c>
       <c r="C127" s="4">
-        <v>610.28</v>
+        <v>569.95</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4">
-        <v>76.39999999999998</v>
+        <v>36.07000000000005</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -10280,11 +10280,11 @@
         <v>529.3200000000001</v>
       </c>
       <c r="C128" s="4">
-        <v>610.1900000000001</v>
+        <v>569.86</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4">
-        <v>80.87</v>
+        <v>40.53999999999996</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -10295,11 +10295,11 @@
         <v>551.6900000000001</v>
       </c>
       <c r="C129" s="4">
-        <v>610.83</v>
+        <v>570.52</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4">
-        <v>59.13999999999999</v>
+        <v>18.82999999999993</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -10310,11 +10310,11 @@
         <v>558.9</v>
       </c>
       <c r="C130" s="4">
-        <v>611.1799999999999</v>
+        <v>570.87</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4">
-        <v>52.27999999999997</v>
+        <v>11.97000000000003</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -10325,11 +10325,11 @@
         <v>535.38</v>
       </c>
       <c r="C131" s="4">
-        <v>611.63</v>
+        <v>571.34</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4">
-        <v>76.25</v>
+        <v>35.96000000000004</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -10340,11 +10340,11 @@
         <v>534.8200000000001</v>
       </c>
       <c r="C132" s="4">
-        <v>612.08</v>
+        <v>571.79</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4">
-        <v>77.25999999999999</v>
+        <v>36.96999999999991</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -10355,11 +10355,11 @@
         <v>536.16</v>
       </c>
       <c r="C133" s="4">
-        <v>613</v>
+        <v>572.74</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4">
-        <v>76.84000000000003</v>
+        <v>36.58000000000004</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -10370,11 +10370,11 @@
         <v>525.22</v>
       </c>
       <c r="C134" s="4">
-        <v>613.24</v>
+        <v>572.98</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4">
-        <v>88.01999999999998</v>
+        <v>47.75999999999999</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -10385,11 +10385,11 @@
         <v>518.62</v>
       </c>
       <c r="C135" s="4">
-        <v>613.53</v>
+        <v>573.28</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4">
-        <v>94.90999999999997</v>
+        <v>54.65999999999997</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -10400,11 +10400,11 @@
         <v>521.41</v>
       </c>
       <c r="C136" s="4">
-        <v>613.87</v>
+        <v>573.64</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4">
-        <v>92.46000000000004</v>
+        <v>52.23000000000002</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -10415,11 +10415,11 @@
         <v>525.21</v>
       </c>
       <c r="C137" s="4">
-        <v>613.73</v>
+        <v>573.48</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4">
-        <v>88.51999999999998</v>
+        <v>48.26999999999998</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -10430,11 +10430,11 @@
         <v>516.67</v>
       </c>
       <c r="C138" s="4">
-        <v>613.85</v>
+        <v>573.61</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4">
-        <v>97.18000000000006</v>
+        <v>56.94000000000005</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -10445,11 +10445,11 @@
         <v>512.39</v>
       </c>
       <c r="C139" s="4">
-        <v>613.79</v>
+        <v>573.55</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4">
-        <v>101.4</v>
+        <v>61.15999999999997</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -10460,11 +10460,11 @@
         <v>520</v>
       </c>
       <c r="C140" s="4">
-        <v>613.74</v>
+        <v>573.5</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4">
-        <v>93.74000000000001</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -10475,11 +10475,11 @@
         <v>525.29</v>
       </c>
       <c r="C141" s="4">
-        <v>613.92</v>
+        <v>573.6799999999999</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4">
-        <v>88.63</v>
+        <v>48.38999999999999</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -10490,11 +10490,11 @@
         <v>552.15</v>
       </c>
       <c r="C142" s="4">
-        <v>613.99</v>
+        <v>573.76</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4">
-        <v>61.84000000000003</v>
+        <v>21.61000000000001</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -10505,11 +10505,11 @@
         <v>533.88</v>
       </c>
       <c r="C143" s="4">
-        <v>614.01</v>
+        <v>573.78</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4">
-        <v>80.13</v>
+        <v>39.89999999999998</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -10520,11 +10520,11 @@
         <v>531.9</v>
       </c>
       <c r="C144" s="4">
-        <v>614.23</v>
+        <v>574</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4">
-        <v>82.33000000000004</v>
+        <v>42.10000000000002</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -10535,11 +10535,11 @@
         <v>528.7</v>
       </c>
       <c r="C145" s="4">
-        <v>614.4</v>
+        <v>574.1799999999999</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4">
-        <v>85.69999999999993</v>
+        <v>45.4799999999999</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -10550,11 +10550,11 @@
         <v>528.84</v>
       </c>
       <c r="C146" s="4">
-        <v>614.67</v>
+        <v>574.45</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4">
-        <v>85.82999999999993</v>
+        <v>45.61000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -10565,11 +10565,11 @@
         <v>522.01</v>
       </c>
       <c r="C147" s="4">
-        <v>614.76</v>
+        <v>574.55</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4">
-        <v>92.75</v>
+        <v>52.53999999999996</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -10580,11 +10580,11 @@
         <v>532.41</v>
       </c>
       <c r="C148" s="4">
-        <v>615.1900000000001</v>
+        <v>574.98</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4">
-        <v>82.78000000000009</v>
+        <v>42.57000000000005</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -10595,11 +10595,11 @@
         <v>532</v>
       </c>
       <c r="C149" s="4">
-        <v>615.39</v>
+        <v>575.1900000000001</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4">
-        <v>83.38999999999999</v>
+        <v>43.19000000000005</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -10610,11 +10610,11 @@
         <v>525.01</v>
       </c>
       <c r="C150" s="4">
-        <v>615.9</v>
+        <v>575.71</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4">
-        <v>90.88999999999999</v>
+        <v>50.70000000000005</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -10625,11 +10625,11 @@
         <v>517.26</v>
       </c>
       <c r="C151" s="4">
-        <v>616.41</v>
+        <v>576.24</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4">
-        <v>99.14999999999998</v>
+        <v>58.98000000000002</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -10640,11 +10640,11 @@
         <v>492.09</v>
       </c>
       <c r="C152" s="4">
-        <v>616.55</v>
+        <v>576.38</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4">
-        <v>124.46</v>
+        <v>84.29000000000002</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -10655,11 +10655,11 @@
         <v>510.43</v>
       </c>
       <c r="C153" s="4">
-        <v>616.54</v>
+        <v>576.37</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4">
-        <v>106.11</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -10670,11 +10670,11 @@
         <v>532.72</v>
       </c>
       <c r="C154" s="4">
-        <v>616.66</v>
+        <v>576.49</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4">
-        <v>83.93999999999994</v>
+        <v>43.76999999999998</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -10685,11 +10685,11 @@
         <v>530.8200000000001</v>
       </c>
       <c r="C155" s="4">
-        <v>617.09</v>
+        <v>576.9299999999999</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4">
-        <v>86.26999999999998</v>
+        <v>46.1099999999999</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -10700,11 +10700,11 @@
         <v>532.53</v>
       </c>
       <c r="C156" s="4">
-        <v>617.54</v>
+        <v>577.39</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4">
-        <v>85.00999999999999</v>
+        <v>44.86000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -10715,11 +10715,11 @@
         <v>538.16</v>
       </c>
       <c r="C157" s="4">
-        <v>617.8</v>
+        <v>577.66</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4">
-        <v>79.63999999999999</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -10730,11 +10730,11 @@
         <v>540.26</v>
       </c>
       <c r="C158" s="4">
-        <v>618.03</v>
+        <v>577.9</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4">
-        <v>77.76999999999998</v>
+        <v>37.63999999999999</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -10745,11 +10745,11 @@
         <v>537.8099999999999</v>
       </c>
       <c r="C159" s="4">
-        <v>618.41</v>
+        <v>578.28</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4">
-        <v>80.60000000000002</v>
+        <v>40.47000000000003</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -10760,11 +10760,11 @@
         <v>540.84</v>
       </c>
       <c r="C160" s="4">
-        <v>618.51</v>
+        <v>578.39</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4">
-        <v>77.66999999999996</v>
+        <v>37.54999999999995</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -10775,11 +10775,11 @@
         <v>537.29</v>
       </c>
       <c r="C161" s="4">
-        <v>619.17</v>
+        <v>579.0700000000001</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4">
-        <v>81.88</v>
+        <v>41.78000000000009</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -10790,11 +10790,11 @@
         <v>542.2</v>
       </c>
       <c r="C162" s="4">
-        <v>619.3</v>
+        <v>579.1900000000001</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4">
-        <v>77.09999999999991</v>
+        <v>36.99000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -10805,11 +10805,11 @@
         <v>549.12</v>
       </c>
       <c r="C163" s="4">
-        <v>619.41</v>
+        <v>579.3099999999999</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4">
-        <v>70.28999999999996</v>
+        <v>30.18999999999994</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -10820,11 +10820,11 @@
         <v>529.65</v>
       </c>
       <c r="C164" s="4">
-        <v>619.75</v>
+        <v>579.66</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4">
-        <v>90.10000000000002</v>
+        <v>50.00999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -10835,11 +10835,11 @@
         <v>532.54</v>
       </c>
       <c r="C165" s="4">
-        <v>619.85</v>
+        <v>579.76</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4">
-        <v>87.31000000000006</v>
+        <v>47.22000000000003</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -10850,11 +10850,11 @@
         <v>529.14</v>
       </c>
       <c r="C166" s="4">
-        <v>619.97</v>
+        <v>579.89</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4">
-        <v>90.83000000000004</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -10865,11 +10865,11 @@
         <v>536.01</v>
       </c>
       <c r="C167" s="4">
-        <v>620</v>
+        <v>579.91</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4">
-        <v>83.99000000000001</v>
+        <v>43.89999999999998</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -10880,11 +10880,11 @@
         <v>532.77</v>
       </c>
       <c r="C168" s="4">
-        <v>620.12</v>
+        <v>580.04</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4">
-        <v>87.35000000000002</v>
+        <v>47.26999999999998</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -10895,11 +10895,11 @@
         <v>535.3</v>
       </c>
       <c r="C169" s="4">
-        <v>620.3200000000001</v>
+        <v>580.25</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4">
-        <v>85.0200000000001</v>
+        <v>44.95000000000005</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -10910,11 +10910,11 @@
         <v>537.8099999999999</v>
       </c>
       <c r="C170" s="4">
-        <v>620.47</v>
+        <v>580.4</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4">
-        <v>82.66000000000008</v>
+        <v>42.59000000000003</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -10925,11 +10925,11 @@
         <v>535.96</v>
       </c>
       <c r="C171" s="4">
-        <v>620.62</v>
+        <v>580.55</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4">
-        <v>84.65999999999997</v>
+        <v>44.58999999999992</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -10940,11 +10940,11 @@
         <v>536.3099999999999</v>
       </c>
       <c r="C172" s="4">
-        <v>620.71</v>
+        <v>580.64</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4">
-        <v>84.40000000000009</v>
+        <v>44.33000000000004</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -10955,11 +10955,11 @@
         <v>534.91</v>
       </c>
       <c r="C173" s="4">
-        <v>620.8</v>
+        <v>580.73</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4">
-        <v>85.88999999999999</v>
+        <v>45.82000000000005</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -10970,11 +10970,11 @@
         <v>536.3</v>
       </c>
       <c r="C174" s="4">
-        <v>620.86</v>
+        <v>580.8</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4">
-        <v>84.56000000000006</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -10985,11 +10985,11 @@
         <v>538.02</v>
       </c>
       <c r="C175" s="4">
-        <v>620.99</v>
+        <v>580.9299999999999</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4">
-        <v>82.97000000000003</v>
+        <v>42.90999999999997</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -11000,11 +11000,11 @@
         <v>529.58</v>
       </c>
       <c r="C176" s="4">
-        <v>621.28</v>
+        <v>581.22</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4">
-        <v>91.69999999999993</v>
+        <v>51.63999999999999</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -11015,11 +11015,11 @@
         <v>531.95</v>
       </c>
       <c r="C177" s="4">
-        <v>621.3200000000001</v>
+        <v>581.26</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4">
-        <v>89.37</v>
+        <v>49.30999999999995</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -11030,11 +11030,11 @@
         <v>533.5700000000001</v>
       </c>
       <c r="C178" s="4">
-        <v>621.33</v>
+        <v>581.28</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4">
-        <v>87.75999999999999</v>
+        <v>47.70999999999992</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -11045,11 +11045,11 @@
         <v>530.35</v>
       </c>
       <c r="C179" s="4">
-        <v>621.41</v>
+        <v>581.36</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4">
-        <v>91.05999999999995</v>
+        <v>51.00999999999999</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -11060,11 +11060,11 @@
         <v>533.64</v>
       </c>
       <c r="C180" s="4">
-        <v>621.49</v>
+        <v>581.4400000000001</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4">
-        <v>87.85000000000002</v>
+        <v>47.80000000000007</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -11075,11 +11075,11 @@
         <v>529.02</v>
       </c>
       <c r="C181" s="4">
-        <v>621.58</v>
+        <v>581.54</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4">
-        <v>92.56000000000006</v>
+        <v>52.51999999999998</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -11090,11 +11090,11 @@
         <v>533.78</v>
       </c>
       <c r="C182" s="4">
-        <v>621.58</v>
+        <v>581.53</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4">
-        <v>87.80000000000007</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -11105,11 +11105,11 @@
         <v>534.59</v>
       </c>
       <c r="C183" s="4">
-        <v>621.65</v>
+        <v>581.6</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4">
-        <v>87.05999999999995</v>
+        <v>47.00999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -11120,11 +11120,11 @@
         <v>534.4</v>
       </c>
       <c r="C184" s="4">
-        <v>621.65</v>
+        <v>581.61</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4">
-        <v>87.25</v>
+        <v>47.21000000000004</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -11135,11 +11135,11 @@
         <v>540.34</v>
       </c>
       <c r="C185" s="4">
-        <v>621.7</v>
+        <v>581.65</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4">
-        <v>81.36000000000001</v>
+        <v>41.30999999999995</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -11150,11 +11150,11 @@
         <v>530.52</v>
       </c>
       <c r="C186" s="4">
-        <v>621.6799999999999</v>
+        <v>581.64</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4">
-        <v>91.15999999999997</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -11165,11 +11165,11 @@
         <v>527.79</v>
       </c>
       <c r="C187" s="4">
-        <v>621.97</v>
+        <v>581.9299999999999</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4">
-        <v>94.18000000000006</v>
+        <v>54.13999999999999</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -11180,11 +11180,11 @@
         <v>528.91</v>
       </c>
       <c r="C188" s="4">
-        <v>622.13</v>
+        <v>582.09</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4">
-        <v>93.22000000000003</v>
+        <v>53.18000000000006</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -11195,11 +11195,11 @@
         <v>527.42</v>
       </c>
       <c r="C189" s="4">
-        <v>622.26</v>
+        <v>582.23</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4">
-        <v>94.84000000000003</v>
+        <v>54.81000000000006</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -11210,11 +11210,11 @@
         <v>524.23</v>
       </c>
       <c r="C190" s="4">
-        <v>622.42</v>
+        <v>582.39</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4">
-        <v>98.18999999999994</v>
+        <v>58.15999999999997</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -11225,11 +11225,11 @@
         <v>523.47</v>
       </c>
       <c r="C191" s="4">
-        <v>622.83</v>
+        <v>582.8099999999999</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4">
-        <v>99.36000000000001</v>
+        <v>59.33999999999992</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -11240,11 +11240,11 @@
         <v>522.1</v>
       </c>
       <c r="C192" s="4">
-        <v>622.83</v>
+        <v>582.8099999999999</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4">
-        <v>100.73</v>
+        <v>60.70999999999992</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -11255,11 +11255,11 @@
         <v>519.59</v>
       </c>
       <c r="C193" s="4">
-        <v>623.0599999999999</v>
+        <v>583.05</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4">
-        <v>103.4699999999999</v>
+        <v>63.45999999999992</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -11270,11 +11270,11 @@
         <v>519.25</v>
       </c>
       <c r="C194" s="4">
-        <v>623.24</v>
+        <v>583.23</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4">
-        <v>103.99</v>
+        <v>63.98000000000002</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -11285,11 +11285,11 @@
         <v>523.4299999999999</v>
       </c>
       <c r="C195" s="4">
-        <v>623.37</v>
+        <v>583.37</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="4">
-        <v>99.94000000000005</v>
+        <v>59.94000000000005</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -11300,11 +11300,11 @@
         <v>520.83</v>
       </c>
       <c r="C196" s="4">
-        <v>623.45</v>
+        <v>583.45</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="4">
-        <v>102.62</v>
+        <v>62.62</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -11315,11 +11315,11 @@
         <v>516.33</v>
       </c>
       <c r="C197" s="4">
-        <v>623.47</v>
+        <v>583.47</v>
       </c>
       <c r="D197" s="4"/>
       <c r="E197" s="4">
-        <v>107.14</v>
+        <v>67.13999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -11330,11 +11330,11 @@
         <v>522.37</v>
       </c>
       <c r="C198" s="4">
-        <v>623.46</v>
+        <v>583.46</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4">
-        <v>101.09</v>
+        <v>61.09000000000003</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -11345,11 +11345,11 @@
         <v>520.47</v>
       </c>
       <c r="C199" s="4">
-        <v>623.5</v>
+        <v>583.5</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4">
-        <v>103.03</v>
+        <v>63.02999999999997</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -11360,11 +11360,11 @@
         <v>511.3</v>
       </c>
       <c r="C200" s="4">
-        <v>623.4</v>
+        <v>583.4</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="4">
-        <v>112.1</v>
+        <v>72.09999999999997</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -11375,11 +11375,11 @@
         <v>526.3099999999999</v>
       </c>
       <c r="C201" s="4">
-        <v>623.3200000000001</v>
+        <v>583.3200000000001</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="4">
-        <v>97.0100000000001</v>
+        <v>57.0100000000001</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -11390,11 +11390,11 @@
         <v>528.05</v>
       </c>
       <c r="C202" s="4">
-        <v>623.33</v>
+        <v>583.33</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="4">
-        <v>95.28000000000009</v>
+        <v>55.28000000000009</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -11405,11 +11405,11 @@
         <v>519.7</v>
       </c>
       <c r="C203" s="4">
-        <v>623.33</v>
+        <v>583.33</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4">
-        <v>103.63</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -11420,11 +11420,11 @@
         <v>515.02</v>
       </c>
       <c r="C204" s="4">
-        <v>623.45</v>
+        <v>583.45</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="4">
-        <v>108.4300000000001</v>
+        <v>68.43000000000006</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -11435,11 +11435,11 @@
         <v>507.89</v>
       </c>
       <c r="C205" s="4">
-        <v>623.4299999999999</v>
+        <v>583.4299999999999</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="4">
-        <v>115.54</v>
+        <v>75.53999999999996</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -11450,11 +11450,11 @@
         <v>517.1</v>
       </c>
       <c r="C206" s="4">
-        <v>623.39</v>
+        <v>583.39</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="4">
-        <v>106.29</v>
+        <v>66.28999999999996</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -11465,11 +11465,11 @@
         <v>518.53</v>
       </c>
       <c r="C207" s="4">
-        <v>623.46</v>
+        <v>583.46</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="4">
-        <v>104.9300000000001</v>
+        <v>64.93000000000006</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -11480,11 +11480,11 @@
         <v>517.33</v>
       </c>
       <c r="C208" s="4">
-        <v>623.38</v>
+        <v>583.38</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="4">
-        <v>106.05</v>
+        <v>66.04999999999995</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -11495,11 +11495,11 @@
         <v>506.08</v>
       </c>
       <c r="C209" s="4">
-        <v>623.39</v>
+        <v>583.39</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="4">
-        <v>117.31</v>
+        <v>77.31</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -11510,11 +11510,11 @@
         <v>503.14</v>
       </c>
       <c r="C210" s="4">
-        <v>623.4400000000001</v>
+        <v>583.4400000000001</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="4">
-        <v>120.3000000000001</v>
+        <v>80.30000000000007</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -11525,11 +11525,11 @@
         <v>522.75</v>
       </c>
       <c r="C211" s="4">
-        <v>623.47</v>
+        <v>583.47</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="4">
-        <v>100.72</v>
+        <v>60.72000000000003</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -11540,11 +11540,11 @@
         <v>531.48</v>
       </c>
       <c r="C212" s="4">
-        <v>623.49</v>
+        <v>583.49</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="4">
-        <v>92.00999999999999</v>
+        <v>52.00999999999999</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -11555,11 +11555,11 @@
         <v>515.45</v>
       </c>
       <c r="C213" s="4">
-        <v>623.4400000000001</v>
+        <v>583.4400000000001</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="4">
-        <v>107.99</v>
+        <v>67.99000000000001</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -11570,11 +11570,11 @@
         <v>518.5700000000001</v>
       </c>
       <c r="C214" s="4">
-        <v>623.41</v>
+        <v>583.41</v>
       </c>
       <c r="D214" s="4"/>
       <c r="E214" s="4">
-        <v>104.8399999999999</v>
+        <v>64.83999999999992</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -11585,11 +11585,11 @@
         <v>512.9299999999999</v>
       </c>
       <c r="C215" s="4">
-        <v>623.4</v>
+        <v>583.4</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="4">
-        <v>110.47</v>
+        <v>70.47000000000003</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -11600,11 +11600,11 @@
         <v>513.78</v>
       </c>
       <c r="C216" s="4">
-        <v>623.33</v>
+        <v>583.3200000000001</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="4">
-        <v>109.5500000000001</v>
+        <v>69.54000000000008</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -11615,11 +11615,11 @@
         <v>520.2</v>
       </c>
       <c r="C217" s="4">
-        <v>623.33</v>
+        <v>583.33</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="4">
-        <v>103.13</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -11630,11 +11630,11 @@
         <v>515.25</v>
       </c>
       <c r="C218" s="4">
-        <v>623.35</v>
+        <v>583.34</v>
       </c>
       <c r="D218" s="4"/>
       <c r="E218" s="4">
-        <v>108.1</v>
+        <v>68.09000000000003</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -11645,11 +11645,11 @@
         <v>532.75</v>
       </c>
       <c r="C219" s="4">
-        <v>623.26</v>
+        <v>583.26</v>
       </c>
       <c r="D219" s="4"/>
       <c r="E219" s="4">
-        <v>90.50999999999999</v>
+        <v>50.50999999999999</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -11660,11 +11660,11 @@
         <v>509.42</v>
       </c>
       <c r="C220" s="4">
-        <v>623.23</v>
+        <v>583.22</v>
       </c>
       <c r="D220" s="4"/>
       <c r="E220" s="4">
-        <v>113.81</v>
+        <v>73.80000000000001</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -11675,11 +11675,11 @@
         <v>506.23</v>
       </c>
       <c r="C221" s="4">
-        <v>623.1799999999999</v>
+        <v>583.1799999999999</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="4">
-        <v>116.9499999999999</v>
+        <v>76.94999999999993</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -11690,11 +11690,11 @@
         <v>515.0700000000001</v>
       </c>
       <c r="C222" s="4">
-        <v>623.25</v>
+        <v>583.24</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="4">
-        <v>108.1799999999999</v>
+        <v>68.16999999999996</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -11705,11 +11705,11 @@
         <v>522.3099999999999</v>
       </c>
       <c r="C223" s="4">
-        <v>623.17</v>
+        <v>583.16</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="4">
-        <v>100.86</v>
+        <v>60.85000000000002</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -11720,11 +11720,11 @@
         <v>511.2</v>
       </c>
       <c r="C224" s="4">
-        <v>623.03</v>
+        <v>583.02</v>
       </c>
       <c r="D224" s="4"/>
       <c r="E224" s="4">
-        <v>111.83</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -11735,11 +11735,11 @@
         <v>515.75</v>
       </c>
       <c r="C225" s="4">
-        <v>622.9400000000001</v>
+        <v>582.9299999999999</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="4">
-        <v>107.1900000000001</v>
+        <v>67.17999999999995</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -11750,11 +11750,11 @@
         <v>534.1</v>
       </c>
       <c r="C226" s="4">
-        <v>622.86</v>
+        <v>582.84</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="4">
-        <v>88.75999999999999</v>
+        <v>48.74000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -11765,11 +11765,11 @@
         <v>537.6</v>
       </c>
       <c r="C227" s="4">
-        <v>622.7</v>
+        <v>582.6799999999999</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="4">
-        <v>85.10000000000002</v>
+        <v>45.07999999999993</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -11780,11 +11780,11 @@
         <v>543.8099999999999</v>
       </c>
       <c r="C228" s="4">
-        <v>622.4400000000001</v>
+        <v>582.41</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="4">
-        <v>78.63000000000011</v>
+        <v>38.60000000000002</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -11795,11 +11795,11 @@
         <v>526.9400000000001</v>
       </c>
       <c r="C229" s="4">
-        <v>622.4</v>
+        <v>582.38</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4">
-        <v>95.45999999999992</v>
+        <v>55.43999999999994</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -11810,11 +11810,11 @@
         <v>527.36</v>
       </c>
       <c r="C230" s="4">
-        <v>622.3</v>
+        <v>582.28</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="4">
-        <v>94.93999999999994</v>
+        <v>54.91999999999996</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -11825,11 +11825,11 @@
         <v>557.2</v>
       </c>
       <c r="C231" s="4">
-        <v>622.25</v>
+        <v>582.22</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="4">
-        <v>65.04999999999995</v>
+        <v>25.01999999999998</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -11840,11 +11840,11 @@
         <v>563.1900000000001</v>
       </c>
       <c r="C232" s="4">
-        <v>622.11</v>
+        <v>582.08</v>
       </c>
       <c r="D232" s="4"/>
       <c r="E232" s="4">
-        <v>58.91999999999996</v>
+        <v>18.88999999999999</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -11855,11 +11855,11 @@
         <v>543.16</v>
       </c>
       <c r="C233" s="4">
-        <v>621.99</v>
+        <v>581.95</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4">
-        <v>78.83000000000004</v>
+        <v>38.79000000000008</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -11870,11 +11870,11 @@
         <v>539.25</v>
       </c>
       <c r="C234" s="4">
-        <v>621.96</v>
+        <v>581.92</v>
       </c>
       <c r="D234" s="4"/>
       <c r="E234" s="4">
-        <v>82.71000000000004</v>
+        <v>42.66999999999996</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -11885,11 +11885,11 @@
         <v>535.67</v>
       </c>
       <c r="C235" s="4">
-        <v>622.05</v>
+        <v>582.01</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="4">
-        <v>86.38</v>
+        <v>46.34000000000003</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -11900,11 +11900,11 @@
         <v>547.49</v>
       </c>
       <c r="C236" s="4">
-        <v>622.0599999999999</v>
+        <v>582.03</v>
       </c>
       <c r="D236" s="4"/>
       <c r="E236" s="4">
-        <v>74.56999999999994</v>
+        <v>34.53999999999996</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -11915,11 +11915,11 @@
         <v>544.87</v>
       </c>
       <c r="C237" s="4">
-        <v>622.0599999999999</v>
+        <v>582.03</v>
       </c>
       <c r="D237" s="4"/>
       <c r="E237" s="4">
-        <v>77.18999999999994</v>
+        <v>37.15999999999997</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -11930,11 +11930,11 @@
         <v>542.23</v>
       </c>
       <c r="C238" s="4">
-        <v>622.03</v>
+        <v>582</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="4">
-        <v>79.79999999999995</v>
+        <v>39.76999999999998</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -11945,11 +11945,11 @@
         <v>537.89</v>
       </c>
       <c r="C239" s="4">
-        <v>622</v>
+        <v>581.97</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4">
-        <v>84.11000000000001</v>
+        <v>44.08000000000004</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -11960,11 +11960,11 @@
         <v>546.01</v>
       </c>
       <c r="C240" s="4">
-        <v>621.98</v>
+        <v>581.95</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="4">
-        <v>75.97000000000003</v>
+        <v>35.94000000000005</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -11975,11 +11975,11 @@
         <v>552.5</v>
       </c>
       <c r="C241" s="4">
-        <v>622</v>
+        <v>581.96</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="4">
-        <v>69.5</v>
+        <v>29.46000000000004</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -11990,11 +11990,11 @@
         <v>549.96</v>
       </c>
       <c r="C242" s="4">
-        <v>622</v>
+        <v>581.97</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4">
-        <v>72.03999999999996</v>
+        <v>32.00999999999999</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -12005,11 +12005,11 @@
         <v>542.5</v>
       </c>
       <c r="C243" s="4">
-        <v>621.95</v>
+        <v>581.92</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="4">
-        <v>79.45000000000005</v>
+        <v>39.41999999999996</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -12020,11 +12020,11 @@
         <v>541.46</v>
       </c>
       <c r="C244" s="4">
-        <v>621.88</v>
+        <v>581.84</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="4">
-        <v>80.41999999999996</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -12035,11 +12035,11 @@
         <v>542.99</v>
       </c>
       <c r="C245" s="4">
-        <v>621.97</v>
+        <v>581.9299999999999</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="4">
-        <v>78.98000000000002</v>
+        <v>38.93999999999994</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -12050,11 +12050,11 @@
         <v>546.8</v>
       </c>
       <c r="C246" s="4">
-        <v>621.91</v>
+        <v>581.87</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="4">
-        <v>75.11000000000001</v>
+        <v>35.07000000000005</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -12065,11 +12065,11 @@
         <v>533.6</v>
       </c>
       <c r="C247" s="4">
-        <v>621.89</v>
+        <v>581.86</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4">
-        <v>88.28999999999996</v>
+        <v>48.25999999999999</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -12080,11 +12080,11 @@
         <v>531.33</v>
       </c>
       <c r="C248" s="4">
-        <v>621.73</v>
+        <v>581.6799999999999</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="4">
-        <v>90.39999999999998</v>
+        <v>50.34999999999991</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -12095,11 +12095,11 @@
         <v>543.8</v>
       </c>
       <c r="C249" s="4">
-        <v>621.5</v>
+        <v>581.45</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="4">
-        <v>77.70000000000005</v>
+        <v>37.65000000000009</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -12110,11 +12110,11 @@
         <v>547.6</v>
       </c>
       <c r="C250" s="4">
-        <v>621.29</v>
+        <v>581.24</v>
       </c>
       <c r="D250" s="4"/>
       <c r="E250" s="4">
-        <v>73.68999999999994</v>
+        <v>33.63999999999999</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -12125,11 +12125,11 @@
         <v>541.1</v>
       </c>
       <c r="C251" s="4">
-        <v>621.05</v>
+        <v>580.99</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="4">
-        <v>79.94999999999993</v>
+        <v>39.88999999999999</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -12140,11 +12140,11 @@
         <v>544.9</v>
       </c>
       <c r="C252" s="4">
-        <v>620.87</v>
+        <v>580.8</v>
       </c>
       <c r="D252" s="4"/>
       <c r="E252" s="4">
-        <v>75.97000000000003</v>
+        <v>35.89999999999998</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -12155,11 +12155,11 @@
         <v>545.14</v>
       </c>
       <c r="C253" s="4">
-        <v>620.74</v>
+        <v>580.6799999999999</v>
       </c>
       <c r="D253" s="4"/>
       <c r="E253" s="4">
-        <v>75.60000000000002</v>
+        <v>35.53999999999996</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -12170,11 +12170,11 @@
         <v>549.99</v>
       </c>
       <c r="C254" s="4">
-        <v>620.61</v>
+        <v>580.54</v>
       </c>
       <c r="D254" s="4"/>
       <c r="E254" s="4">
-        <v>70.62</v>
+        <v>30.54999999999995</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -12185,11 +12185,11 @@
         <v>539.5</v>
       </c>
       <c r="C255" s="4">
-        <v>620.48</v>
+        <v>580.41</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="4">
-        <v>80.98000000000002</v>
+        <v>40.90999999999997</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -12200,11 +12200,11 @@
         <v>543.2</v>
       </c>
       <c r="C256" s="4">
-        <v>620.3099999999999</v>
+        <v>580.23</v>
       </c>
       <c r="D256" s="4"/>
       <c r="E256" s="4">
-        <v>77.1099999999999</v>
+        <v>37.02999999999997</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -12215,11 +12215,11 @@
         <v>539</v>
       </c>
       <c r="C257" s="4">
-        <v>620.29</v>
+        <v>580.22</v>
       </c>
       <c r="D257" s="4"/>
       <c r="E257" s="4">
-        <v>81.28999999999996</v>
+        <v>41.22000000000003</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -12230,11 +12230,11 @@
         <v>537.9</v>
       </c>
       <c r="C258" s="4">
-        <v>620.1900000000001</v>
+        <v>580.11</v>
       </c>
       <c r="D258" s="4"/>
       <c r="E258" s="4">
-        <v>82.29000000000008</v>
+        <v>42.21000000000004</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -12245,11 +12245,11 @@
         <v>539.5</v>
       </c>
       <c r="C259" s="4">
-        <v>620.05</v>
+        <v>579.97</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="4">
-        <v>80.54999999999995</v>
+        <v>40.47000000000003</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -12260,11 +12260,11 @@
         <v>559</v>
       </c>
       <c r="C260" s="4">
-        <v>620</v>
+        <v>579.91</v>
       </c>
       <c r="D260" s="4"/>
       <c r="E260" s="4">
-        <v>61</v>
+        <v>20.90999999999997</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -12275,11 +12275,11 @@
         <v>552.1</v>
       </c>
       <c r="C261" s="4">
-        <v>619.9</v>
+        <v>579.8099999999999</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="4">
-        <v>67.79999999999995</v>
+        <v>27.70999999999992</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -12290,11 +12290,11 @@
         <v>548.5</v>
       </c>
       <c r="C262" s="4">
-        <v>619.83</v>
+        <v>579.74</v>
       </c>
       <c r="D262" s="4"/>
       <c r="E262" s="4">
-        <v>71.33000000000004</v>
+        <v>31.24000000000001</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -12305,11 +12305,11 @@
         <v>531.88</v>
       </c>
       <c r="C263" s="4">
-        <v>619.63</v>
+        <v>579.53</v>
       </c>
       <c r="D263" s="4"/>
       <c r="E263" s="4">
-        <v>87.75</v>
+        <v>47.64999999999998</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -12320,11 +12320,11 @@
         <v>529.3099999999999</v>
       </c>
       <c r="C264" s="4">
-        <v>619.45</v>
+        <v>579.35</v>
       </c>
       <c r="D264" s="4"/>
       <c r="E264" s="4">
-        <v>90.1400000000001</v>
+        <v>50.04000000000008</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -12335,11 +12335,11 @@
         <v>543.4</v>
       </c>
       <c r="C265" s="4">
-        <v>619.2</v>
+        <v>579.1</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4">
-        <v>75.80000000000007</v>
+        <v>35.70000000000005</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -12350,11 +12350,11 @@
         <v>532.77</v>
       </c>
       <c r="C266" s="4">
-        <v>618.85</v>
+        <v>578.73</v>
       </c>
       <c r="D266" s="4"/>
       <c r="E266" s="4">
-        <v>86.08000000000004</v>
+        <v>45.96000000000004</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -12365,11 +12365,11 @@
         <v>548.0700000000001</v>
       </c>
       <c r="C267" s="4">
-        <v>618.62</v>
+        <v>578.5</v>
       </c>
       <c r="D267" s="4"/>
       <c r="E267" s="4">
-        <v>70.54999999999995</v>
+        <v>30.42999999999995</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -12380,11 +12380,11 @@
         <v>541.3</v>
       </c>
       <c r="C268" s="4">
-        <v>618.35</v>
+        <v>578.22</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4">
-        <v>77.05000000000007</v>
+        <v>36.92000000000007</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -12395,11 +12395,11 @@
         <v>529.6</v>
       </c>
       <c r="C269" s="4">
-        <v>618</v>
+        <v>577.87</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="4">
-        <v>88.39999999999998</v>
+        <v>48.26999999999998</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -12410,11 +12410,11 @@
         <v>539.3200000000001</v>
       </c>
       <c r="C270" s="4">
-        <v>617.79</v>
+        <v>577.65</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4">
-        <v>78.46999999999991</v>
+        <v>38.32999999999993</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -12425,11 +12425,11 @@
         <v>534.4</v>
       </c>
       <c r="C271" s="4">
-        <v>617.51</v>
+        <v>577.36</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4">
-        <v>83.11000000000001</v>
+        <v>42.96000000000004</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -12440,11 +12440,11 @@
         <v>542.77</v>
       </c>
       <c r="C272" s="4">
-        <v>616.97</v>
+        <v>576.8</v>
       </c>
       <c r="D272" s="4"/>
       <c r="E272" s="4">
-        <v>74.20000000000005</v>
+        <v>34.02999999999997</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -12455,11 +12455,11 @@
         <v>546.29</v>
       </c>
       <c r="C273" s="4">
-        <v>616.58</v>
+        <v>576.41</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4">
-        <v>70.29000000000008</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -12470,11 +12470,11 @@
         <v>547.23</v>
       </c>
       <c r="C274" s="4">
-        <v>615.55</v>
+        <v>575.35</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4">
-        <v>68.31999999999994</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -12485,11 +12485,11 @@
         <v>545.83</v>
       </c>
       <c r="C275" s="4">
-        <v>614.78</v>
+        <v>574.5700000000001</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4">
-        <v>68.94999999999993</v>
+        <v>28.74000000000001</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -12500,11 +12500,11 @@
         <v>544.61</v>
       </c>
       <c r="C276" s="4">
-        <v>614.33</v>
+        <v>574.1</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4">
-        <v>69.72000000000003</v>
+        <v>29.49000000000001</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -12515,11 +12515,11 @@
         <v>537.1</v>
       </c>
       <c r="C277" s="4">
-        <v>613.79</v>
+        <v>573.55</v>
       </c>
       <c r="D277" s="4"/>
       <c r="E277" s="4">
-        <v>76.68999999999994</v>
+        <v>36.44999999999993</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -12530,11 +12530,11 @@
         <v>541.67</v>
       </c>
       <c r="C278" s="4">
-        <v>613.21</v>
+        <v>572.96</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4">
-        <v>71.54000000000008</v>
+        <v>31.29000000000008</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -12545,11 +12545,11 @@
         <v>552.25</v>
       </c>
       <c r="C279" s="4">
-        <v>613.02</v>
+        <v>572.76</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4">
-        <v>60.76999999999998</v>
+        <v>20.50999999999999</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -12560,11 +12560,11 @@
         <v>534.7</v>
       </c>
       <c r="C280" s="4">
-        <v>612.77</v>
+        <v>572.51</v>
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="4">
-        <v>78.06999999999994</v>
+        <v>37.80999999999995</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -12575,11 +12575,11 @@
         <v>524</v>
       </c>
       <c r="C281" s="4">
-        <v>612.61</v>
+        <v>572.34</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="4">
-        <v>88.61000000000001</v>
+        <v>48.34000000000003</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -12590,11 +12590,11 @@
         <v>529.7</v>
       </c>
       <c r="C282" s="4">
-        <v>612.51</v>
+        <v>572.24</v>
       </c>
       <c r="D282" s="4"/>
       <c r="E282" s="4">
-        <v>82.80999999999995</v>
+        <v>42.53999999999996</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -12605,11 +12605,11 @@
         <v>525.5</v>
       </c>
       <c r="C283" s="4">
-        <v>612.23</v>
+        <v>571.95</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4">
-        <v>86.73000000000002</v>
+        <v>46.45000000000005</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -12620,11 +12620,11 @@
         <v>530.59</v>
       </c>
       <c r="C284" s="4">
-        <v>611.9</v>
+        <v>571.61</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4">
-        <v>81.30999999999995</v>
+        <v>41.01999999999998</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -12635,11 +12635,11 @@
         <v>542.4</v>
       </c>
       <c r="C285" s="4">
-        <v>611.71</v>
+        <v>571.42</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4">
-        <v>69.31000000000006</v>
+        <v>29.01999999999998</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -12650,11 +12650,11 @@
         <v>538.35</v>
       </c>
       <c r="C286" s="4">
-        <v>611.41</v>
+        <v>571.11</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4">
-        <v>73.05999999999995</v>
+        <v>32.75999999999999</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -12665,11 +12665,11 @@
         <v>540.8</v>
       </c>
       <c r="C287" s="4">
-        <v>611.28</v>
+        <v>570.97</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4">
-        <v>70.48000000000002</v>
+        <v>30.17000000000007</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -12680,11 +12680,11 @@
         <v>535.04</v>
       </c>
       <c r="C288" s="4">
-        <v>611</v>
+        <v>570.6900000000001</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4">
-        <v>75.96000000000004</v>
+        <v>35.65000000000009</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -12695,11 +12695,11 @@
         <v>547.72</v>
       </c>
       <c r="C289" s="4">
-        <v>610.9</v>
+        <v>570.59</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4">
-        <v>63.17999999999995</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -12710,11 +12710,11 @@
         <v>531.36</v>
       </c>
       <c r="C290" s="4">
-        <v>610.71</v>
+        <v>570.39</v>
       </c>
       <c r="D290" s="4"/>
       <c r="E290" s="4">
-        <v>79.35000000000002</v>
+        <v>39.02999999999997</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -12725,11 +12725,11 @@
         <v>534.1799999999999</v>
       </c>
       <c r="C291" s="4">
-        <v>610.5599999999999</v>
+        <v>570.24</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4">
-        <v>76.38</v>
+        <v>36.06000000000006</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -12740,11 +12740,11 @@
         <v>550.66</v>
       </c>
       <c r="C292" s="4">
-        <v>610.3</v>
+        <v>569.97</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4">
-        <v>59.63999999999999</v>
+        <v>19.31000000000006</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -12755,11 +12755,11 @@
         <v>530</v>
       </c>
       <c r="C293" s="4">
-        <v>610.03</v>
+        <v>569.6900000000001</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4">
-        <v>80.02999999999997</v>
+        <v>39.69000000000005</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -12770,11 +12770,11 @@
         <v>528.47</v>
       </c>
       <c r="C294" s="4">
-        <v>609.79</v>
+        <v>569.45</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4">
-        <v>81.31999999999994</v>
+        <v>40.98000000000002</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -12785,11 +12785,11 @@
         <v>540.89</v>
       </c>
       <c r="C295" s="4">
-        <v>609.46</v>
+        <v>569.12</v>
       </c>
       <c r="D295" s="4"/>
       <c r="E295" s="4">
-        <v>68.57000000000005</v>
+        <v>28.23000000000002</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -12800,11 +12800,11 @@
         <v>538</v>
       </c>
       <c r="C296" s="4">
-        <v>609.28</v>
+        <v>568.92</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4">
-        <v>71.27999999999997</v>
+        <v>30.91999999999996</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -12815,11 +12815,11 @@
         <v>530.6</v>
       </c>
       <c r="C297" s="4">
-        <v>609.13</v>
+        <v>568.78</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4">
-        <v>78.52999999999997</v>
+        <v>38.17999999999995</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -12830,11 +12830,11 @@
         <v>537.77</v>
       </c>
       <c r="C298" s="4">
-        <v>608.96</v>
+        <v>568.6</v>
       </c>
       <c r="D298" s="4"/>
       <c r="E298" s="4">
-        <v>71.19000000000005</v>
+        <v>30.83000000000004</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -12845,11 +12845,11 @@
         <v>539.3</v>
       </c>
       <c r="C299" s="4">
-        <v>608.8</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="D299" s="4"/>
       <c r="E299" s="4">
-        <v>69.5</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -12860,11 +12860,11 @@
         <v>516.83</v>
       </c>
       <c r="C300" s="4">
-        <v>608.35</v>
+        <v>567.97</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="4">
-        <v>91.51999999999998</v>
+        <v>51.13999999999999</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -12875,11 +12875,11 @@
         <v>517.2</v>
       </c>
       <c r="C301" s="4">
-        <v>607.88</v>
+        <v>567.49</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4">
-        <v>90.67999999999995</v>
+        <v>50.28999999999996</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -12890,11 +12890,11 @@
         <v>518.4</v>
       </c>
       <c r="C302" s="4">
-        <v>607.4400000000001</v>
+        <v>567.04</v>
       </c>
       <c r="D302" s="4"/>
       <c r="E302" s="4">
-        <v>89.04000000000008</v>
+        <v>48.63999999999999</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -12905,11 +12905,11 @@
         <v>535.29</v>
       </c>
       <c r="C303" s="4">
-        <v>607.01</v>
+        <v>566.6</v>
       </c>
       <c r="D303" s="4"/>
       <c r="E303" s="4">
-        <v>71.72000000000003</v>
+        <v>31.31000000000006</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -12920,11 +12920,11 @@
         <v>528.74</v>
       </c>
       <c r="C304" s="4">
-        <v>606.37</v>
+        <v>565.95</v>
       </c>
       <c r="D304" s="4"/>
       <c r="E304" s="4">
-        <v>77.63</v>
+        <v>37.21000000000004</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -12935,11 +12935,11 @@
         <v>566.9</v>
       </c>
       <c r="C305" s="4">
-        <v>606.29</v>
+        <v>565.86</v>
       </c>
       <c r="D305" s="4"/>
       <c r="E305" s="4">
-        <v>39.38999999999999</v>
+        <v>-1.039999999999964</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -12950,11 +12950,11 @@
         <v>549.6</v>
       </c>
       <c r="C306" s="4">
-        <v>605.96</v>
+        <v>565.53</v>
       </c>
       <c r="D306" s="4"/>
       <c r="E306" s="4">
-        <v>56.36000000000001</v>
+        <v>15.92999999999995</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -12965,11 +12965,11 @@
         <v>569.95</v>
       </c>
       <c r="C307" s="4">
-        <v>605.77</v>
+        <v>565.33</v>
       </c>
       <c r="D307" s="4"/>
       <c r="E307" s="4">
-        <v>35.81999999999994</v>
+        <v>-4.620000000000005</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -12980,11 +12980,11 @@
         <v>544.4400000000001</v>
       </c>
       <c r="C308" s="4">
-        <v>605.5700000000001</v>
+        <v>565.12</v>
       </c>
       <c r="D308" s="4"/>
       <c r="E308" s="4">
-        <v>61.13</v>
+        <v>20.67999999999995</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -12995,11 +12995,11 @@
         <v>533.6900000000001</v>
       </c>
       <c r="C309" s="4">
-        <v>605.67</v>
+        <v>565.23</v>
       </c>
       <c r="D309" s="4"/>
       <c r="E309" s="4">
-        <v>71.9799999999999</v>
+        <v>31.53999999999996</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -13010,11 +13010,11 @@
         <v>546.75</v>
       </c>
       <c r="C310" s="4">
-        <v>605.87</v>
+        <v>565.4299999999999</v>
       </c>
       <c r="D310" s="4"/>
       <c r="E310" s="4">
-        <v>59.12</v>
+        <v>18.67999999999995</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -13025,11 +13025,11 @@
         <v>563.9</v>
       </c>
       <c r="C311" s="4">
-        <v>605.9</v>
+        <v>565.46</v>
       </c>
       <c r="D311" s="4"/>
       <c r="E311" s="4">
-        <v>42</v>
+        <v>1.560000000000059</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -13040,11 +13040,11 @@
         <v>558.04</v>
       </c>
       <c r="C312" s="4">
-        <v>606</v>
+        <v>565.5700000000001</v>
       </c>
       <c r="D312" s="4"/>
       <c r="E312" s="4">
-        <v>47.96000000000004</v>
+        <v>7.530000000000086</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -13055,11 +13055,11 @@
         <v>562.8</v>
       </c>
       <c r="C313" s="4">
-        <v>605.92</v>
+        <v>565.48</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4">
-        <v>43.12</v>
+        <v>2.680000000000064</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -13070,11 +13070,11 @@
         <v>574.17</v>
       </c>
       <c r="C314" s="4">
-        <v>605.8</v>
+        <v>565.35</v>
       </c>
       <c r="D314" s="4"/>
       <c r="E314" s="4">
-        <v>31.63</v>
+        <v>-8.819999999999936</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -13085,11 +13085,11 @@
         <v>522.64</v>
       </c>
       <c r="C315" s="4">
-        <v>606.08</v>
+        <v>565.64</v>
       </c>
       <c r="D315" s="4"/>
       <c r="E315" s="4">
-        <v>83.44000000000005</v>
+        <v>43</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -13100,11 +13100,11 @@
         <v>554.36</v>
       </c>
       <c r="C316" s="4">
-        <v>606.24</v>
+        <v>565.8099999999999</v>
       </c>
       <c r="D316" s="4"/>
       <c r="E316" s="4">
-        <v>51.88</v>
+        <v>11.44999999999993</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -13115,11 +13115,11 @@
         <v>564.3</v>
       </c>
       <c r="C317" s="4">
-        <v>606.33</v>
+        <v>565.91</v>
       </c>
       <c r="D317" s="4"/>
       <c r="E317" s="4">
-        <v>42.03000000000009</v>
+        <v>1.610000000000014</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -13130,11 +13130,11 @@
         <v>555.75</v>
       </c>
       <c r="C318" s="4">
-        <v>606.3200000000001</v>
+        <v>565.89</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4">
-        <v>50.57000000000005</v>
+        <v>10.13999999999999</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -13145,11 +13145,11 @@
         <v>553.1</v>
       </c>
       <c r="C319" s="4">
-        <v>606.4299999999999</v>
+        <v>566</v>
       </c>
       <c r="D319" s="4"/>
       <c r="E319" s="4">
-        <v>53.32999999999993</v>
+        <v>12.89999999999998</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -13160,11 +13160,11 @@
         <v>563.1799999999999</v>
       </c>
       <c r="C320" s="4">
-        <v>606.91</v>
+        <v>566.5</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4">
-        <v>43.73000000000002</v>
+        <v>3.32000000000005</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -13175,11 +13175,11 @@
         <v>574.96</v>
       </c>
       <c r="C321" s="4">
-        <v>607.17</v>
+        <v>566.76</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4">
-        <v>32.20999999999992</v>
+        <v>-8.200000000000045</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -13190,11 +13190,11 @@
         <v>564.92</v>
       </c>
       <c r="C322" s="4">
-        <v>607.38</v>
+        <v>566.98</v>
       </c>
       <c r="D322" s="4"/>
       <c r="E322" s="4">
-        <v>42.46000000000004</v>
+        <v>2.060000000000059</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -13205,11 +13205,11 @@
         <v>559.13</v>
       </c>
       <c r="C323" s="4">
-        <v>607.53</v>
+        <v>567.14</v>
       </c>
       <c r="D323" s="4"/>
       <c r="E323" s="4">
-        <v>48.39999999999998</v>
+        <v>8.009999999999991</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -13220,11 +13220,11 @@
         <v>576.84</v>
       </c>
       <c r="C324" s="4">
-        <v>607.74</v>
+        <v>567.35</v>
       </c>
       <c r="D324" s="4"/>
       <c r="E324" s="4">
-        <v>30.89999999999998</v>
+        <v>-9.490000000000009</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -13235,11 +13235,11 @@
         <v>564.8</v>
       </c>
       <c r="C325" s="4">
-        <v>608.1900000000001</v>
+        <v>567.8</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4">
-        <v>43.3900000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -13250,11 +13250,11 @@
         <v>555.1</v>
       </c>
       <c r="C326" s="4">
-        <v>608.54</v>
+        <v>568.17</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4">
-        <v>53.43999999999994</v>
+        <v>13.06999999999994</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -13265,11 +13265,11 @@
         <v>549.2</v>
       </c>
       <c r="C327" s="4">
-        <v>608.84</v>
+        <v>568.48</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4">
-        <v>59.63999999999999</v>
+        <v>19.27999999999997</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -13280,11 +13280,11 @@
         <v>565.77</v>
       </c>
       <c r="C328" s="4">
-        <v>609.24</v>
+        <v>568.88</v>
       </c>
       <c r="D328" s="4"/>
       <c r="E328" s="4">
-        <v>43.47000000000003</v>
+        <v>3.110000000000014</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -13295,11 +13295,11 @@
         <v>543.7</v>
       </c>
       <c r="C329" s="4">
-        <v>609.36</v>
+        <v>569.01</v>
       </c>
       <c r="D329" s="4"/>
       <c r="E329" s="4">
-        <v>65.65999999999997</v>
+        <v>25.30999999999995</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -13310,11 +13310,11 @@
         <v>572.3200000000001</v>
       </c>
       <c r="C330" s="4">
-        <v>609.6900000000001</v>
+        <v>569.34</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4">
-        <v>37.37</v>
+        <v>-2.980000000000018</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -13325,11 +13325,11 @@
         <v>583.72</v>
       </c>
       <c r="C331" s="4">
-        <v>610.0599999999999</v>
+        <v>569.72</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4">
-        <v>26.33999999999992</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -13340,11 +13340,11 @@
         <v>564.98</v>
       </c>
       <c r="C332" s="4">
-        <v>610.38</v>
+        <v>570.0599999999999</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4">
-        <v>45.39999999999998</v>
+        <v>5.079999999999927</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -13355,11 +13355,11 @@
         <v>526.2</v>
       </c>
       <c r="C333" s="4">
-        <v>610.99</v>
+        <v>570.6799999999999</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="4">
-        <v>84.78999999999996</v>
+        <v>44.4799999999999</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -13370,11 +13370,11 @@
         <v>552.52</v>
       </c>
       <c r="C334" s="4">
-        <v>611.02</v>
+        <v>570.71</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4">
-        <v>58.5</v>
+        <v>18.19000000000005</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -13385,11 +13385,11 @@
         <v>559.13</v>
       </c>
       <c r="C335" s="4">
-        <v>611.5599999999999</v>
+        <v>571.26</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4">
-        <v>52.42999999999995</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -13400,11 +13400,11 @@
         <v>538.6</v>
       </c>
       <c r="C336" s="4">
-        <v>611.53</v>
+        <v>571.23</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="4">
-        <v>72.92999999999995</v>
+        <v>32.63</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -13415,11 +13415,11 @@
         <v>545.38</v>
       </c>
       <c r="C337" s="4">
-        <v>612.09</v>
+        <v>571.8</v>
       </c>
       <c r="D337" s="4"/>
       <c r="E337" s="4">
-        <v>66.71000000000004</v>
+        <v>26.41999999999996</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -13430,11 +13430,11 @@
         <v>536.16</v>
       </c>
       <c r="C338" s="4">
-        <v>612.5700000000001</v>
+        <v>572.3</v>
       </c>
       <c r="D338" s="4"/>
       <c r="E338" s="4">
-        <v>76.41000000000008</v>
+        <v>36.13999999999999</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -13445,11 +13445,11 @@
         <v>538.36</v>
       </c>
       <c r="C339" s="4">
-        <v>613.12</v>
+        <v>572.86</v>
       </c>
       <c r="D339" s="4"/>
       <c r="E339" s="4">
-        <v>74.75999999999999</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -13460,11 +13460,11 @@
         <v>535.9</v>
       </c>
       <c r="C340" s="4">
-        <v>613.65</v>
+        <v>573.4</v>
       </c>
       <c r="D340" s="4"/>
       <c r="E340" s="4">
-        <v>77.75</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -13475,11 +13475,11 @@
         <v>526.1900000000001</v>
       </c>
       <c r="C341" s="4">
-        <v>614.02</v>
+        <v>573.78</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4">
-        <v>87.82999999999993</v>
+        <v>47.58999999999992</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -13490,11 +13490,11 @@
         <v>528.8</v>
       </c>
       <c r="C342" s="4">
-        <v>614.5599999999999</v>
+        <v>574.34</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4">
-        <v>85.75999999999999</v>
+        <v>45.54000000000008</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -13505,11 +13505,11 @@
         <v>532.75</v>
       </c>
       <c r="C343" s="4">
-        <v>615.13</v>
+        <v>574.9299999999999</v>
       </c>
       <c r="D343" s="4"/>
       <c r="E343" s="4">
-        <v>82.38</v>
+        <v>42.17999999999995</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -13520,11 +13520,11 @@
         <v>529.2</v>
       </c>
       <c r="C344" s="4">
-        <v>615.58</v>
+        <v>575.39</v>
       </c>
       <c r="D344" s="4"/>
       <c r="E344" s="4">
-        <v>86.38</v>
+        <v>46.18999999999994</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -13535,11 +13535,11 @@
         <v>542.58</v>
       </c>
       <c r="C345" s="4">
-        <v>616.09</v>
+        <v>575.91</v>
       </c>
       <c r="D345" s="4"/>
       <c r="E345" s="4">
-        <v>73.50999999999999</v>
+        <v>33.32999999999993</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -13550,11 +13550,11 @@
         <v>536.42</v>
       </c>
       <c r="C346" s="4">
-        <v>616.59</v>
+        <v>576.42</v>
       </c>
       <c r="D346" s="4"/>
       <c r="E346" s="4">
-        <v>80.17000000000007</v>
+        <v>40</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -13565,11 +13565,11 @@
         <v>518.1</v>
       </c>
       <c r="C347" s="4">
-        <v>617.0700000000001</v>
+        <v>576.91</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4">
-        <v>98.97000000000003</v>
+        <v>58.80999999999995</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -13580,11 +13580,11 @@
         <v>536.14</v>
       </c>
       <c r="C348" s="4">
-        <v>617.16</v>
+        <v>577</v>
       </c>
       <c r="D348" s="4"/>
       <c r="E348" s="4">
-        <v>81.01999999999998</v>
+        <v>40.86000000000001</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -13595,11 +13595,11 @@
         <v>532.3</v>
       </c>
       <c r="C349" s="4">
-        <v>617.46</v>
+        <v>577.3099999999999</v>
       </c>
       <c r="D349" s="4"/>
       <c r="E349" s="4">
-        <v>85.16000000000008</v>
+        <v>45.00999999999999</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -13610,11 +13610,11 @@
         <v>525.8099999999999</v>
       </c>
       <c r="C350" s="4">
-        <v>618.05</v>
+        <v>577.92</v>
       </c>
       <c r="D350" s="4"/>
       <c r="E350" s="4">
-        <v>92.24000000000001</v>
+        <v>52.11000000000001</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -13625,11 +13625,11 @@
         <v>532.6</v>
       </c>
       <c r="C351" s="4">
-        <v>618.51</v>
+        <v>578.39</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4">
-        <v>85.90999999999997</v>
+        <v>45.78999999999996</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -13640,11 +13640,11 @@
         <v>541.84</v>
       </c>
       <c r="C352" s="4">
-        <v>619</v>
+        <v>578.89</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4">
-        <v>77.15999999999997</v>
+        <v>37.04999999999995</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -13655,11 +13655,11 @@
         <v>524.8</v>
       </c>
       <c r="C353" s="4">
-        <v>619.53</v>
+        <v>579.4299999999999</v>
       </c>
       <c r="D353" s="4"/>
       <c r="E353" s="4">
-        <v>94.73000000000002</v>
+        <v>54.63</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -13670,11 +13670,11 @@
         <v>539.0700000000001</v>
       </c>
       <c r="C354" s="4">
-        <v>620.41</v>
+        <v>580.33</v>
       </c>
       <c r="D354" s="4"/>
       <c r="E354" s="4">
-        <v>81.33999999999992</v>
+        <v>41.25999999999999</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -13685,11 +13685,11 @@
         <v>521.5</v>
       </c>
       <c r="C355" s="4">
-        <v>621.38</v>
+        <v>581.33</v>
       </c>
       <c r="D355" s="4"/>
       <c r="E355" s="4">
-        <v>99.88</v>
+        <v>59.83000000000004</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -13700,11 +13700,11 @@
         <v>520</v>
       </c>
       <c r="C356" s="4">
-        <v>622.17</v>
+        <v>582.14</v>
       </c>
       <c r="D356" s="4"/>
       <c r="E356" s="4">
-        <v>102.17</v>
+        <v>62.13999999999999</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -13715,11 +13715,11 @@
         <v>543.87</v>
       </c>
       <c r="C357" s="4">
-        <v>623.09</v>
+        <v>583.08</v>
       </c>
       <c r="D357" s="4"/>
       <c r="E357" s="4">
-        <v>79.22000000000003</v>
+        <v>39.21000000000004</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -13730,11 +13730,11 @@
         <v>525.2</v>
       </c>
       <c r="C358" s="4">
-        <v>623.91</v>
+        <v>583.92</v>
       </c>
       <c r="D358" s="4"/>
       <c r="E358" s="4">
-        <v>98.70999999999992</v>
+        <v>58.71999999999991</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -13745,11 +13745,11 @@
         <v>520.8</v>
       </c>
       <c r="C359" s="4">
-        <v>624.72</v>
+        <v>584.76</v>
       </c>
       <c r="D359" s="4"/>
       <c r="E359" s="4">
-        <v>103.9200000000001</v>
+        <v>63.96000000000004</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -13760,11 +13760,11 @@
         <v>529.9</v>
       </c>
       <c r="C360" s="4">
-        <v>625.55</v>
+        <v>585.6</v>
       </c>
       <c r="D360" s="4"/>
       <c r="E360" s="4">
-        <v>95.64999999999998</v>
+        <v>55.70000000000005</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -13775,11 +13775,11 @@
         <v>526.8099999999999</v>
       </c>
       <c r="C361" s="4">
-        <v>626.3099999999999</v>
+        <v>586.39</v>
       </c>
       <c r="D361" s="4"/>
       <c r="E361" s="4">
-        <v>99.5</v>
+        <v>59.58000000000004</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -13790,11 +13790,11 @@
         <v>529.89</v>
       </c>
       <c r="C362" s="4">
-        <v>627.08</v>
+        <v>587.17</v>
       </c>
       <c r="D362" s="4"/>
       <c r="E362" s="4">
-        <v>97.19000000000005</v>
+        <v>57.27999999999997</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -13805,11 +13805,11 @@
         <v>474.05</v>
       </c>
       <c r="C363" s="4">
-        <v>627.92</v>
+        <v>588.03</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4">
-        <v>153.8699999999999</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -13820,11 +13820,11 @@
         <v>516.26</v>
       </c>
       <c r="C364" s="4">
-        <v>628.6799999999999</v>
+        <v>588.8099999999999</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4">
-        <v>112.42</v>
+        <v>72.54999999999995</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -13835,11 +13835,11 @@
         <v>521.4</v>
       </c>
       <c r="C365" s="4">
-        <v>629.42</v>
+        <v>589.5700000000001</v>
       </c>
       <c r="D365" s="4"/>
       <c r="E365" s="4">
-        <v>108.02</v>
+        <v>68.17000000000007</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -13850,11 +13850,11 @@
         <v>521.12</v>
       </c>
       <c r="C366" s="4">
-        <v>630.37</v>
+        <v>590.55</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4">
-        <v>109.25</v>
+        <v>69.42999999999995</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -13865,11 +13865,11 @@
         <v>534.4</v>
       </c>
       <c r="C367" s="4">
-        <v>630.87</v>
+        <v>591.0599999999999</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4">
-        <v>96.47000000000003</v>
+        <v>56.65999999999997</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -13880,11 +13880,11 @@
         <v>477.5</v>
       </c>
       <c r="C368" s="4">
-        <v>631.83</v>
+        <v>592.04</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4">
-        <v>154.33</v>
+        <v>114.54</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -13895,11 +13895,11 @@
         <v>496.55</v>
       </c>
       <c r="C369" s="4">
-        <v>632.66</v>
+        <v>592.89</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4">
-        <v>136.11</v>
+        <v>96.33999999999997</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -13910,11 +13910,11 @@
         <v>531.2</v>
       </c>
       <c r="C370" s="4">
-        <v>633.15</v>
+        <v>593.39</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4">
-        <v>101.9499999999999</v>
+        <v>62.18999999999994</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -13925,11 +13925,11 @@
         <v>524.2</v>
       </c>
       <c r="C371" s="4">
-        <v>634.04</v>
+        <v>594.3099999999999</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4">
-        <v>109.8399999999999</v>
+        <v>70.1099999999999</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -13940,11 +13940,11 @@
         <v>526.4</v>
       </c>
       <c r="C372" s="4">
-        <v>634.71</v>
+        <v>594.99</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4">
-        <v>108.3100000000001</v>
+        <v>68.59000000000003</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -13955,11 +13955,11 @@
         <v>528.6</v>
       </c>
       <c r="C373" s="4">
-        <v>635.48</v>
+        <v>595.78</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4">
-        <v>106.88</v>
+        <v>67.17999999999995</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -13970,11 +13970,11 @@
         <v>529</v>
       </c>
       <c r="C374" s="4">
-        <v>637.04</v>
+        <v>597.38</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4">
-        <v>108.04</v>
+        <v>68.38</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -13985,11 +13985,11 @@
         <v>527.1</v>
       </c>
       <c r="C375" s="4">
-        <v>638.21</v>
+        <v>598.58</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4">
-        <v>111.11</v>
+        <v>71.48000000000002</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -14000,11 +14000,11 @@
         <v>527.3</v>
       </c>
       <c r="C376" s="4">
-        <v>638.99</v>
+        <v>599.38</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4">
-        <v>111.6900000000001</v>
+        <v>72.08000000000004</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -14015,11 +14015,11 @@
         <v>534.35</v>
       </c>
       <c r="C377" s="4">
-        <v>640.34</v>
+        <v>600.76</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4">
-        <v>105.99</v>
+        <v>66.40999999999997</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -14030,11 +14030,11 @@
         <v>542.6</v>
       </c>
       <c r="C378" s="4">
-        <v>641.3</v>
+        <v>601.75</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4">
-        <v>98.69999999999993</v>
+        <v>59.14999999999998</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -14045,11 +14045,11 @@
         <v>537.98</v>
       </c>
       <c r="C379" s="4">
-        <v>642.55</v>
+        <v>603.03</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4">
-        <v>104.5699999999999</v>
+        <v>65.04999999999995</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -14060,11 +14060,11 @@
         <v>536.08</v>
       </c>
       <c r="C380" s="4">
-        <v>643.98</v>
+        <v>604.5</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4">
-        <v>107.9</v>
+        <v>68.41999999999996</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -14075,11 +14075,11 @@
         <v>543.76</v>
       </c>
       <c r="C381" s="4">
-        <v>645.15</v>
+        <v>605.7</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4">
-        <v>101.39</v>
+        <v>61.94000000000005</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -14090,11 +14090,11 @@
         <v>531.3</v>
       </c>
       <c r="C382" s="4">
-        <v>646.4400000000001</v>
+        <v>607.02</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4">
-        <v>115.1400000000001</v>
+        <v>75.72000000000003</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -14105,11 +14105,11 @@
         <v>535.1</v>
       </c>
       <c r="C383" s="4">
-        <v>647.67</v>
+        <v>608.27</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4">
-        <v>112.5699999999999</v>
+        <v>73.16999999999996</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -14120,11 +14120,11 @@
         <v>537.9</v>
       </c>
       <c r="C384" s="4">
-        <v>649</v>
+        <v>609.64</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4">
-        <v>111.1</v>
+        <v>71.74000000000001</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -14135,11 +14135,11 @@
         <v>528.9</v>
       </c>
       <c r="C385" s="4">
-        <v>650.52</v>
+        <v>611.1900000000001</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4">
-        <v>121.62</v>
+        <v>82.29000000000008</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -14150,11 +14150,11 @@
         <v>559.35</v>
       </c>
       <c r="C386" s="4">
-        <v>652.03</v>
+        <v>612.75</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4">
-        <v>92.67999999999995</v>
+        <v>53.39999999999998</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -14165,11 +14165,11 @@
         <v>531.33</v>
       </c>
       <c r="C387" s="4">
-        <v>653.49</v>
+        <v>614.24</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4">
-        <v>122.16</v>
+        <v>82.90999999999997</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -14180,11 +14180,11 @@
         <v>552.61</v>
       </c>
       <c r="C388" s="4">
-        <v>654.96</v>
+        <v>615.75</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4">
-        <v>102.35</v>
+        <v>63.13999999999999</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -14195,11 +14195,11 @@
         <v>540.1</v>
       </c>
       <c r="C389" s="4">
-        <v>656.6</v>
+        <v>617.4299999999999</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4">
-        <v>116.5</v>
+        <v>77.32999999999993</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -14210,11 +14210,11 @@
         <v>533.55</v>
       </c>
       <c r="C390" s="4">
-        <v>658.27</v>
+        <v>619.14</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4">
-        <v>124.72</v>
+        <v>85.59000000000003</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -14225,11 +14225,11 @@
         <v>546.97</v>
       </c>
       <c r="C391" s="4">
-        <v>659.99</v>
+        <v>620.91</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4">
-        <v>113.02</v>
+        <v>73.93999999999994</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -14240,11 +14240,11 @@
         <v>540.79</v>
       </c>
       <c r="C392" s="4">
-        <v>661.4400000000001</v>
+        <v>622.39</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4">
-        <v>120.6500000000001</v>
+        <v>81.60000000000002</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -14255,11 +14255,11 @@
         <v>549.67</v>
       </c>
       <c r="C393" s="4">
-        <v>663.03</v>
+        <v>624.02</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4">
-        <v>113.36</v>
+        <v>74.35000000000002</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -14270,11 +14270,11 @@
         <v>527.46</v>
       </c>
       <c r="C394" s="4">
-        <v>664.28</v>
+        <v>625.3</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4">
-        <v>136.8199999999999</v>
+        <v>97.83999999999992</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -14285,11 +14285,11 @@
         <v>521.01</v>
       </c>
       <c r="C395" s="4">
-        <v>665.98</v>
+        <v>627.04</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4">
-        <v>144.97</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -14300,11 +14300,11 @@
         <v>518.24</v>
       </c>
       <c r="C396" s="4">
-        <v>666.92</v>
+        <v>628.01</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4">
-        <v>148.6799999999999</v>
+        <v>109.77</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -14315,11 +14315,11 @@
         <v>528.67</v>
       </c>
       <c r="C397" s="4">
-        <v>668.1</v>
+        <v>629.22</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4">
-        <v>139.4300000000001</v>
+        <v>100.5500000000001</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -14330,11 +14330,11 @@
         <v>522.5</v>
       </c>
       <c r="C398" s="4">
-        <v>668.59</v>
+        <v>629.72</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4">
-        <v>146.09</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -14345,11 +14345,11 @@
         <v>520.67</v>
       </c>
       <c r="C399" s="4">
-        <v>669.22</v>
+        <v>630.37</v>
       </c>
       <c r="D399" s="4"/>
       <c r="E399" s="4">
-        <v>148.5500000000001</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -14360,11 +14360,11 @@
         <v>529.48</v>
       </c>
       <c r="C400" s="4">
-        <v>669.72</v>
+        <v>630.88</v>
       </c>
       <c r="D400" s="4"/>
       <c r="E400" s="4">
-        <v>140.24</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -14375,11 +14375,11 @@
         <v>529.42</v>
       </c>
       <c r="C401" s="4">
-        <v>670.38</v>
+        <v>631.5599999999999</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4">
-        <v>140.96</v>
+        <v>102.14</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -14390,11 +14390,11 @@
         <v>534.4</v>
       </c>
       <c r="C402" s="4">
-        <v>671.01</v>
+        <v>632.2</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4">
-        <v>136.61</v>
+        <v>97.80000000000007</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -14405,11 +14405,11 @@
         <v>537.8099999999999</v>
       </c>
       <c r="C403" s="4">
-        <v>671.25</v>
+        <v>632.45</v>
       </c>
       <c r="D403" s="4"/>
       <c r="E403" s="4">
-        <v>133.4400000000001</v>
+        <v>94.6400000000001</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -14420,11 +14420,11 @@
         <v>534.02</v>
       </c>
       <c r="C404" s="4">
-        <v>671.6799999999999</v>
+        <v>632.89</v>
       </c>
       <c r="D404" s="4"/>
       <c r="E404" s="4">
-        <v>137.66</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -14435,11 +14435,11 @@
         <v>534.0700000000001</v>
       </c>
       <c r="C405" s="4">
-        <v>672.4400000000001</v>
+        <v>633.67</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="4">
-        <v>138.37</v>
+        <v>99.59999999999991</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -14450,11 +14450,11 @@
         <v>533.35</v>
       </c>
       <c r="C406" s="4">
-        <v>672.91</v>
+        <v>634.15</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4">
-        <v>139.5599999999999</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -14465,11 +14465,11 @@
         <v>539.92</v>
       </c>
       <c r="C407" s="4">
-        <v>673.4</v>
+        <v>634.65</v>
       </c>
       <c r="D407" s="4"/>
       <c r="E407" s="4">
-        <v>133.48</v>
+        <v>94.73000000000002</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -14480,11 +14480,11 @@
         <v>504.5</v>
       </c>
       <c r="C408" s="4">
-        <v>673.6799999999999</v>
+        <v>634.9400000000001</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4">
-        <v>169.1799999999999</v>
+        <v>130.4400000000001</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -14495,11 +14495,11 @@
         <v>501.48</v>
       </c>
       <c r="C409" s="4">
-        <v>674.2</v>
+        <v>635.47</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4">
-        <v>172.72</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -14510,11 +14510,11 @@
         <v>502.8</v>
       </c>
       <c r="C410" s="4">
-        <v>674.49</v>
+        <v>635.77</v>
       </c>
       <c r="D410" s="4"/>
       <c r="E410" s="4">
-        <v>171.69</v>
+        <v>132.97</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -14525,11 +14525,11 @@
         <v>501.7</v>
       </c>
       <c r="C411" s="4">
-        <v>675.0700000000001</v>
+        <v>636.37</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4">
-        <v>173.3700000000001</v>
+        <v>134.67</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -14540,11 +14540,11 @@
         <v>497.64</v>
       </c>
       <c r="C412" s="4">
-        <v>675.6900000000001</v>
+        <v>636.99</v>
       </c>
       <c r="D412" s="4"/>
       <c r="E412" s="4">
-        <v>178.0500000000001</v>
+        <v>139.35</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -14555,11 +14555,11 @@
         <v>491.91</v>
       </c>
       <c r="C413" s="4">
-        <v>676.01</v>
+        <v>637.3200000000001</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4">
-        <v>184.1</v>
+        <v>145.41</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -14570,11 +14570,11 @@
         <v>501.46</v>
       </c>
       <c r="C414" s="4">
-        <v>676.62</v>
+        <v>637.95</v>
       </c>
       <c r="D414" s="4"/>
       <c r="E414" s="4">
-        <v>175.16</v>
+        <v>136.4900000000001</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -14585,11 +14585,11 @@
         <v>506.63</v>
       </c>
       <c r="C415" s="4">
-        <v>677.0599999999999</v>
+        <v>638.4</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4">
-        <v>170.4299999999999</v>
+        <v>131.77</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -14600,11 +14600,11 @@
         <v>506.02</v>
       </c>
       <c r="C416" s="4">
-        <v>677.49</v>
+        <v>638.84</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4">
-        <v>171.47</v>
+        <v>132.8200000000001</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -14615,11 +14615,11 @@
         <v>504.05</v>
       </c>
       <c r="C417" s="4">
-        <v>677.91</v>
+        <v>639.27</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4">
-        <v>173.86</v>
+        <v>135.22</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -14630,11 +14630,11 @@
         <v>498.9</v>
       </c>
       <c r="C418" s="4">
-        <v>678.45</v>
+        <v>639.83</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4">
-        <v>179.5500000000001</v>
+        <v>140.9300000000001</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -14645,11 +14645,11 @@
         <v>504.56</v>
       </c>
       <c r="C419" s="4">
-        <v>679.02</v>
+        <v>640.41</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4">
-        <v>174.46</v>
+        <v>135.85</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -14660,11 +14660,11 @@
         <v>507.06</v>
       </c>
       <c r="C420" s="4">
-        <v>679.46</v>
+        <v>640.87</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4">
-        <v>172.4</v>
+        <v>133.81</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -14675,11 +14675,11 @@
         <v>501.24</v>
       </c>
       <c r="C421" s="4">
-        <v>679.77</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4">
-        <v>178.53</v>
+        <v>139.9399999999999</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -14690,11 +14690,11 @@
         <v>504.15</v>
       </c>
       <c r="C422" s="4">
-        <v>680.34</v>
+        <v>641.76</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4">
-        <v>176.1900000000001</v>
+        <v>137.61</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -14705,11 +14705,11 @@
         <v>505.98</v>
       </c>
       <c r="C423" s="4">
-        <v>680.9</v>
+        <v>642.33</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4">
-        <v>174.92</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -14720,11 +14720,11 @@
         <v>510.67</v>
       </c>
       <c r="C424" s="4">
-        <v>681.45</v>
+        <v>642.91</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4">
-        <v>170.78</v>
+        <v>132.24</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -14735,11 +14735,11 @@
         <v>506.85</v>
       </c>
       <c r="C425" s="4">
-        <v>681.6</v>
+        <v>643.05</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4">
-        <v>174.75</v>
+        <v>136.1999999999999</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -14750,11 +14750,11 @@
         <v>504.85</v>
       </c>
       <c r="C426" s="4">
-        <v>682.17</v>
+        <v>643.64</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4">
-        <v>177.3199999999999</v>
+        <v>138.79</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -14765,11 +14765,11 @@
         <v>501.74</v>
       </c>
       <c r="C427" s="4">
-        <v>682.67</v>
+        <v>644.15</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4">
-        <v>180.9299999999999</v>
+        <v>142.41</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -14780,11 +14780,11 @@
         <v>500.42</v>
       </c>
       <c r="C428" s="4">
-        <v>682.99</v>
+        <v>644.48</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4">
-        <v>182.57</v>
+        <v>144.06</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -14795,11 +14795,11 @@
         <v>508.82</v>
       </c>
       <c r="C429" s="4">
-        <v>683.53</v>
+        <v>645.03</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4">
-        <v>174.71</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -14810,11 +14810,11 @@
         <v>505.18</v>
       </c>
       <c r="C430" s="4">
-        <v>683.75</v>
+        <v>645.26</v>
       </c>
       <c r="D430" s="4"/>
       <c r="E430" s="4">
-        <v>178.57</v>
+        <v>140.08</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -14825,11 +14825,11 @@
         <v>502.59</v>
       </c>
       <c r="C431" s="4">
-        <v>684.09</v>
+        <v>645.6</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4">
-        <v>181.5000000000001</v>
+        <v>143.01</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -14840,11 +14840,11 @@
         <v>507.02</v>
       </c>
       <c r="C432" s="4">
-        <v>684.39</v>
+        <v>645.92</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4">
-        <v>177.37</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -14855,11 +14855,11 @@
         <v>505.2</v>
       </c>
       <c r="C433" s="4">
-        <v>684.6</v>
+        <v>646.13</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4">
-        <v>179.4</v>
+        <v>140.93</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -14870,11 +14870,11 @@
         <v>508.8</v>
       </c>
       <c r="C434" s="4">
-        <v>684.83</v>
+        <v>646.37</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4">
-        <v>176.03</v>
+        <v>137.57</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -14885,11 +14885,11 @@
         <v>501.62</v>
       </c>
       <c r="C435" s="4">
-        <v>685.08</v>
+        <v>646.62</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4">
-        <v>183.46</v>
+        <v>145</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -14900,11 +14900,11 @@
         <v>505.5</v>
       </c>
       <c r="C436" s="4">
-        <v>685.6</v>
+        <v>647.16</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4">
-        <v>180.1</v>
+        <v>141.66</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -14915,11 +14915,11 @@
         <v>494.25</v>
       </c>
       <c r="C437" s="4">
-        <v>685.9299999999999</v>
+        <v>647.49</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4">
-        <v>191.6799999999999</v>
+        <v>153.24</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -14930,11 +14930,11 @@
         <v>497.43</v>
       </c>
       <c r="C438" s="4">
-        <v>686.3099999999999</v>
+        <v>647.89</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4">
-        <v>188.8799999999999</v>
+        <v>150.46</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -14945,11 +14945,11 @@
         <v>501.73</v>
       </c>
       <c r="C439" s="4">
-        <v>686.78</v>
+        <v>648.36</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4">
-        <v>185.05</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -14960,11 +14960,11 @@
         <v>500.22</v>
       </c>
       <c r="C440" s="4">
-        <v>687.3</v>
+        <v>648.9</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4">
-        <v>187.0799999999999</v>
+        <v>148.6799999999999</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -14975,11 +14975,11 @@
         <v>504.43</v>
       </c>
       <c r="C441" s="4">
-        <v>687.75</v>
+        <v>649.36</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4">
-        <v>183.32</v>
+        <v>144.93</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -14990,11 +14990,11 @@
         <v>506.67</v>
       </c>
       <c r="C442" s="4">
-        <v>688.25</v>
+        <v>649.87</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4">
-        <v>181.58</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -15005,11 +15005,11 @@
         <v>509.9</v>
       </c>
       <c r="C443" s="4">
-        <v>688.63</v>
+        <v>650.26</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4">
-        <v>178.73</v>
+        <v>140.36</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -15020,11 +15020,11 @@
         <v>508.09</v>
       </c>
       <c r="C444" s="4">
-        <v>689.01</v>
+        <v>650.65</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4">
-        <v>180.92</v>
+        <v>142.56</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -15035,11 +15035,11 @@
         <v>503.37</v>
       </c>
       <c r="C445" s="4">
-        <v>689.64</v>
+        <v>651.29</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4">
-        <v>186.27</v>
+        <v>147.92</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -15050,11 +15050,11 @@
         <v>497.81</v>
       </c>
       <c r="C446" s="4">
-        <v>690.04</v>
+        <v>651.71</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4">
-        <v>192.23</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -15065,11 +15065,11 @@
         <v>492.5</v>
       </c>
       <c r="C447" s="4">
-        <v>690.5599999999999</v>
+        <v>652.24</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4">
-        <v>198.0599999999999</v>
+        <v>159.74</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -15080,11 +15080,11 @@
         <v>510.03</v>
       </c>
       <c r="C448" s="4">
-        <v>690.7</v>
+        <v>652.38</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4">
-        <v>180.6700000000001</v>
+        <v>142.35</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -15095,11 +15095,11 @@
         <v>509.55</v>
       </c>
       <c r="C449" s="4">
-        <v>690.83</v>
+        <v>652.51</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4">
-        <v>181.28</v>
+        <v>142.96</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -15110,11 +15110,11 @@
         <v>518.24</v>
       </c>
       <c r="C450" s="4">
-        <v>691.27</v>
+        <v>652.96</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4">
-        <v>173.03</v>
+        <v>134.72</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -15125,11 +15125,11 @@
         <v>520.99</v>
       </c>
       <c r="C451" s="4">
-        <v>691.66</v>
+        <v>653.37</v>
       </c>
       <c r="D451" s="4"/>
       <c r="E451" s="4">
-        <v>170.67</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -15140,11 +15140,11 @@
         <v>515.78</v>
       </c>
       <c r="C452" s="4">
-        <v>692.15</v>
+        <v>653.87</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4">
-        <v>176.37</v>
+        <v>138.09</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -15155,11 +15155,11 @@
         <v>513.62</v>
       </c>
       <c r="C453" s="4">
-        <v>692.71</v>
+        <v>654.4400000000001</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4">
-        <v>179.09</v>
+        <v>140.8200000000001</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -15170,11 +15170,11 @@
         <v>513.66</v>
       </c>
       <c r="C454" s="4">
-        <v>693.16</v>
+        <v>654.9</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4">
-        <v>179.5</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -15185,11 +15185,11 @@
         <v>516.61</v>
       </c>
       <c r="C455" s="4">
-        <v>693.64</v>
+        <v>655.39</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4">
-        <v>177.03</v>
+        <v>138.78</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -15200,11 +15200,11 @@
         <v>515.87</v>
       </c>
       <c r="C456" s="4">
-        <v>694.12</v>
+        <v>655.89</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4">
-        <v>178.25</v>
+        <v>140.02</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -15215,11 +15215,11 @@
         <v>514.71</v>
       </c>
       <c r="C457" s="4">
-        <v>694.75</v>
+        <v>656.53</v>
       </c>
       <c r="D457" s="4"/>
       <c r="E457" s="4">
-        <v>180.04</v>
+        <v>141.8199999999999</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -15230,11 +15230,11 @@
         <v>514.48</v>
       </c>
       <c r="C458" s="4">
-        <v>694.91</v>
+        <v>656.7</v>
       </c>
       <c r="D458" s="4"/>
       <c r="E458" s="4">
-        <v>180.4299999999999</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -15245,11 +15245,11 @@
         <v>515.38</v>
       </c>
       <c r="C459" s="4">
-        <v>695.35</v>
+        <v>657.15</v>
       </c>
       <c r="D459" s="4"/>
       <c r="E459" s="4">
-        <v>179.97</v>
+        <v>141.77</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -15260,11 +15260,11 @@
         <v>507.33</v>
       </c>
       <c r="C460" s="4">
-        <v>695.73</v>
+        <v>657.53</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4">
-        <v>188.4</v>
+        <v>150.2</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -15275,11 +15275,11 @@
         <v>514.8200000000001</v>
       </c>
       <c r="C461" s="4">
-        <v>696.16</v>
+        <v>657.98</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4">
-        <v>181.3399999999999</v>
+        <v>143.16</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -15290,11 +15290,11 @@
         <v>514.51</v>
       </c>
       <c r="C462" s="4">
-        <v>696.76</v>
+        <v>658.59</v>
       </c>
       <c r="D462" s="4"/>
       <c r="E462" s="4">
-        <v>182.25</v>
+        <v>144.08</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -15305,11 +15305,11 @@
         <v>513.39</v>
       </c>
       <c r="C463" s="4">
-        <v>697.23</v>
+        <v>659.0700000000001</v>
       </c>
       <c r="D463" s="4"/>
       <c r="E463" s="4">
-        <v>183.84</v>
+        <v>145.6800000000001</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -15320,11 +15320,11 @@
         <v>507.94</v>
       </c>
       <c r="C464" s="4">
-        <v>697.53</v>
+        <v>659.38</v>
       </c>
       <c r="D464" s="4"/>
       <c r="E464" s="4">
-        <v>189.59</v>
+        <v>151.44</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -15335,11 +15335,11 @@
         <v>509.7</v>
       </c>
       <c r="C465" s="4">
-        <v>698</v>
+        <v>659.86</v>
       </c>
       <c r="D465" s="4"/>
       <c r="E465" s="4">
-        <v>188.3</v>
+        <v>150.16</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -15350,11 +15350,11 @@
         <v>508.82</v>
       </c>
       <c r="C466" s="4">
-        <v>698.4400000000001</v>
+        <v>660.3099999999999</v>
       </c>
       <c r="D466" s="4"/>
       <c r="E466" s="4">
-        <v>189.6200000000001</v>
+        <v>151.49</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -15365,11 +15365,11 @@
         <v>497.49</v>
       </c>
       <c r="C467" s="4">
-        <v>698.86</v>
+        <v>660.74</v>
       </c>
       <c r="D467" s="4"/>
       <c r="E467" s="4">
-        <v>201.37</v>
+        <v>163.25</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -15380,11 +15380,11 @@
         <v>497.34</v>
       </c>
       <c r="C468" s="4">
-        <v>699.29</v>
+        <v>661.1900000000001</v>
       </c>
       <c r="D468" s="4"/>
       <c r="E468" s="4">
-        <v>201.95</v>
+        <v>163.8500000000001</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -15395,11 +15395,11 @@
         <v>495.13</v>
       </c>
       <c r="C469" s="4">
-        <v>699.61</v>
+        <v>661.51</v>
       </c>
       <c r="D469" s="4"/>
       <c r="E469" s="4">
-        <v>204.48</v>
+        <v>166.38</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -15410,11 +15410,11 @@
         <v>493.85</v>
       </c>
       <c r="C470" s="4">
-        <v>700</v>
+        <v>661.91</v>
       </c>
       <c r="D470" s="4"/>
       <c r="E470" s="4">
-        <v>206.15</v>
+        <v>168.0599999999999</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -15425,11 +15425,11 @@
         <v>494.28</v>
       </c>
       <c r="C471" s="4">
-        <v>700.3099999999999</v>
+        <v>662.24</v>
       </c>
       <c r="D471" s="4"/>
       <c r="E471" s="4">
-        <v>206.03</v>
+        <v>167.96</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -15440,11 +15440,11 @@
         <v>498.04</v>
       </c>
       <c r="C472" s="4">
-        <v>700.58</v>
+        <v>662.51</v>
       </c>
       <c r="D472" s="4"/>
       <c r="E472" s="4">
-        <v>202.54</v>
+        <v>164.47</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -15455,11 +15455,11 @@
         <v>506.08</v>
       </c>
       <c r="C473" s="4">
-        <v>700.88</v>
+        <v>662.8099999999999</v>
       </c>
       <c r="D473" s="4"/>
       <c r="E473" s="4">
-        <v>194.8</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -15470,11 +15470,11 @@
         <v>507.31</v>
       </c>
       <c r="C474" s="4">
-        <v>701.33</v>
+        <v>663.28</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4">
-        <v>194.02</v>
+        <v>155.97</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -15485,11 +15485,11 @@
         <v>497.99</v>
       </c>
       <c r="C475" s="4">
-        <v>701.55</v>
+        <v>663.5</v>
       </c>
       <c r="D475" s="4"/>
       <c r="E475" s="4">
-        <v>203.5599999999999</v>
+        <v>165.51</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -15500,11 +15500,11 @@
         <v>502.51</v>
       </c>
       <c r="C476" s="4">
-        <v>701.67</v>
+        <v>663.63</v>
       </c>
       <c r="D476" s="4"/>
       <c r="E476" s="4">
-        <v>199.16</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -15515,11 +15515,11 @@
         <v>504.41</v>
       </c>
       <c r="C477" s="4">
-        <v>702.09</v>
+        <v>664.0599999999999</v>
       </c>
       <c r="D477" s="4"/>
       <c r="E477" s="4">
-        <v>197.68</v>
+        <v>159.6499999999999</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -15530,11 +15530,11 @@
         <v>501.78</v>
       </c>
       <c r="C478" s="4">
-        <v>702.39</v>
+        <v>664.37</v>
       </c>
       <c r="D478" s="4"/>
       <c r="E478" s="4">
-        <v>200.61</v>
+        <v>162.59</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -15545,11 +15545,11 @@
         <v>504.86</v>
       </c>
       <c r="C479" s="4">
-        <v>702.5700000000001</v>
+        <v>664.55</v>
       </c>
       <c r="D479" s="4"/>
       <c r="E479" s="4">
-        <v>197.71</v>
+        <v>159.6899999999999</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -15560,11 +15560,11 @@
         <v>504.55</v>
       </c>
       <c r="C480" s="4">
-        <v>702.73</v>
+        <v>664.71</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="4">
-        <v>198.18</v>
+        <v>160.16</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -15575,11 +15575,11 @@
         <v>496.05</v>
       </c>
       <c r="C481" s="4">
-        <v>703.0599999999999</v>
+        <v>665.05</v>
       </c>
       <c r="D481" s="4"/>
       <c r="E481" s="4">
-        <v>207.0099999999999</v>
+        <v>168.9999999999999</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -15590,11 +15590,11 @@
         <v>498.98</v>
       </c>
       <c r="C482" s="4">
-        <v>703.3</v>
+        <v>665.3</v>
       </c>
       <c r="D482" s="4"/>
       <c r="E482" s="4">
-        <v>204.3199999999999</v>
+        <v>166.3199999999999</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -15605,11 +15605,11 @@
         <v>499.33</v>
       </c>
       <c r="C483" s="4">
-        <v>703.65</v>
+        <v>665.66</v>
       </c>
       <c r="D483" s="4"/>
       <c r="E483" s="4">
-        <v>204.32</v>
+        <v>166.33</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -15620,11 +15620,11 @@
         <v>497.98</v>
       </c>
       <c r="C484" s="4">
-        <v>703.9400000000001</v>
+        <v>665.95</v>
       </c>
       <c r="D484" s="4"/>
       <c r="E484" s="4">
-        <v>205.96</v>
+        <v>167.97</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -15635,11 +15635,11 @@
         <v>496.86</v>
       </c>
       <c r="C485" s="4">
-        <v>704.0599999999999</v>
+        <v>666.08</v>
       </c>
       <c r="D485" s="4"/>
       <c r="E485" s="4">
-        <v>207.1999999999999</v>
+        <v>169.22</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -15650,11 +15650,11 @@
         <v>490.97</v>
       </c>
       <c r="C486" s="4">
-        <v>704.38</v>
+        <v>666.41</v>
       </c>
       <c r="D486" s="4"/>
       <c r="E486" s="4">
-        <v>213.41</v>
+        <v>175.4399999999999</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -15665,11 +15665,11 @@
         <v>496.29</v>
       </c>
       <c r="C487" s="4">
-        <v>704.59</v>
+        <v>666.62</v>
       </c>
       <c r="D487" s="4"/>
       <c r="E487" s="4">
-        <v>208.3</v>
+        <v>170.33</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -15680,11 +15680,11 @@
         <v>493.25</v>
       </c>
       <c r="C488" s="4">
-        <v>704.22</v>
+        <v>666.24</v>
       </c>
       <c r="D488" s="4"/>
       <c r="E488" s="4">
-        <v>210.97</v>
+        <v>172.99</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -15695,11 +15695,11 @@
         <v>488.73</v>
       </c>
       <c r="C489" s="4">
-        <v>704.4</v>
+        <v>666.42</v>
       </c>
       <c r="D489" s="4"/>
       <c r="E489" s="4">
-        <v>215.67</v>
+        <v>177.6899999999999</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -15710,11 +15710,11 @@
         <v>485.92</v>
       </c>
       <c r="C490" s="4">
-        <v>704.34</v>
+        <v>666.36</v>
       </c>
       <c r="D490" s="4"/>
       <c r="E490" s="4">
-        <v>218.42</v>
+        <v>180.44</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -15725,11 +15725,11 @@
         <v>505.27</v>
       </c>
       <c r="C491" s="4">
-        <v>704.45</v>
+        <v>666.48</v>
       </c>
       <c r="D491" s="4"/>
       <c r="E491" s="4">
-        <v>199.1800000000001</v>
+        <v>161.21</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -15740,11 +15740,11 @@
         <v>514.77</v>
       </c>
       <c r="C492" s="4">
-        <v>704.79</v>
+        <v>666.8200000000001</v>
       </c>
       <c r="D492" s="4"/>
       <c r="E492" s="4">
-        <v>190.02</v>
+        <v>152.0500000000001</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -15755,11 +15755,11 @@
         <v>509.56</v>
       </c>
       <c r="C493" s="4">
-        <v>704.7</v>
+        <v>666.74</v>
       </c>
       <c r="D493" s="4"/>
       <c r="E493" s="4">
-        <v>195.14</v>
+        <v>157.18</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -15770,11 +15770,11 @@
         <v>510.65</v>
       </c>
       <c r="C494" s="4">
-        <v>705</v>
+        <v>667.04</v>
       </c>
       <c r="D494" s="4"/>
       <c r="E494" s="4">
-        <v>194.35</v>
+        <v>156.39</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -15785,11 +15785,11 @@
         <v>509.61</v>
       </c>
       <c r="C495" s="4">
-        <v>705.33</v>
+        <v>667.38</v>
       </c>
       <c r="D495" s="4"/>
       <c r="E495" s="4">
-        <v>195.72</v>
+        <v>157.77</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -15800,11 +15800,11 @@
         <v>519.9</v>
       </c>
       <c r="C496" s="4">
-        <v>705.55</v>
+        <v>667.61</v>
       </c>
       <c r="D496" s="4"/>
       <c r="E496" s="4">
-        <v>185.65</v>
+        <v>147.71</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -15815,11 +15815,11 @@
         <v>515.7</v>
       </c>
       <c r="C497" s="4">
-        <v>705.8099999999999</v>
+        <v>667.87</v>
       </c>
       <c r="D497" s="4"/>
       <c r="E497" s="4">
-        <v>190.1099999999999</v>
+        <v>152.17</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -15830,11 +15830,11 @@
         <v>502.94</v>
       </c>
       <c r="C498" s="4">
-        <v>706.11</v>
+        <v>668.1799999999999</v>
       </c>
       <c r="D498" s="4"/>
       <c r="E498" s="4">
-        <v>203.17</v>
+        <v>165.24</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -15845,11 +15845,11 @@
         <v>493.44</v>
       </c>
       <c r="C499" s="4">
-        <v>706.34</v>
+        <v>668.41</v>
       </c>
       <c r="D499" s="4"/>
       <c r="E499" s="4">
-        <v>212.9</v>
+        <v>174.97</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -15860,11 +15860,11 @@
         <v>516.97</v>
       </c>
       <c r="C500" s="4">
-        <v>706.59</v>
+        <v>668.67</v>
       </c>
       <c r="D500" s="4"/>
       <c r="E500" s="4">
-        <v>189.62</v>
+        <v>151.6999999999999</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -15875,11 +15875,11 @@
         <v>517.22</v>
       </c>
       <c r="C501" s="4">
-        <v>706.77</v>
+        <v>668.86</v>
       </c>
       <c r="D501" s="4"/>
       <c r="E501" s="4">
-        <v>189.55</v>
+        <v>151.64</v>
       </c>
     </row>
     <row r="502" spans="1:5">
@@ -15890,11 +15890,11 @@
         <v>516.5700000000001</v>
       </c>
       <c r="C502" s="4">
-        <v>707.05</v>
+        <v>669.14</v>
       </c>
       <c r="D502" s="4"/>
       <c r="E502" s="4">
-        <v>190.4799999999999</v>
+        <v>152.5699999999999</v>
       </c>
     </row>
     <row r="503" spans="1:5">
@@ -15905,11 +15905,11 @@
         <v>506.87</v>
       </c>
       <c r="C503" s="4">
-        <v>707.33</v>
+        <v>669.4299999999999</v>
       </c>
       <c r="D503" s="4"/>
       <c r="E503" s="4">
-        <v>200.46</v>
+        <v>162.5599999999999</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -15920,11 +15920,11 @@
         <v>503.23</v>
       </c>
       <c r="C504" s="4">
-        <v>707.59</v>
+        <v>669.6900000000001</v>
       </c>
       <c r="D504" s="4"/>
       <c r="E504" s="4">
-        <v>204.36</v>
+        <v>166.46</v>
       </c>
     </row>
     <row r="505" spans="1:5">
@@ -15935,11 +15935,11 @@
         <v>511.43</v>
       </c>
       <c r="C505" s="4">
-        <v>707.89</v>
+        <v>670</v>
       </c>
       <c r="D505" s="4"/>
       <c r="E505" s="4">
-        <v>196.46</v>
+        <v>158.57</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -15950,11 +15950,11 @@
         <v>506.15</v>
       </c>
       <c r="C506" s="4">
-        <v>708.11</v>
+        <v>670.23</v>
       </c>
       <c r="D506" s="4"/>
       <c r="E506" s="4">
-        <v>201.96</v>
+        <v>164.08</v>
       </c>
     </row>
     <row r="507" spans="1:5">
@@ -15965,11 +15965,11 @@
         <v>519.78</v>
       </c>
       <c r="C507" s="4">
-        <v>708.29</v>
+        <v>670.42</v>
       </c>
       <c r="D507" s="4"/>
       <c r="E507" s="4">
-        <v>188.51</v>
+        <v>150.64</v>
       </c>
     </row>
     <row r="508" spans="1:5">
@@ -15980,11 +15980,11 @@
         <v>528.41</v>
       </c>
       <c r="C508" s="4">
-        <v>708.26</v>
+        <v>670.38</v>
       </c>
       <c r="D508" s="4"/>
       <c r="E508" s="4">
-        <v>179.85</v>
+        <v>141.97</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -15995,11 +15995,11 @@
         <v>490.5</v>
       </c>
       <c r="C509" s="4">
-        <v>708.02</v>
+        <v>670.13</v>
       </c>
       <c r="D509" s="4"/>
       <c r="E509" s="4">
-        <v>217.52</v>
+        <v>179.63</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -16010,11 +16010,11 @@
         <v>514.4</v>
       </c>
       <c r="C510" s="4">
-        <v>707.92</v>
+        <v>670.03</v>
       </c>
       <c r="D510" s="4"/>
       <c r="E510" s="4">
-        <v>193.52</v>
+        <v>155.63</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -16025,11 +16025,11 @@
         <v>509.1</v>
       </c>
       <c r="C511" s="4">
-        <v>707.8</v>
+        <v>669.91</v>
       </c>
       <c r="D511" s="4"/>
       <c r="E511" s="4">
-        <v>198.6999999999999</v>
+        <v>160.8099999999999</v>
       </c>
     </row>
     <row r="512" spans="1:5">
@@ -16040,11 +16040,11 @@
         <v>483.4</v>
       </c>
       <c r="C512" s="4">
-        <v>707.66</v>
+        <v>669.76</v>
       </c>
       <c r="D512" s="4"/>
       <c r="E512" s="4">
-        <v>224.26</v>
+        <v>186.36</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -16055,11 +16055,11 @@
         <v>535</v>
       </c>
       <c r="C513" s="4">
-        <v>707.64</v>
+        <v>669.75</v>
       </c>
       <c r="D513" s="4"/>
       <c r="E513" s="4">
-        <v>172.64</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -16070,11 +16070,11 @@
         <v>549.79</v>
       </c>
       <c r="C514" s="4">
-        <v>707.5700000000001</v>
+        <v>669.67</v>
       </c>
       <c r="D514" s="4"/>
       <c r="E514" s="4">
-        <v>157.7800000000001</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -16085,11 +16085,11 @@
         <v>500.8</v>
       </c>
       <c r="C515" s="4">
-        <v>707.46</v>
+        <v>669.5599999999999</v>
       </c>
       <c r="D515" s="4"/>
       <c r="E515" s="4">
-        <v>206.66</v>
+        <v>168.7599999999999</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -16100,11 +16100,11 @@
         <v>523.9</v>
       </c>
       <c r="C516" s="4">
-        <v>707.4400000000001</v>
+        <v>669.54</v>
       </c>
       <c r="D516" s="4"/>
       <c r="E516" s="4">
-        <v>183.5400000000001</v>
+        <v>145.64</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -16115,11 +16115,11 @@
         <v>540.83</v>
       </c>
       <c r="C517" s="4">
-        <v>707.03</v>
+        <v>669.12</v>
       </c>
       <c r="D517" s="4"/>
       <c r="E517" s="4">
-        <v>166.1999999999999</v>
+        <v>128.29</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -16130,11 +16130,11 @@
         <v>514.26</v>
       </c>
       <c r="C518" s="4">
-        <v>706.97</v>
+        <v>669.0599999999999</v>
       </c>
       <c r="D518" s="4"/>
       <c r="E518" s="4">
-        <v>192.71</v>
+        <v>154.8</v>
       </c>
     </row>
   </sheetData>
@@ -16187,13 +16187,13 @@
         <v>1.67</v>
       </c>
       <c r="C2" s="4">
-        <v>-8.44</v>
+        <v>-8.23</v>
       </c>
       <c r="D2" s="4">
-        <v>12.33</v>
+        <v>12.22</v>
       </c>
       <c r="E2" s="4">
-        <v>89.7</v>
+        <v>90.8</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>92</v>
@@ -16210,13 +16210,13 @@
         <v>1.53</v>
       </c>
       <c r="C3" s="4">
-        <v>-7.83</v>
+        <v>-7.63</v>
       </c>
       <c r="D3" s="4">
-        <v>11.68</v>
+        <v>11.57</v>
       </c>
       <c r="E3" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>92</v>
@@ -16233,10 +16233,10 @@
         <v>1.41</v>
       </c>
       <c r="C4" s="4">
-        <v>-9.06</v>
+        <v>-8.85</v>
       </c>
       <c r="D4" s="4">
-        <v>12.62</v>
+        <v>12.52</v>
       </c>
       <c r="E4" s="4">
         <v>92</v>
@@ -16256,10 +16256,10 @@
         <v>1.3</v>
       </c>
       <c r="C5" s="4">
-        <v>-9.07</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="D5" s="4">
-        <v>12.53</v>
+        <v>12.42</v>
       </c>
       <c r="E5" s="4">
         <v>92</v>
@@ -16279,10 +16279,10 @@
         <v>1.19</v>
       </c>
       <c r="C6" s="4">
-        <v>-9.279999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="D6" s="4">
-        <v>12.58</v>
+        <v>12.47</v>
       </c>
       <c r="E6" s="4">
         <v>92</v>
@@ -16302,10 +16302,10 @@
         <v>1.1</v>
       </c>
       <c r="C7" s="4">
-        <v>-9.140000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="D7" s="4">
-        <v>12.29</v>
+        <v>12.17</v>
       </c>
       <c r="E7" s="4">
         <v>92</v>
@@ -16325,13 +16325,13 @@
         <v>1.01</v>
       </c>
       <c r="C8" s="4">
-        <v>-7.77</v>
+        <v>-7.56</v>
       </c>
       <c r="D8" s="4">
-        <v>10.91</v>
+        <v>10.79</v>
       </c>
       <c r="E8" s="4">
-        <v>86.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>92</v>
@@ -16348,16 +16348,16 @@
         <v>0.93</v>
       </c>
       <c r="C9" s="4">
-        <v>-5.84</v>
+        <v>-5.63</v>
       </c>
       <c r="D9" s="4">
-        <v>9.039999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="E9" s="4">
-        <v>77.8</v>
+        <v>74.8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>95</v>
@@ -16371,13 +16371,13 @@
         <v>0.85</v>
       </c>
       <c r="C10" s="4">
-        <v>-4.08</v>
+        <v>-3.87</v>
       </c>
       <c r="D10" s="4">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="E10" s="4">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>96</v>
@@ -16394,16 +16394,16 @@
         <v>0.79</v>
       </c>
       <c r="C11" s="4">
-        <v>-3.16</v>
+        <v>-2.95</v>
       </c>
       <c r="D11" s="4">
-        <v>6.18</v>
+        <v>6.06</v>
       </c>
       <c r="E11" s="4">
-        <v>58.9</v>
+        <v>53.9</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>95</v>
@@ -16417,19 +16417,19 @@
         <v>0.72</v>
       </c>
       <c r="C12" s="4">
-        <v>-3.56</v>
+        <v>-3.35</v>
       </c>
       <c r="D12" s="4">
-        <v>6.68</v>
+        <v>6.55</v>
       </c>
       <c r="E12" s="4">
-        <v>59.9</v>
+        <v>54.8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -16440,19 +16440,19 @@
         <v>0.67</v>
       </c>
       <c r="C13" s="4">
-        <v>-5.16</v>
+        <v>-4.96</v>
       </c>
       <c r="D13" s="4">
-        <v>8.02</v>
+        <v>7.9</v>
       </c>
       <c r="E13" s="4">
-        <v>66.3</v>
+        <v>61.2</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -16463,19 +16463,19 @@
         <v>0.61</v>
       </c>
       <c r="C14" s="4">
-        <v>-7.13</v>
+        <v>-6.93</v>
       </c>
       <c r="D14" s="4">
-        <v>9.73</v>
+        <v>9.6</v>
       </c>
       <c r="E14" s="4">
-        <v>76.3</v>
+        <v>71.2</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -16486,19 +16486,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C15" s="4">
-        <v>-8.859999999999999</v>
+        <v>-8.65</v>
       </c>
       <c r="D15" s="4">
-        <v>11.29</v>
+        <v>11.17</v>
       </c>
       <c r="E15" s="4">
-        <v>88.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -16509,10 +16509,10 @@
         <v>0.52</v>
       </c>
       <c r="C16" s="4">
-        <v>-9.630000000000001</v>
+        <v>-9.42</v>
       </c>
       <c r="D16" s="4">
-        <v>12.04</v>
+        <v>11.92</v>
       </c>
       <c r="E16" s="4">
         <v>92</v>
@@ -16521,7 +16521,7 @@
         <v>92</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -16532,19 +16532,19 @@
         <v>0.48</v>
       </c>
       <c r="C17" s="4">
-        <v>-9.08</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="D17" s="4">
-        <v>11.5</v>
+        <v>11.38</v>
       </c>
       <c r="E17" s="4">
-        <v>91.7</v>
+        <v>89.2</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -16555,19 +16555,19 @@
         <v>0.44</v>
       </c>
       <c r="C18" s="4">
-        <v>-7.51</v>
+        <v>-7.31</v>
       </c>
       <c r="D18" s="4">
-        <v>10.02</v>
+        <v>9.9</v>
       </c>
       <c r="E18" s="4">
-        <v>83.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -16578,19 +16578,19 @@
         <v>0.4</v>
       </c>
       <c r="C19" s="4">
-        <v>-5.62</v>
+        <v>-5.42</v>
       </c>
       <c r="D19" s="4">
-        <v>8.26</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E19" s="4">
-        <v>71.3</v>
+        <v>66.3</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -16601,19 +16601,19 @@
         <v>0.37</v>
       </c>
       <c r="C20" s="4">
-        <v>-4.05</v>
+        <v>-3.84</v>
       </c>
       <c r="D20" s="4">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="E20" s="4">
-        <v>61.6</v>
+        <v>56.5</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -16624,19 +16624,19 @@
         <v>0.34</v>
       </c>
       <c r="C21" s="4">
-        <v>-3.05</v>
+        <v>-2.84</v>
       </c>
       <c r="D21" s="4">
-        <v>5.85</v>
+        <v>5.73</v>
       </c>
       <c r="E21" s="4">
-        <v>55.1</v>
+        <v>50.2</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -16647,19 +16647,19 @@
         <v>0.33</v>
       </c>
       <c r="C22" s="4">
-        <v>-2.75</v>
+        <v>-2.54</v>
       </c>
       <c r="D22" s="4">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="E22" s="4">
-        <v>51.2</v>
+        <v>48</v>
       </c>
       <c r="F22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -16670,19 +16670,19 @@
         <v>0.33</v>
       </c>
       <c r="C23" s="4">
-        <v>-2.64</v>
+        <v>-2.44</v>
       </c>
       <c r="D23" s="4">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="E23" s="4">
-        <v>48.9</v>
+        <v>47</v>
       </c>
       <c r="F23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -16693,19 +16693,19 @@
         <v>0.33</v>
       </c>
       <c r="C24" s="4">
-        <v>-2.61</v>
+        <v>-2.4</v>
       </c>
       <c r="D24" s="4">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="E24" s="4">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -16716,16 +16716,16 @@
         <v>0.33</v>
       </c>
       <c r="C25" s="4">
-        <v>-2.59</v>
+        <v>-2.39</v>
       </c>
       <c r="D25" s="4">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="E25" s="4">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>99</v>
@@ -16739,16 +16739,16 @@
         <v>0.33</v>
       </c>
       <c r="C26" s="4">
-        <v>-2.59</v>
+        <v>-2.39</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
       </c>
       <c r="E26" s="4">
-        <v>45.7</v>
+        <v>46.6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>99</v>
@@ -22009,7 +22009,7 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>112</v>
